--- a/research/traditional_assets/database/data/finland/finland_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_telecom_services.xlsx
@@ -650,10 +650,10 @@
         <v>0.3290977383521138</v>
       </c>
       <c r="X2">
-        <v>0.07638257427983716</v>
+        <v>0.07636669527008444</v>
       </c>
       <c r="Y2">
-        <v>0.2527151640722767</v>
+        <v>0.2527310430820294</v>
       </c>
       <c r="Z2">
         <v>1.633850076789036</v>
@@ -662,10 +662,10 @@
         <v>0.2995051729392402</v>
       </c>
       <c r="AB2">
-        <v>0.07122905151761018</v>
+        <v>0.07121608508385163</v>
       </c>
       <c r="AC2">
-        <v>0.22827612142163</v>
+        <v>0.2282890878553885</v>
       </c>
       <c r="AD2">
         <v>1539.8</v>
@@ -787,10 +787,10 @@
         <v>0.3290977383521138</v>
       </c>
       <c r="X3">
-        <v>0.07638257427983716</v>
+        <v>0.07636669527008444</v>
       </c>
       <c r="Y3">
-        <v>0.2527151640722767</v>
+        <v>0.2527310430820294</v>
       </c>
       <c r="Z3">
         <v>1.633850076789036</v>
@@ -799,10 +799,10 @@
         <v>0.2995051729392402</v>
       </c>
       <c r="AB3">
-        <v>0.07122905151761018</v>
+        <v>0.07121608508385163</v>
       </c>
       <c r="AC3">
-        <v>0.22827612142163</v>
+        <v>0.2282890878553885</v>
       </c>
       <c r="AD3">
         <v>1539.8</v>
@@ -1139,49 +1139,49 @@
         <v>11.8067415730337</v>
       </c>
       <c r="F2">
-        <v>6.80085544728251</v>
+        <v>3.06538212881635</v>
       </c>
       <c r="G2">
         <v>1.86293883074656</v>
       </c>
       <c r="H2">
-        <v>1.62504251473416</v>
+        <v>3.45321534381009</v>
       </c>
       <c r="I2">
         <v>0.183423024454355</v>
       </c>
       <c r="J2">
-        <v>0.16</v>
+        <v>0.34</v>
       </c>
       <c r="K2">
         <v>6946.7</v>
       </c>
       <c r="L2">
-        <v>7222.94691102985</v>
+        <v>5755.40245069122</v>
       </c>
       <c r="M2">
         <v>8415.29756463332</v>
       </c>
       <c r="N2">
-        <v>8492.28252137118</v>
+        <v>8556.015622666549</v>
       </c>
       <c r="O2">
         <v>1560.39756463332</v>
       </c>
       <c r="P2">
-        <v>1361.13561034133</v>
+        <v>2892.41317197533</v>
       </c>
       <c r="Q2">
-        <v>0.07122905151761021</v>
+        <v>0.0712160850838516</v>
       </c>
       <c r="R2">
-        <v>0.070831461178926</v>
+        <v>0.07049476604762139</v>
       </c>
       <c r="S2">
         <v>0.0482861955533515</v>
       </c>
       <c r="T2">
-        <v>0.0454061955533515</v>
+        <v>0.0474061955533515</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1190,20 +1190,20 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="W2">
-        <v>0.0763825742798372</v>
+        <v>0.0763666952700844</v>
       </c>
       <c r="X2">
-        <v>0.0756743689171306</v>
+        <v>0.0823888781204271</v>
       </c>
       <c r="Y2">
         <v>0.628483426757138</v>
       </c>
       <c r="Z2">
-        <v>0.613929539660229</v>
+        <v>0.752305844617456</v>
       </c>
       <c r="AA2">
         <v>1539.8</v>
@@ -1236,7 +1236,7 @@
         <v>6946.7</v>
       </c>
       <c r="AK2">
-        <v>0.0486609081127847</v>
+        <v>0.04863564251455779</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.0717240391429646</v>
+        <v>0.07171057892648268</v>
       </c>
       <c r="C2">
-        <v>8413.182461766122</v>
+        <v>8413.273980742724</v>
       </c>
       <c r="D2">
-        <v>8321.382461766123</v>
+        <v>8321.473980742725</v>
       </c>
       <c r="E2">
         <v>-1560.397564633318</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.0717240391429646</v>
+        <v>0.07171057892648268</v>
       </c>
       <c r="T2">
         <v>0.532748774085323</v>
       </c>
       <c r="U2">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V2">
         <v>0.2</v>
       </c>
       <c r="W2">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07165945302021219</v>
+        <v>0.07163481972416322</v>
       </c>
       <c r="C3">
-        <v>8340.246469395361</v>
+        <v>8342.441358387407</v>
       </c>
       <c r="D3">
-        <v>8333.517445041694</v>
+        <v>8335.71233403374</v>
       </c>
       <c r="E3">
         <v>-1475.326588986985</v>
@@ -1539,37 +1539,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M3">
-        <v>4.734858621928795</v>
+        <v>4.615759256023928</v>
       </c>
       <c r="N3">
-        <v>520.6651413780713</v>
+        <v>520.7842407439762</v>
       </c>
       <c r="O3">
-        <v>104.1330282756143</v>
+        <v>104.1568481487952</v>
       </c>
       <c r="P3">
-        <v>416.5321131024571</v>
+        <v>416.6273925951809</v>
       </c>
       <c r="Q3">
-        <v>728.7321131024571</v>
+        <v>728.827392595181</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07193352632795826</v>
+        <v>0.07191995734205021</v>
       </c>
       <c r="T3">
         <v>0.5370538146839923</v>
       </c>
       <c r="U3">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V3">
         <v>0.2</v>
       </c>
       <c r="W3">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>110.9642424309541</v>
+        <v>113.827427050991</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07159486689745977</v>
+        <v>0.07155906052184377</v>
       </c>
       <c r="C4">
-        <v>8267.345921345999</v>
+        <v>8271.657544255067</v>
       </c>
       <c r="D4">
-        <v>8345.687872638666</v>
+        <v>8349.999495547734</v>
       </c>
       <c r="E4">
         <v>-1390.255613340652</v>
@@ -1621,37 +1621,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M4">
-        <v>9.469717243857589</v>
+        <v>9.231518512047856</v>
       </c>
       <c r="N4">
-        <v>515.9302827561424</v>
+        <v>516.1684814879522</v>
       </c>
       <c r="O4">
-        <v>103.1860565512285</v>
+        <v>103.2336962975905</v>
       </c>
       <c r="P4">
-        <v>412.744226204914</v>
+        <v>412.9347851903618</v>
       </c>
       <c r="Q4">
-        <v>724.944226204914</v>
+        <v>725.1347851903618</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07214728876162524</v>
+        <v>0.07213360878650689</v>
       </c>
       <c r="T4">
         <v>0.5414467132540629</v>
       </c>
       <c r="U4">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>55.48212121547705</v>
+        <v>56.9137135254955</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07153028077470736</v>
+        <v>0.07148330131952432</v>
       </c>
       <c r="C5">
-        <v>8194.48097313584</v>
+        <v>8200.922789744103</v>
       </c>
       <c r="D5">
-        <v>8357.89390007484</v>
+        <v>8364.335716683103</v>
       </c>
       <c r="E5">
         <v>-1305.184637694319</v>
@@ -1703,37 +1703,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M5">
-        <v>14.20457586578638</v>
+        <v>13.84727776807179</v>
       </c>
       <c r="N5">
-        <v>511.1954241342137</v>
+        <v>511.5527222319283</v>
       </c>
       <c r="O5">
-        <v>102.2390848268427</v>
+        <v>102.3105444463857</v>
       </c>
       <c r="P5">
-        <v>408.956339307371</v>
+        <v>409.2421777855427</v>
       </c>
       <c r="Q5">
-        <v>721.1563393073709</v>
+        <v>721.4421777855426</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07236545866815135</v>
+        <v>0.07235166541538533</v>
       </c>
       <c r="T5">
         <v>0.5459301870523824</v>
       </c>
       <c r="U5">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>36.98808081031804</v>
+        <v>37.94247568366366</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07146569465195494</v>
+        <v>0.07140754211720488</v>
       </c>
       <c r="C6">
-        <v>8121.651781193838</v>
+        <v>8130.237347982388</v>
       </c>
       <c r="D6">
-        <v>8370.135683779172</v>
+        <v>8378.721250567722</v>
       </c>
       <c r="E6">
         <v>-1220.113662047986</v>
@@ -1785,37 +1785,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M6">
-        <v>18.93943448771518</v>
+        <v>18.46303702409571</v>
       </c>
       <c r="N6">
-        <v>506.4605655122849</v>
+        <v>506.9369629759044</v>
       </c>
       <c r="O6">
-        <v>101.292113102457</v>
+        <v>101.3873925951809</v>
       </c>
       <c r="P6">
-        <v>405.1684524098279</v>
+        <v>405.5495703807235</v>
       </c>
       <c r="Q6">
-        <v>717.3684524098279</v>
+        <v>717.7495703807235</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07258817378106341</v>
+        <v>0.07257426489069876</v>
       </c>
       <c r="T6">
         <v>0.5505070665548337</v>
       </c>
       <c r="U6">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.74106060773853</v>
+        <v>28.45685676274775</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07140110852920252</v>
+        <v>0.07133178291488543</v>
       </c>
       <c r="C7">
-        <v>8048.858502866778</v>
+        <v>8059.601473842185</v>
       </c>
       <c r="D7">
-        <v>8382.413381098444</v>
+        <v>8393.156352073851</v>
       </c>
       <c r="E7">
         <v>-1135.042686401652</v>
@@ -1867,37 +1867,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M7">
-        <v>23.67429310964398</v>
+        <v>23.07879628011964</v>
       </c>
       <c r="N7">
-        <v>501.7257068903561</v>
+        <v>502.3212037198804</v>
       </c>
       <c r="O7">
-        <v>100.3451413780712</v>
+        <v>100.4642407439761</v>
       </c>
       <c r="P7">
-        <v>401.3805655122849</v>
+        <v>401.8569629759044</v>
       </c>
       <c r="Q7">
-        <v>713.5805655122849</v>
+        <v>714.0569629759043</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07281557763319468</v>
+        <v>0.07280155067075564</v>
       </c>
       <c r="T7">
         <v>0.5551803014152312</v>
       </c>
       <c r="U7">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.19284848619082</v>
+        <v>22.76548541019819</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07133652240645012</v>
+        <v>0.07125602371256598</v>
       </c>
       <c r="C8">
-        <v>7976.101296426005</v>
+        <v>7989.015423955188</v>
       </c>
       <c r="D8">
-        <v>8394.727150304005</v>
+        <v>8407.641277833187</v>
       </c>
       <c r="E8">
         <v>-1049.971710755319</v>
@@ -1949,37 +1949,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M8">
-        <v>28.40915173157277</v>
+        <v>27.69455553614357</v>
       </c>
       <c r="N8">
-        <v>496.9908482684273</v>
+        <v>497.7054444638565</v>
       </c>
       <c r="O8">
-        <v>99.39816965368547</v>
+        <v>99.54108889277131</v>
       </c>
       <c r="P8">
-        <v>397.5926786147419</v>
+        <v>398.1643555710852</v>
       </c>
       <c r="Q8">
-        <v>709.7926786147418</v>
+        <v>710.3643555710852</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07304781986515854</v>
+        <v>0.07303367231847328</v>
       </c>
       <c r="T8">
         <v>0.5599529668045735</v>
       </c>
       <c r="U8">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.49404040515902</v>
+        <v>18.97123784183183</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.0712719362836977</v>
+        <v>0.07118026451024652</v>
       </c>
       <c r="C9">
-        <v>7903.38032107425</v>
+        <v>7918.479456727742</v>
       </c>
       <c r="D9">
-        <v>8407.077150598583</v>
+        <v>8422.176286252075</v>
       </c>
       <c r="E9">
         <v>-964.9007351089861</v>
@@ -2031,37 +2031,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M9">
-        <v>33.14401035350156</v>
+        <v>32.3103147921675</v>
       </c>
       <c r="N9">
-        <v>492.2559896464985</v>
+        <v>493.0896852078326</v>
       </c>
       <c r="O9">
-        <v>98.45119792929971</v>
+        <v>98.61793704156652</v>
       </c>
       <c r="P9">
-        <v>393.8047917171988</v>
+        <v>394.4717481662661</v>
       </c>
       <c r="Q9">
-        <v>706.0047917171987</v>
+        <v>706.6717481662661</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07328505655372376</v>
+        <v>0.07327078582958271</v>
       </c>
       <c r="T9">
         <v>0.5648282701592779</v>
       </c>
       <c r="U9">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.85203463299344</v>
+        <v>16.26106100728443</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.0712073501609453</v>
+        <v>0.07110450530792707</v>
       </c>
       <c r="C10">
-        <v>7830.695736952459</v>
+        <v>7847.993832356191</v>
       </c>
       <c r="D10">
-        <v>8419.463542123125</v>
+        <v>8436.761637526857</v>
       </c>
       <c r="E10">
         <v>-879.829759462653</v>
@@ -2113,37 +2113,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M10">
-        <v>37.87886897543036</v>
+        <v>36.92607404819142</v>
       </c>
       <c r="N10">
-        <v>487.5211310245697</v>
+        <v>488.4739259518087</v>
       </c>
       <c r="O10">
-        <v>97.50422620491395</v>
+        <v>97.69478519036174</v>
       </c>
       <c r="P10">
-        <v>390.0169048196558</v>
+        <v>390.7791407614469</v>
       </c>
       <c r="Q10">
-        <v>702.2169048196558</v>
+        <v>702.9791407614468</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07352745056160562</v>
+        <v>0.07351305398223799</v>
       </c>
       <c r="T10">
         <v>0.5698095583695193</v>
       </c>
       <c r="U10">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>13.87053030386926</v>
+        <v>14.22842838137387</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07114276403819288</v>
+        <v>0.07102874610560764</v>
       </c>
       <c r="C11">
-        <v>7758.047705146753</v>
+        <v>7777.55881284243</v>
       </c>
       <c r="D11">
-        <v>8431.886485963752</v>
+        <v>8451.397593659429</v>
       </c>
       <c r="E11">
         <v>-794.7587838163198</v>
@@ -2195,37 +2195,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M11">
-        <v>42.61372759735915</v>
+        <v>41.54183330421535</v>
       </c>
       <c r="N11">
-        <v>482.7862724026409</v>
+        <v>483.8581666957847</v>
       </c>
       <c r="O11">
-        <v>96.55725448052819</v>
+        <v>96.77163333915695</v>
       </c>
       <c r="P11">
-        <v>386.2290179221127</v>
+        <v>387.0865333566278</v>
       </c>
       <c r="Q11">
-        <v>698.4290179221127</v>
+        <v>699.2865333566278</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07377517191032003</v>
+        <v>0.07376064670967691</v>
       </c>
       <c r="T11">
         <v>0.5749003254415243</v>
       </c>
       <c r="U11">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.32936027010601</v>
+        <v>12.64749189455455</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07107817791544047</v>
+        <v>0.07095298690328818</v>
       </c>
       <c r="C12">
-        <v>7685.436387695365</v>
+        <v>7707.174662009576</v>
       </c>
       <c r="D12">
-        <v>8444.346144158697</v>
+        <v>8466.084418472909</v>
       </c>
       <c r="E12">
         <v>-709.6878081699865</v>
@@ -2277,37 +2277,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M12">
-        <v>47.34858621928795</v>
+        <v>46.15759256023929</v>
       </c>
       <c r="N12">
-        <v>478.0514137807122</v>
+        <v>479.2424074397608</v>
       </c>
       <c r="O12">
-        <v>95.61028275614244</v>
+        <v>95.84848148795217</v>
       </c>
       <c r="P12">
-        <v>382.4411310245697</v>
+        <v>383.3939259518087</v>
       </c>
       <c r="Q12">
-        <v>694.6411310245696</v>
+        <v>695.5939259518086</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07402839817789478</v>
+        <v>0.07401374149772558</v>
       </c>
       <c r="T12">
         <v>0.580104220670685</v>
       </c>
       <c r="U12">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.09642424309541</v>
+        <v>11.3827427050991</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07101359179268804</v>
+        <v>0.07087722770096873</v>
       </c>
       <c r="C13">
-        <v>7612.86194759573</v>
+        <v>7636.841645517822</v>
       </c>
       <c r="D13">
-        <v>8456.842679705396</v>
+        <v>8480.822377627488</v>
       </c>
       <c r="E13">
         <v>-624.6168325236534</v>
@@ -2359,37 +2359,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M13">
-        <v>52.08344484121674</v>
+        <v>50.77335181626321</v>
       </c>
       <c r="N13">
-        <v>473.3165551587833</v>
+        <v>474.6266481837369</v>
       </c>
       <c r="O13">
-        <v>94.66331103175668</v>
+        <v>94.92532963674739</v>
       </c>
       <c r="P13">
-        <v>378.6532441270267</v>
+        <v>379.7013185469895</v>
       </c>
       <c r="Q13">
-        <v>690.8532441270266</v>
+        <v>691.9013185469895</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07428731492339255</v>
+        <v>0.07427252380910118</v>
       </c>
       <c r="T13">
         <v>0.5854250573656694</v>
       </c>
       <c r="U13">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.08765840281401</v>
+        <v>10.34794791372645</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07094900566993564</v>
+        <v>0.07080146849864928</v>
       </c>
       <c r="C14">
-        <v>7540.324548811562</v>
+        <v>7566.560030880454</v>
       </c>
       <c r="D14">
-        <v>8469.376256567561</v>
+        <v>8495.611738636453</v>
       </c>
       <c r="E14">
         <v>-539.5458568773203</v>
@@ -2441,37 +2441,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M14">
-        <v>56.81830346314553</v>
+        <v>55.38911107228714</v>
       </c>
       <c r="N14">
-        <v>468.5816965368546</v>
+        <v>470.0108889277129</v>
       </c>
       <c r="O14">
-        <v>93.71633930737092</v>
+        <v>94.00217778554259</v>
       </c>
       <c r="P14">
-        <v>374.8653572294837</v>
+        <v>376.0087111421703</v>
       </c>
       <c r="Q14">
-        <v>687.0653572294837</v>
+        <v>688.2087111421704</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07455211614037892</v>
+        <v>0.07453718753664443</v>
       </c>
       <c r="T14">
         <v>0.5908668221673582</v>
       </c>
       <c r="U14">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04452619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.24702020257951</v>
+        <v>9.485618920915915</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07099881954718321</v>
+        <v>0.07072570929632982</v>
       </c>
       <c r="C15">
-        <v>7445.583423729852</v>
+        <v>7496.330087480047</v>
       </c>
       <c r="D15">
-        <v>8459.706107132184</v>
+        <v>8510.452770882379</v>
       </c>
       <c r="E15">
         <v>-454.474881230987</v>
@@ -2523,45 +2523,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M15">
-        <v>62.7696770368169</v>
+        <v>60.00487032831107</v>
       </c>
       <c r="N15">
-        <v>462.6303229631832</v>
+        <v>465.395129671689</v>
       </c>
       <c r="O15">
-        <v>92.52606459263664</v>
+        <v>93.07902593433781</v>
       </c>
       <c r="P15">
-        <v>370.1042583705465</v>
+        <v>372.3161037373512</v>
       </c>
       <c r="Q15">
-        <v>682.3042583705464</v>
+        <v>684.5161037373512</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07482300474166381</v>
+        <v>0.07480793548780934</v>
       </c>
       <c r="T15">
         <v>0.596433685010465</v>
       </c>
       <c r="U15">
-        <v>0.0567577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04540619555335152</v>
+        <v>0.04340619555335153</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>8.370283627424627</v>
+        <v>8.755955926999306</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.0709430334244308</v>
+        <v>0.07081795009401037</v>
       </c>
       <c r="C16">
-        <v>7371.343447677211</v>
+        <v>7393.196230295174</v>
       </c>
       <c r="D16">
-        <v>8470.537106725877</v>
+        <v>8492.38988934384</v>
       </c>
       <c r="E16">
         <v>-369.4039055846538</v>
@@ -2605,37 +2605,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M16">
-        <v>67.59811373195666</v>
+        <v>66.407120072908</v>
       </c>
       <c r="N16">
-        <v>457.8018862680434</v>
+        <v>458.9928799270921</v>
       </c>
       <c r="O16">
-        <v>91.56037725360869</v>
+        <v>91.79857598541842</v>
       </c>
       <c r="P16">
-        <v>366.2415090144347</v>
+        <v>367.1943039416736</v>
       </c>
       <c r="Q16">
-        <v>678.4415090144347</v>
+        <v>679.3943039416736</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07510019307786231</v>
+        <v>0.07508497990295485</v>
       </c>
       <c r="T16">
         <v>0.6021300097801557</v>
       </c>
       <c r="U16">
-        <v>0.0567577444416894</v>
+        <v>0.0557577444416894</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04540619555335152</v>
+        <v>0.04460619555335152</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.772406225465725</v>
+        <v>7.911802219749425</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07088724730167838</v>
+        <v>0.07075419089169094</v>
       </c>
       <c r="C17">
-        <v>7297.131241132516</v>
+        <v>7320.602586635501</v>
       </c>
       <c r="D17">
-        <v>8481.395875827515</v>
+        <v>8504.8672213305</v>
       </c>
       <c r="E17">
         <v>-284.3329299383208</v>
@@ -2687,37 +2687,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M17">
-        <v>72.4265504270964</v>
+        <v>71.15048579240141</v>
       </c>
       <c r="N17">
-        <v>452.9734495729037</v>
+        <v>454.2495142075987</v>
       </c>
       <c r="O17">
-        <v>90.59468991458074</v>
+        <v>90.84990284151974</v>
       </c>
       <c r="P17">
-        <v>362.378759658323</v>
+        <v>363.3996113660789</v>
       </c>
       <c r="Q17">
-        <v>674.578759658323</v>
+        <v>675.599611366079</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07538390349255959</v>
+        <v>0.07536854301022142</v>
       </c>
       <c r="T17">
         <v>0.607960365720898</v>
       </c>
       <c r="U17">
-        <v>0.0567577444416894</v>
+        <v>0.0557577444416894</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.04540619555335152</v>
+        <v>0.04460619555335152</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.254245810434679</v>
+        <v>7.384348738432798</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07083146117892597</v>
+        <v>0.07069043168937147</v>
       </c>
       <c r="C18">
-        <v>7222.946911029852</v>
+        <v>7248.045661235004</v>
       </c>
       <c r="D18">
-        <v>8492.282521371184</v>
+        <v>8517.381271576336</v>
       </c>
       <c r="E18">
         <v>-199.2619542919876</v>
@@ -2769,37 +2769,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M18">
-        <v>77.25498712223617</v>
+        <v>75.89385151189484</v>
       </c>
       <c r="N18">
-        <v>448.1450128777639</v>
+        <v>449.5061484881053</v>
       </c>
       <c r="O18">
-        <v>89.62900257555279</v>
+        <v>89.90122969762106</v>
       </c>
       <c r="P18">
-        <v>358.5160103022112</v>
+        <v>359.6049187904842</v>
       </c>
       <c r="Q18">
-        <v>670.7160103022111</v>
+        <v>671.8049187904842</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07567436891713063</v>
+        <v>0.07565885762004194</v>
       </c>
       <c r="T18">
         <v>0.6139295396602292</v>
       </c>
       <c r="U18">
-        <v>0.0567577444416894</v>
+        <v>0.0557577444416894</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04540619555335152</v>
+        <v>0.04460619555335152</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.800855447282511</v>
+        <v>6.922826942280749</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07107487505617355</v>
+        <v>0.07085787248705203</v>
       </c>
       <c r="C19">
-        <v>7090.577720375808</v>
+        <v>7130.189327658223</v>
       </c>
       <c r="D19">
-        <v>8444.984306363473</v>
+        <v>8484.595913645888</v>
       </c>
       <c r="E19">
         <v>-114.1909786456542</v>
@@ -2851,37 +2851,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M19">
-        <v>85.2650783065488</v>
+        <v>83.09576842756731</v>
       </c>
       <c r="N19">
-        <v>440.1349216934513</v>
+        <v>442.3042315724328</v>
       </c>
       <c r="O19">
-        <v>88.02698433869027</v>
+        <v>88.46084631448656</v>
       </c>
       <c r="P19">
-        <v>352.107937354761</v>
+        <v>353.8433852579462</v>
       </c>
       <c r="Q19">
-        <v>664.307937354761</v>
+        <v>666.0433852579463</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07597183350855879</v>
+        <v>0.07595616776262924</v>
       </c>
       <c r="T19">
         <v>0.6200425491161711</v>
       </c>
       <c r="U19">
-        <v>0.0589577444416894</v>
+        <v>0.0574577444416894</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04716619555335153</v>
+        <v>0.04596619555335152</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.161959977460628</v>
+        <v>6.322824975834712</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07103668893342116</v>
+        <v>0.07080771328473258</v>
       </c>
       <c r="C20">
-        <v>7012.891889602377</v>
+        <v>7054.913148368292</v>
       </c>
       <c r="D20">
-        <v>8452.369451236375</v>
+        <v>8494.39071000229</v>
       </c>
       <c r="E20">
         <v>-29.12000299932129</v>
@@ -2933,37 +2933,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M20">
-        <v>90.28067114811049</v>
+        <v>87.98375480565949</v>
       </c>
       <c r="N20">
-        <v>435.1193288518896</v>
+        <v>437.4162451943406</v>
       </c>
       <c r="O20">
-        <v>87.02386577037792</v>
+        <v>87.48324903886812</v>
       </c>
       <c r="P20">
-        <v>348.0954630815116</v>
+        <v>349.9329961554725</v>
       </c>
       <c r="Q20">
-        <v>660.2954630815116</v>
+        <v>662.1329961554725</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07627655333392423</v>
+        <v>0.0762607293721089</v>
       </c>
       <c r="T20">
         <v>0.6263046563637211</v>
       </c>
       <c r="U20">
-        <v>0.0589577444416894</v>
+        <v>0.0574577444416894</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.04716619555335153</v>
+        <v>0.04596619555335152</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.819628867601704</v>
+        <v>5.971556921621674</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07122650281066874</v>
+        <v>0.07075755408241313</v>
       </c>
       <c r="C21">
-        <v>6891.238085199278</v>
+        <v>6979.659609854078</v>
       </c>
       <c r="D21">
-        <v>8415.786622479609</v>
+        <v>8504.208147134408</v>
       </c>
       <c r="E21">
         <v>55.95097264701189</v>
@@ -3015,45 +3015,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M21">
-        <v>97.72078679559267</v>
+        <v>92.87174118375168</v>
       </c>
       <c r="N21">
-        <v>427.6792132044074</v>
+        <v>432.5282588162484</v>
       </c>
       <c r="O21">
-        <v>85.53584264088148</v>
+        <v>86.50565176324969</v>
       </c>
       <c r="P21">
-        <v>342.1433705635259</v>
+        <v>346.0226070529988</v>
       </c>
       <c r="Q21">
-        <v>654.3433705635259</v>
+        <v>658.2226070529987</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07658879710559499</v>
+        <v>0.07657281102132882</v>
       </c>
       <c r="T21">
         <v>0.6327213835433095</v>
       </c>
       <c r="U21">
-        <v>0.0604577444416894</v>
+        <v>0.0574577444416894</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04836619555335153</v>
+        <v>0.04596619555335152</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>5.376542875151065</v>
+        <v>5.657264452062639</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07120031668791632</v>
+        <v>0.07083539488009367</v>
       </c>
       <c r="C22">
-        <v>6811.195119853574</v>
+        <v>6879.362902030521</v>
       </c>
       <c r="D22">
-        <v>8420.814632780239</v>
+        <v>8488.982414957185</v>
       </c>
       <c r="E22">
         <v>141.0219482933453</v>
@@ -3097,37 +3097,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M22">
-        <v>102.8639861006239</v>
+        <v>99.12086317218522</v>
       </c>
       <c r="N22">
-        <v>422.5360138993762</v>
+        <v>426.2791368278149</v>
       </c>
       <c r="O22">
-        <v>84.50720277987524</v>
+        <v>85.25582736556298</v>
       </c>
       <c r="P22">
-        <v>338.028811119501</v>
+        <v>341.0233094622519</v>
       </c>
       <c r="Q22">
-        <v>650.228811119501</v>
+        <v>653.2233094622518</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.0769088469715575</v>
+        <v>0.0768926947117792</v>
       </c>
       <c r="T22">
         <v>0.6392985289023875</v>
       </c>
       <c r="U22">
-        <v>0.0604577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.04836619555335153</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.107715731393511</v>
+        <v>5.300599522497248</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.0711741305651639</v>
+        <v>0.07079163567777422</v>
       </c>
       <c r="C23">
-        <v>6731.15816606729</v>
+        <v>6802.844550548968</v>
       </c>
       <c r="D23">
-        <v>8425.848654640287</v>
+        <v>8497.535039121965</v>
       </c>
       <c r="E23">
         <v>226.0929239396783</v>
@@ -3179,37 +3179,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M23">
-        <v>108.0071854056551</v>
+        <v>104.0769063307945</v>
       </c>
       <c r="N23">
-        <v>417.3928145943451</v>
+        <v>421.3230936692056</v>
       </c>
       <c r="O23">
-        <v>83.47856291886902</v>
+        <v>84.26461873384113</v>
       </c>
       <c r="P23">
-        <v>333.9142516754761</v>
+        <v>337.0584749353645</v>
       </c>
       <c r="Q23">
-        <v>646.114251675476</v>
+        <v>649.2584749353645</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07723699936577225</v>
+        <v>0.07722067672350684</v>
       </c>
       <c r="T23">
         <v>0.6460421842705562</v>
       </c>
       <c r="U23">
-        <v>0.0604577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.04836619555335153</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.864491172755725</v>
+        <v>5.048190021425952</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.0711479444424115</v>
+        <v>0.07074787647545477</v>
       </c>
       <c r="C24">
-        <v>6651.12723462813</v>
+        <v>6726.343449933681</v>
       </c>
       <c r="D24">
-        <v>8430.888698847461</v>
+        <v>8506.104914153011</v>
       </c>
       <c r="E24">
         <v>311.1638995860114</v>
@@ -3261,37 +3261,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M24">
-        <v>113.1503847106863</v>
+        <v>109.0329494894037</v>
       </c>
       <c r="N24">
-        <v>412.2496152893139</v>
+        <v>416.3670505105964</v>
       </c>
       <c r="O24">
-        <v>82.44992305786278</v>
+        <v>83.27341010211927</v>
       </c>
       <c r="P24">
-        <v>329.7996922314511</v>
+        <v>333.0936404084771</v>
       </c>
       <c r="Q24">
-        <v>641.999692231451</v>
+        <v>645.2936404084771</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07757356592394123</v>
+        <v>0.07755706853040698</v>
       </c>
       <c r="T24">
         <v>0.6529587538789343</v>
       </c>
       <c r="U24">
-        <v>0.0604577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.04836619555335153</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.643377937630465</v>
+        <v>4.818726838633863</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07112175831965908</v>
+        <v>0.07070411727313533</v>
       </c>
       <c r="C25">
-        <v>6571.102336349632</v>
+        <v>6649.859652430523</v>
       </c>
       <c r="D25">
-        <v>8435.934776215296</v>
+        <v>8514.692092296187</v>
       </c>
       <c r="E25">
         <v>396.2348752323446</v>
@@ -3343,37 +3343,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M25">
-        <v>118.2935840157175</v>
+        <v>113.988992648013</v>
       </c>
       <c r="N25">
-        <v>407.1064159842826</v>
+        <v>411.4110073519871</v>
       </c>
       <c r="O25">
-        <v>81.42128319685654</v>
+        <v>82.28220147039742</v>
       </c>
       <c r="P25">
-        <v>325.6851327874261</v>
+        <v>329.1288058815897</v>
       </c>
       <c r="Q25">
-        <v>637.8851327874261</v>
+        <v>641.3288058815897</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07791887447063406</v>
+        <v>0.07790219778683699</v>
       </c>
       <c r="T25">
         <v>0.6600549746459716</v>
       </c>
       <c r="U25">
-        <v>0.0604577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.04836619555335153</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.441491940342184</v>
+        <v>4.609216976084564</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07109557219690665</v>
+        <v>0.07066035807081587</v>
       </c>
       <c r="C26">
-        <v>6491.08348207123</v>
+        <v>6573.39321049655</v>
       </c>
       <c r="D26">
-        <v>8440.986897583227</v>
+        <v>8523.296626008547</v>
       </c>
       <c r="E26">
         <v>481.3058508786778</v>
@@ -3425,37 +3425,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M26">
-        <v>123.4367833207486</v>
+        <v>118.9450358066223</v>
       </c>
       <c r="N26">
-        <v>401.9632166792514</v>
+        <v>406.4549641933778</v>
       </c>
       <c r="O26">
-        <v>80.39264333585029</v>
+        <v>81.29099283867556</v>
       </c>
       <c r="P26">
-        <v>321.5705733434012</v>
+        <v>325.1639713547023</v>
       </c>
       <c r="Q26">
-        <v>633.7705733434011</v>
+        <v>637.3639713547022</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07827327008434512</v>
+        <v>0.0782564093921204</v>
       </c>
       <c r="T26">
         <v>0.6673379380647729</v>
       </c>
       <c r="U26">
-        <v>0.0604577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.04836619555335153</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.25642977616126</v>
+        <v>4.417166268747707</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07134938607415425</v>
+        <v>0.07081659886849642</v>
       </c>
       <c r="C27">
-        <v>6357.297331896722</v>
+        <v>6457.679546003166</v>
       </c>
       <c r="D27">
-        <v>8392.271723055052</v>
+        <v>8492.653937161496</v>
       </c>
       <c r="E27">
         <v>566.376826525011</v>
@@ -3507,37 +3507,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M27">
-        <v>131.5574667734015</v>
+        <v>126.0278533563899</v>
       </c>
       <c r="N27">
-        <v>393.8425332265986</v>
+        <v>399.3721466436102</v>
       </c>
       <c r="O27">
-        <v>78.76850664531972</v>
+        <v>79.87442932872204</v>
       </c>
       <c r="P27">
-        <v>315.0740265812789</v>
+        <v>319.4977173148882</v>
       </c>
       <c r="Q27">
-        <v>627.2740265812788</v>
+        <v>631.6977173148882</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07863711624775516</v>
+        <v>0.07862006664021139</v>
       </c>
       <c r="T27">
         <v>0.674815113841409</v>
       </c>
       <c r="U27">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.993691980288467</v>
+        <v>4.168919695190232</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07133439995140183</v>
+        <v>0.07078083966617699</v>
       </c>
       <c r="C28">
-        <v>6275.087057527939</v>
+        <v>6379.602376182995</v>
       </c>
       <c r="D28">
-        <v>8395.132424332602</v>
+        <v>8499.647742987658</v>
       </c>
       <c r="E28">
         <v>651.4478021713444</v>
@@ -3589,37 +3589,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M28">
-        <v>136.8197654443376</v>
+        <v>131.0689674906455</v>
       </c>
       <c r="N28">
-        <v>388.5802345556625</v>
+        <v>394.3310325093546</v>
       </c>
       <c r="O28">
-        <v>77.71604691113251</v>
+        <v>78.86620650187092</v>
       </c>
       <c r="P28">
-        <v>310.86418764453</v>
+        <v>315.4648260074837</v>
       </c>
       <c r="Q28">
-        <v>623.06418764453</v>
+        <v>627.6648260074837</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07901079609125734</v>
+        <v>0.07899355246257511</v>
       </c>
       <c r="T28">
         <v>0.6824943754498461</v>
       </c>
       <c r="U28">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.840088442585064</v>
+        <v>4.008576629990607</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07131941382864943</v>
+        <v>0.07074508046385752</v>
       </c>
       <c r="C29">
-        <v>6192.87873409749</v>
+        <v>6301.536734828303</v>
       </c>
       <c r="D29">
-        <v>8397.995076548486</v>
+        <v>8506.653077279299</v>
       </c>
       <c r="E29">
         <v>736.5187778176773</v>
@@ -3671,37 +3671,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M29">
-        <v>142.0820641152736</v>
+        <v>136.110081624901</v>
       </c>
       <c r="N29">
-        <v>383.3179358847265</v>
+        <v>389.2899183750991</v>
       </c>
       <c r="O29">
-        <v>76.6635871769453</v>
+        <v>77.85798367501982</v>
       </c>
       <c r="P29">
-        <v>306.6543487077812</v>
+        <v>311.4319347000793</v>
       </c>
       <c r="Q29">
-        <v>618.8543487077811</v>
+        <v>623.6319347000792</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07939471373869111</v>
+        <v>0.07937727077322276</v>
       </c>
       <c r="T29">
         <v>0.6903840277872816</v>
       </c>
       <c r="U29">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.697862944711544</v>
+        <v>3.860110828879845</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.071304427705897</v>
+        <v>0.07070932126153807</v>
       </c>
       <c r="C30">
-        <v>6110.672363601815</v>
+        <v>6223.482650467576</v>
       </c>
       <c r="D30">
-        <v>8400.859681699145</v>
+        <v>8513.669968564906</v>
       </c>
       <c r="E30">
         <v>821.5897534640108</v>
@@ -3753,37 +3753,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M30">
-        <v>147.3443627862097</v>
+        <v>141.1511957591566</v>
       </c>
       <c r="N30">
-        <v>378.0556372137904</v>
+        <v>384.2488042408435</v>
       </c>
       <c r="O30">
-        <v>75.61112744275809</v>
+        <v>76.8497608481687</v>
       </c>
       <c r="P30">
-        <v>302.4445097710324</v>
+        <v>307.3990433926748</v>
       </c>
       <c r="Q30">
-        <v>614.6445097710323</v>
+        <v>619.5990433926747</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07978929576522024</v>
+        <v>0.07977164792583284</v>
       </c>
       <c r="T30">
         <v>0.69849283713409</v>
       </c>
       <c r="U30">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.565796410971846</v>
+        <v>3.722249727848422</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.0712894415831446</v>
+        <v>0.07067356205921863</v>
       </c>
       <c r="C31">
-        <v>6028.467948040056</v>
+        <v>6145.44015172351</v>
       </c>
       <c r="D31">
-        <v>8403.726241783719</v>
+        <v>8520.698445467173</v>
       </c>
       <c r="E31">
         <v>906.6607291103437</v>
@@ -3835,37 +3835,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M31">
-        <v>152.6066614571457</v>
+        <v>146.1923098934122</v>
       </c>
       <c r="N31">
-        <v>372.7933385428544</v>
+        <v>379.2076901065878</v>
       </c>
       <c r="O31">
-        <v>74.55866770857088</v>
+        <v>75.84153802131758</v>
       </c>
       <c r="P31">
-        <v>298.2346708342835</v>
+        <v>303.3661520852703</v>
       </c>
       <c r="Q31">
-        <v>610.4346708342835</v>
+        <v>615.5661520852702</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08019499277841219</v>
+        <v>0.08017713429400941</v>
       </c>
       <c r="T31">
         <v>0.7068300636455975</v>
       </c>
       <c r="U31">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.442837914041782</v>
+        <v>3.593896288957097</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07127445546039218</v>
+        <v>0.07063780285689916</v>
       </c>
       <c r="C32">
-        <v>5946.265489414106</v>
+        <v>6067.409267313406</v>
       </c>
       <c r="D32">
-        <v>8406.594758804102</v>
+        <v>8527.738536703402</v>
       </c>
       <c r="E32">
         <v>991.7317047566767</v>
@@ -3917,37 +3917,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M32">
-        <v>157.8689601280818</v>
+        <v>151.2334240276678</v>
       </c>
       <c r="N32">
-        <v>367.5310398719183</v>
+        <v>374.1665759723323</v>
       </c>
       <c r="O32">
-        <v>73.50620797438367</v>
+        <v>74.83331519446646</v>
       </c>
       <c r="P32">
-        <v>294.0248318975347</v>
+        <v>299.3332607778658</v>
       </c>
       <c r="Q32">
-        <v>606.2248318975346</v>
+        <v>611.5332607778657</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08061228113483818</v>
+        <v>0.08059420598699102</v>
       </c>
       <c r="T32">
         <v>0.7154054966288623</v>
       </c>
       <c r="U32">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.32807665024039</v>
+        <v>3.474099745991861</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07125946933763976</v>
+        <v>0.07060204365457973</v>
       </c>
       <c r="C33">
-        <v>5864.064989728582</v>
+        <v>5989.39002604953</v>
       </c>
       <c r="D33">
-        <v>8409.465234764912</v>
+        <v>8534.79027108586</v>
       </c>
       <c r="E33">
         <v>1076.80268040301</v>
@@ -3999,37 +3999,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M33">
-        <v>163.1312587990179</v>
+        <v>156.2745381619234</v>
       </c>
       <c r="N33">
-        <v>362.2687412009822</v>
+        <v>369.1254618380767</v>
       </c>
       <c r="O33">
-        <v>72.45374824019645</v>
+        <v>73.82509236761534</v>
       </c>
       <c r="P33">
-        <v>289.8149929607858</v>
+        <v>295.3003694704614</v>
       </c>
       <c r="Q33">
-        <v>602.0149929607858</v>
+        <v>607.5003694704614</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08104166480594317</v>
+        <v>0.08102336671455182</v>
       </c>
       <c r="T33">
         <v>0.7242294928870042</v>
       </c>
       <c r="U33">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.220719338942312</v>
+        <v>3.362032012250188</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07124448321488734</v>
+        <v>0.07056628445226028</v>
       </c>
       <c r="C34">
-        <v>5781.866450990836</v>
+        <v>5911.382456839558</v>
       </c>
       <c r="D34">
-        <v>8412.337671673498</v>
+        <v>8541.85367752222</v>
       </c>
       <c r="E34">
         <v>1161.873656049343</v>
@@ -4081,37 +4081,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M34">
-        <v>168.3935574699539</v>
+        <v>161.315652296179</v>
       </c>
       <c r="N34">
-        <v>357.0064425300462</v>
+        <v>364.0843477038211</v>
       </c>
       <c r="O34">
-        <v>71.40128850600924</v>
+        <v>72.81686954076422</v>
       </c>
       <c r="P34">
-        <v>285.6051540240369</v>
+        <v>291.2674781630569</v>
       </c>
       <c r="Q34">
-        <v>597.8051540240369</v>
+        <v>603.4674781630569</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08148367740855127</v>
+        <v>0.08146514981645263</v>
       </c>
       <c r="T34">
         <v>0.7333130184468563</v>
       </c>
       <c r="U34">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.120071859600365</v>
+        <v>3.256968511867369</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.07122949709213494</v>
+        <v>0.07053052524994083</v>
       </c>
       <c r="C35">
-        <v>5699.66987521097</v>
+        <v>5833.386588686919</v>
       </c>
       <c r="D35">
-        <v>8415.212071539965</v>
+        <v>8548.928785015914</v>
       </c>
       <c r="E35">
         <v>1246.944631695676</v>
@@ -4163,37 +4163,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M35">
-        <v>173.65585614089</v>
+        <v>166.3567664304346</v>
       </c>
       <c r="N35">
-        <v>351.7441438591101</v>
+        <v>359.0432335695655</v>
       </c>
       <c r="O35">
-        <v>70.34882877182201</v>
+        <v>71.80864671391309</v>
       </c>
       <c r="P35">
-        <v>281.3953150872881</v>
+        <v>287.2345868556524</v>
       </c>
       <c r="Q35">
-        <v>593.5953150872881</v>
+        <v>599.4345868556524</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08193888441720737</v>
+        <v>0.08192012047363406</v>
       </c>
       <c r="T35">
         <v>0.7426676940234204</v>
       </c>
       <c r="U35">
-        <v>0.0618577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.04948619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.025524227491263</v>
+        <v>3.158272496356236</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07192171096938252</v>
+        <v>0.07049476604762137</v>
       </c>
       <c r="C36">
-        <v>5483.847678602893</v>
+        <v>5755.402450691223</v>
       </c>
       <c r="D36">
-        <v>8284.460850578222</v>
+        <v>8556.015622666551</v>
       </c>
       <c r="E36">
         <v>1332.01560734201</v>
@@ -4245,45 +4245,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M36">
-        <v>186.4384290589619</v>
+        <v>171.3978805646902</v>
       </c>
       <c r="N36">
-        <v>338.9615709410382</v>
+        <v>354.0021194353099</v>
       </c>
       <c r="O36">
-        <v>67.79231418820764</v>
+        <v>70.80042388706197</v>
       </c>
       <c r="P36">
-        <v>271.1692567528306</v>
+        <v>283.2016955482479</v>
       </c>
       <c r="Q36">
-        <v>583.3692567528306</v>
+        <v>595.4016955482479</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08240788557764092</v>
+        <v>0.08238887812042706</v>
       </c>
       <c r="T36">
         <v>0.7523058446174561</v>
       </c>
       <c r="U36">
-        <v>0.06445774444168939</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.05156619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.818088538140601</v>
+        <v>3.065382128816347</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07192752484663009</v>
+        <v>0.07115900684530192</v>
       </c>
       <c r="C37">
-        <v>5397.695732503917</v>
+        <v>5540.579625101802</v>
       </c>
       <c r="D37">
-        <v>8283.379880125578</v>
+        <v>8426.263772723463</v>
       </c>
       <c r="E37">
         <v>1417.086582988343</v>
@@ -4327,37 +4327,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M37">
-        <v>191.9219122665784</v>
+        <v>183.8827050679999</v>
       </c>
       <c r="N37">
-        <v>333.4780877334217</v>
+        <v>341.5172949320001</v>
       </c>
       <c r="O37">
-        <v>66.69561754668435</v>
+        <v>68.30345898640003</v>
       </c>
       <c r="P37">
-        <v>266.7824701867374</v>
+        <v>273.2138359456001</v>
       </c>
       <c r="Q37">
-        <v>578.9824701867374</v>
+        <v>585.4138359456001</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08289131754301088</v>
+        <v>0.08287205907942907</v>
       </c>
       <c r="T37">
         <v>0.7622405536913083</v>
       </c>
       <c r="U37">
-        <v>0.06445774444168939</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.05156619555335151</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.737571722765156</v>
+        <v>2.857256204740445</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07193333872387769</v>
+        <v>0.07114324764298248</v>
       </c>
       <c r="C38">
-        <v>5311.544068461832</v>
+        <v>5458.541437139658</v>
       </c>
       <c r="D38">
-        <v>8282.299191729826</v>
+        <v>8429.296560407653</v>
       </c>
       <c r="E38">
         <v>1502.157558634676</v>
@@ -4409,37 +4409,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M38">
-        <v>197.4053954741949</v>
+        <v>189.1364966413713</v>
       </c>
       <c r="N38">
-        <v>327.9946045258052</v>
+        <v>336.2635033586288</v>
       </c>
       <c r="O38">
-        <v>65.59892090516104</v>
+        <v>67.25270067172576</v>
       </c>
       <c r="P38">
-        <v>262.3956836206441</v>
+        <v>269.010802686903</v>
       </c>
       <c r="Q38">
-        <v>574.5956836206442</v>
+        <v>581.210802686903</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08338985675729867</v>
+        <v>0.08337033944339989</v>
       </c>
       <c r="T38">
         <v>0.7724857224237183</v>
       </c>
       <c r="U38">
-        <v>0.06445774444168939</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.05156619555335151</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.661528063799457</v>
+        <v>2.777887976830989</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07193915260112528</v>
+        <v>0.07112748844066302</v>
       </c>
       <c r="C39">
-        <v>5225.39268636627</v>
+        <v>5376.505433090354</v>
       </c>
       <c r="D39">
-        <v>8281.218785280598</v>
+        <v>8432.331532004682</v>
       </c>
       <c r="E39">
         <v>1587.228534281009</v>
@@ -4491,37 +4491,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M39">
-        <v>202.8888786818115</v>
+        <v>194.3902882147428</v>
       </c>
       <c r="N39">
-        <v>322.5111213181887</v>
+        <v>331.0097117852573</v>
       </c>
       <c r="O39">
-        <v>64.50222426363773</v>
+        <v>66.20194235705146</v>
       </c>
       <c r="P39">
-        <v>258.0088970545509</v>
+        <v>264.8077694282059</v>
       </c>
       <c r="Q39">
-        <v>570.2088970545509</v>
+        <v>577.0077694282058</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08390422261330988</v>
+        <v>0.08388443823162375</v>
       </c>
       <c r="T39">
         <v>0.783056134607951</v>
       </c>
       <c r="U39">
-        <v>0.06445774444168939</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V39">
         <v>0.2</v>
       </c>
       <c r="W39">
-        <v>0.05156619555335151</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.589594872885958</v>
+        <v>2.702809923403124</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.07194496647837287</v>
+        <v>0.07111172923834358</v>
       </c>
       <c r="C40">
-        <v>5139.241586106903</v>
+        <v>5294.47161531369</v>
       </c>
       <c r="D40">
-        <v>8280.138660667564</v>
+        <v>8435.368689874351</v>
       </c>
       <c r="E40">
         <v>1672.299509927342</v>
@@ -4573,37 +4573,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M40">
-        <v>208.372361889428</v>
+        <v>199.6440797881142</v>
       </c>
       <c r="N40">
-        <v>317.0276381105721</v>
+        <v>325.7559202118859</v>
       </c>
       <c r="O40">
-        <v>63.40552762211443</v>
+        <v>65.15118404237718</v>
       </c>
       <c r="P40">
-        <v>253.6221104884577</v>
+        <v>260.6047361695087</v>
       </c>
       <c r="Q40">
-        <v>565.8221104884577</v>
+        <v>572.8047361695087</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08443518091628917</v>
+        <v>0.0844151208517258</v>
       </c>
       <c r="T40">
         <v>0.7939675278303845</v>
       </c>
       <c r="U40">
-        <v>0.06445774444168939</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V40">
         <v>0.2</v>
       </c>
       <c r="W40">
-        <v>0.05156619555335151</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.521447639388959</v>
+        <v>2.631683346471463</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07279318035562045</v>
+        <v>0.07109597003602412</v>
       </c>
       <c r="C41">
-        <v>4899.549023394262</v>
+        <v>5212.439986172878</v>
       </c>
       <c r="D41">
-        <v>8125.517073601256</v>
+        <v>8438.408036379873</v>
       </c>
       <c r="E41">
         <v>1757.370485573676</v>
@@ -4655,45 +4655,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M41">
-        <v>222.8138188326034</v>
+        <v>204.8978713614856</v>
       </c>
       <c r="N41">
-        <v>302.5861811673967</v>
+        <v>320.5021286385145</v>
       </c>
       <c r="O41">
-        <v>60.51723623347934</v>
+        <v>64.1004257277029</v>
       </c>
       <c r="P41">
-        <v>242.0689449339174</v>
+        <v>256.4017029108116</v>
       </c>
       <c r="Q41">
-        <v>554.2689449339174</v>
+        <v>568.6017029108116</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08498354768821861</v>
+        <v>0.08496320290199513</v>
       </c>
       <c r="T41">
         <v>0.805236671650275</v>
       </c>
       <c r="U41">
-        <v>0.0671577444416894</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.05372619555335152</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.358022508445605</v>
+        <v>2.564204286305528</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07282059423286803</v>
+        <v>0.07108021083370467</v>
       </c>
       <c r="C42">
-        <v>4809.577026508627</v>
+        <v>5130.410548034528</v>
       </c>
       <c r="D42">
-        <v>8120.616052361954</v>
+        <v>8441.449573887856</v>
       </c>
       <c r="E42">
         <v>1842.441461220009</v>
@@ -4737,45 +4737,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M42">
-        <v>228.526993674465</v>
+        <v>210.1516629348571</v>
       </c>
       <c r="N42">
-        <v>296.873006325535</v>
+        <v>315.248337065143</v>
       </c>
       <c r="O42">
-        <v>59.374601265107</v>
+        <v>63.0496674130286</v>
       </c>
       <c r="P42">
-        <v>237.498405060428</v>
+        <v>252.1986696521144</v>
       </c>
       <c r="Q42">
-        <v>549.6984050604281</v>
+        <v>564.3986696521144</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08555019335254571</v>
+        <v>0.08552955435394011</v>
       </c>
       <c r="T42">
         <v>0.8168814535974952</v>
       </c>
       <c r="U42">
-        <v>0.0671577444416894</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.05372619555335152</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.299071945734465</v>
+        <v>2.500099179147889</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.07438960811011563</v>
+        <v>0.07221245163138523</v>
       </c>
       <c r="C43">
-        <v>4453.523529079019</v>
+        <v>4832.255591002307</v>
       </c>
       <c r="D43">
-        <v>7849.633530578679</v>
+        <v>8228.365592501968</v>
       </c>
       <c r="E43">
         <v>1927.512436866342</v>
@@ -4819,45 +4819,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M43">
-        <v>250.6333455233751</v>
+        <v>227.6131395134773</v>
       </c>
       <c r="N43">
-        <v>274.766654476625</v>
+        <v>297.7868604865228</v>
       </c>
       <c r="O43">
-        <v>54.953330895325</v>
+        <v>59.55737209730455</v>
       </c>
       <c r="P43">
-        <v>219.8133235813</v>
+        <v>238.2294883892182</v>
       </c>
       <c r="Q43">
-        <v>532.0133235813</v>
+        <v>550.4294883892182</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08613604734447712</v>
+        <v>0.0861151041601883</v>
       </c>
       <c r="T43">
         <v>0.8289209739158077</v>
       </c>
       <c r="U43">
-        <v>0.07185774444168941</v>
+        <v>0.0652577444416894</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.05748619555335153</v>
+        <v>0.05220619555335152</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.09628929822907</v>
+        <v>2.308302592385667</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.07445462198736322</v>
+        <v>0.07222469242906576</v>
       </c>
       <c r="C44">
-        <v>4357.613761550218</v>
+        <v>4744.939701043006</v>
       </c>
       <c r="D44">
-        <v>7838.794738696211</v>
+        <v>8226.120678189</v>
       </c>
       <c r="E44">
         <v>2012.583412512675</v>
@@ -4901,45 +4901,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M44">
-        <v>256.7463539507745</v>
+        <v>233.1646795016109</v>
       </c>
       <c r="N44">
-        <v>268.6536460492256</v>
+        <v>292.2353204983892</v>
       </c>
       <c r="O44">
-        <v>53.73072920984512</v>
+        <v>58.44706409967785</v>
       </c>
       <c r="P44">
-        <v>214.9229168393805</v>
+        <v>233.7882563987114</v>
       </c>
       <c r="Q44">
-        <v>527.1229168393804</v>
+        <v>545.9882563987114</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08674210319819925</v>
+        <v>0.08672084533906574</v>
       </c>
       <c r="T44">
         <v>0.8413756501071651</v>
       </c>
       <c r="U44">
-        <v>0.07185774444168941</v>
+        <v>0.0652577444416894</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.05748619555335153</v>
+        <v>0.05220619555335152</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.046377648271235</v>
+        <v>2.253343006852675</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.0777188358646108</v>
+        <v>0.07320013322674632</v>
       </c>
       <c r="C45">
-        <v>3764.333390408079</v>
+        <v>4484.830989830723</v>
       </c>
       <c r="D45">
-        <v>7330.585343200405</v>
+        <v>8051.08294262305</v>
       </c>
       <c r="E45">
         <v>2097.654388159008</v>
@@ -4983,45 +4983,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M45">
-        <v>296.8792455391425</v>
+        <v>248.958764957563</v>
       </c>
       <c r="N45">
-        <v>228.5207544608576</v>
+        <v>276.4412350424371</v>
       </c>
       <c r="O45">
-        <v>45.70415089217153</v>
+        <v>55.28824700848742</v>
       </c>
       <c r="P45">
-        <v>182.8166035686861</v>
+        <v>221.1529880339497</v>
       </c>
       <c r="Q45">
-        <v>495.0166035686861</v>
+        <v>533.3529880339497</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08736942416959587</v>
+        <v>0.08734784059439503</v>
       </c>
       <c r="T45">
         <v>0.8542673324806758</v>
       </c>
       <c r="U45">
-        <v>0.0811577444416894</v>
+        <v>0.0680577444416894</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.06492619555335152</v>
+        <v>0.05444619555335152</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>1.769743112375055</v>
+        <v>2.110389646612999</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.0795126497418584</v>
+        <v>0.07323477402442688</v>
       </c>
       <c r="C46">
-        <v>3427.072906171961</v>
+        <v>4393.680766669393</v>
       </c>
       <c r="D46">
-        <v>7078.39583461062</v>
+        <v>8045.003695108052</v>
       </c>
       <c r="E46">
         <v>2182.725363805341</v>
@@ -5065,45 +5065,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M46">
-        <v>321.3760918037144</v>
+        <v>254.7485036775063</v>
       </c>
       <c r="N46">
-        <v>204.0239081962857</v>
+        <v>270.6514963224938</v>
       </c>
       <c r="O46">
-        <v>40.80478163925714</v>
+        <v>54.13029926449877</v>
       </c>
       <c r="P46">
-        <v>163.2191265570285</v>
+        <v>216.521197057995</v>
       </c>
       <c r="Q46">
-        <v>475.4191265570286</v>
+        <v>528.721197057995</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.08801914946139949</v>
+        <v>0.08799722853741465</v>
       </c>
       <c r="T46">
         <v>0.8676194320818117</v>
       </c>
       <c r="U46">
-        <v>0.08585774444168939</v>
+        <v>0.0680577444416894</v>
       </c>
       <c r="V46">
         <v>0.2</v>
       </c>
       <c r="W46">
-        <v>0.06868619555335152</v>
+        <v>0.05444619555335152</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.634844698780196</v>
+        <v>2.062426245553613</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07968966361910597</v>
+        <v>0.07326941482210743</v>
       </c>
       <c r="C47">
-        <v>3318.053267012909</v>
+        <v>4302.539717271598</v>
       </c>
       <c r="D47">
-        <v>7054.447171097901</v>
+        <v>8038.933621356591</v>
       </c>
       <c r="E47">
         <v>2267.796339451675</v>
@@ -5147,45 +5147,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M47">
-        <v>328.6800938901625</v>
+        <v>260.5382423974497</v>
       </c>
       <c r="N47">
-        <v>196.7199061098376</v>
+        <v>264.8617576025504</v>
       </c>
       <c r="O47">
-        <v>39.34398122196751</v>
+        <v>52.97235152051009</v>
       </c>
       <c r="P47">
-        <v>157.37592488787</v>
+        <v>211.8894060820404</v>
       </c>
       <c r="Q47">
-        <v>469.57592488787</v>
+        <v>524.0894060820403</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.0886925011274505</v>
+        <v>0.08867023058745316</v>
       </c>
       <c r="T47">
         <v>0.8814570625775343</v>
       </c>
       <c r="U47">
-        <v>0.08585774444168939</v>
+        <v>0.0680577444416894</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.06868619555335152</v>
+        <v>0.05444619555335152</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.59851481658508</v>
+        <v>2.016594551207977</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.07986667749635357</v>
+        <v>0.07617445561978797</v>
       </c>
       <c r="C48">
-        <v>3209.195134658879</v>
+        <v>3739.075631231319</v>
       </c>
       <c r="D48">
-        <v>7030.660014390205</v>
+        <v>7560.540510962644</v>
       </c>
       <c r="E48">
         <v>2352.867315098008</v>
@@ -5229,45 +5229,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M48">
-        <v>335.9840959766105</v>
+        <v>296.8514471792973</v>
       </c>
       <c r="N48">
-        <v>189.4159040233895</v>
+        <v>228.5485528207028</v>
       </c>
       <c r="O48">
-        <v>37.88318080467791</v>
+        <v>45.70971056414055</v>
       </c>
       <c r="P48">
-        <v>151.5327232187116</v>
+        <v>182.8388422565622</v>
       </c>
       <c r="Q48">
-        <v>463.7327232187116</v>
+        <v>495.0388422565622</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08939079174409603</v>
+        <v>0.08936815863934494</v>
       </c>
       <c r="T48">
         <v>0.8958071979064319</v>
       </c>
       <c r="U48">
-        <v>0.08585774444168939</v>
+        <v>0.0758577444416894</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.06868619555335152</v>
+        <v>0.06068619555335152</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.563764494485405</v>
+        <v>1.769908838216511</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08004369137360115</v>
+        <v>0.07773789641746853</v>
       </c>
       <c r="C49">
-        <v>3100.496880827669</v>
+        <v>3419.377928820603</v>
       </c>
       <c r="D49">
-        <v>7007.032736205328</v>
+        <v>7325.913784198262</v>
       </c>
       <c r="E49">
         <v>2437.938290744341</v>
@@ -5311,37 +5311,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M49">
-        <v>343.2880980630586</v>
+        <v>318.898249345255</v>
       </c>
       <c r="N49">
-        <v>182.1119019369415</v>
+        <v>206.5017506547451</v>
       </c>
       <c r="O49">
-        <v>36.42238038738829</v>
+        <v>41.30035013094903</v>
       </c>
       <c r="P49">
-        <v>145.6895215495532</v>
+        <v>165.2014005237961</v>
       </c>
       <c r="Q49">
-        <v>457.8895215495531</v>
+        <v>477.4014005237961</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09011543295004892</v>
+        <v>0.0900924235988553</v>
       </c>
       <c r="T49">
         <v>0.9106988477760427</v>
       </c>
       <c r="U49">
-        <v>0.08585774444168939</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.06868619555335152</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.530492909496354</v>
+        <v>1.647547457782298</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08647990525084873</v>
+        <v>0.07786613721514908</v>
       </c>
       <c r="C50">
-        <v>2252.455049909165</v>
+        <v>3315.706345700909</v>
       </c>
       <c r="D50">
-        <v>6244.061880933157</v>
+        <v>7307.313176724901</v>
       </c>
       <c r="E50">
         <v>2523.009266390674</v>
@@ -5393,45 +5393,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M50">
-        <v>417.1516314951978</v>
+        <v>325.6833184802604</v>
       </c>
       <c r="N50">
-        <v>108.2483685048023</v>
+        <v>199.7166815197397</v>
       </c>
       <c r="O50">
-        <v>21.64967370096047</v>
+        <v>39.94333630394794</v>
       </c>
       <c r="P50">
-        <v>86.59869480384187</v>
+        <v>159.7733452157918</v>
       </c>
       <c r="Q50">
-        <v>398.7986948038418</v>
+        <v>471.9733452157918</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09086794497161538</v>
+        <v>0.0908445449029622</v>
       </c>
       <c r="T50">
         <v>0.9261632534098692</v>
       </c>
       <c r="U50">
-        <v>0.1021577444416894</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V50">
         <v>0.2</v>
       </c>
       <c r="W50">
-        <v>0.08172619555335153</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.25949405523552</v>
+        <v>1.613223552411833</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1006358319106945</v>
+        <v>0.07799437801282963</v>
       </c>
       <c r="C51">
-        <v>960.9407631049453</v>
+        <v>3212.128977822667</v>
       </c>
       <c r="D51">
-        <v>5037.618569775271</v>
+        <v>7288.806784492993</v>
       </c>
       <c r="E51">
         <v>2608.080242037007</v>
@@ -5475,45 +5475,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M51">
-        <v>562.1515147628007</v>
+        <v>332.4683876152658</v>
       </c>
       <c r="N51">
-        <v>-36.75151476280064</v>
+        <v>192.9316123847343</v>
       </c>
       <c r="O51">
-        <v>-7.350302952560128</v>
+        <v>38.58632247694686</v>
       </c>
       <c r="P51">
-        <v>-29.40121181024051</v>
+        <v>154.3452899077874</v>
       </c>
       <c r="Q51">
-        <v>282.7987881897595</v>
+        <v>466.5452899077874</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09197563927263155</v>
+        <v>0.09162616116017133</v>
       </c>
       <c r="T51">
-        <v>0.9489267887398879</v>
+        <v>0.9422341063234535</v>
       </c>
       <c r="U51">
-        <v>0.1348577444416894</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V51">
-        <v>0.1869246942158262</v>
+        <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.1096495017992906</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.9346234710791308</v>
+        <v>1.580300622770775</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1015264093551114</v>
+        <v>0.07812261881051016</v>
       </c>
       <c r="C52">
-        <v>815.3703763142084</v>
+        <v>3108.645111169845</v>
       </c>
       <c r="D52">
-        <v>4977.119158630867</v>
+        <v>7270.393893486504</v>
       </c>
       <c r="E52">
         <v>2693.15121768334</v>
@@ -5557,45 +5557,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M52">
-        <v>573.6239946559191</v>
+        <v>339.2534567502712</v>
       </c>
       <c r="N52">
-        <v>-48.223994655919</v>
+        <v>186.1465432497289</v>
       </c>
       <c r="O52">
-        <v>-9.6447989311838</v>
+        <v>37.22930864994578</v>
       </c>
       <c r="P52">
-        <v>-38.5791957247352</v>
+        <v>148.9172345997831</v>
       </c>
       <c r="Q52">
-        <v>273.6208042752648</v>
+        <v>461.1172345997831</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09289915205808418</v>
+        <v>0.09243904206766881</v>
       </c>
       <c r="T52">
-        <v>0.9679053245146857</v>
+        <v>0.9589477933535814</v>
       </c>
       <c r="U52">
-        <v>0.1348577444416894</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V52">
-        <v>0.1831862003315097</v>
+        <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.1101536666521386</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.9159310016575483</v>
+        <v>1.54869461031536</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1024169867995283</v>
+        <v>0.07825085960819073</v>
       </c>
       <c r="C53">
-        <v>671.2358836171416</v>
+        <v>3005.254038923174</v>
       </c>
       <c r="D53">
-        <v>4918.055641580133</v>
+        <v>7252.073796886165</v>
       </c>
       <c r="E53">
         <v>2778.222193329673</v>
@@ -5639,45 +5639,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M53">
-        <v>585.0964745490375</v>
+        <v>346.0385258852766</v>
       </c>
       <c r="N53">
-        <v>-59.69647454903736</v>
+        <v>179.3614741147235</v>
       </c>
       <c r="O53">
-        <v>-11.93929490980747</v>
+        <v>35.8722948229447</v>
       </c>
       <c r="P53">
-        <v>-47.75717963922989</v>
+        <v>143.4891792917788</v>
       </c>
       <c r="Q53">
-        <v>264.4428203607701</v>
+        <v>455.6891792917788</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09386035924294304</v>
+        <v>0.09328510178771723</v>
       </c>
       <c r="T53">
-        <v>0.9876584944027407</v>
+        <v>0.9763436716910614</v>
       </c>
       <c r="U53">
-        <v>0.1348577444416894</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V53">
-        <v>0.1795943140504997</v>
+        <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.1106380603342866</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.8979715702524983</v>
+        <v>1.518328049328785</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1033075642439452</v>
+        <v>0.08428630040587128</v>
       </c>
       <c r="C54">
-        <v>528.4867652287739</v>
+        <v>2151.329902743016</v>
       </c>
       <c r="D54">
-        <v>4860.377498838099</v>
+        <v>6483.220636352341</v>
       </c>
       <c r="E54">
         <v>2863.293168976007</v>
@@ -5721,45 +5721,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M54">
-        <v>596.5689544421559</v>
+        <v>415.6400034375345</v>
       </c>
       <c r="N54">
-        <v>-71.16895444215584</v>
+        <v>109.7599965624656</v>
       </c>
       <c r="O54">
-        <v>-14.23379088843117</v>
+        <v>21.95199931249311</v>
       </c>
       <c r="P54">
-        <v>-56.93516355372467</v>
+        <v>87.80799724997246</v>
       </c>
       <c r="Q54">
-        <v>255.2648364462753</v>
+        <v>400.0079972499724</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09486161672717103</v>
+        <v>0.094166413996101</v>
       </c>
       <c r="T54">
-        <v>1.008234713036131</v>
+        <v>0.9944643782926028</v>
       </c>
       <c r="U54">
-        <v>0.1348577444416894</v>
+        <v>0.0939577444416894</v>
       </c>
       <c r="V54">
-        <v>0.1761405772418362</v>
+        <v>0.2</v>
       </c>
       <c r="W54">
-        <v>0.1111038234901982</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.8807028862091809</v>
+        <v>1.264074669557068</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1041981416883621</v>
+        <v>0.0974287349181065</v>
       </c>
       <c r="C55">
-        <v>387.0748438426463</v>
+        <v>850.268134639281</v>
       </c>
       <c r="D55">
-        <v>4804.036553098304</v>
+        <v>5267.229843894939</v>
       </c>
       <c r="E55">
         <v>2948.36414462234</v>
@@ -5803,37 +5803,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M55">
-        <v>608.0414343352743</v>
+        <v>552.5836653114296</v>
       </c>
       <c r="N55">
-        <v>-82.6414343352742</v>
+        <v>-27.18366531142954</v>
       </c>
       <c r="O55">
-        <v>-16.52828686705484</v>
+        <v>-5.436733062285907</v>
       </c>
       <c r="P55">
-        <v>-66.11314746821935</v>
+        <v>-21.74693224914363</v>
       </c>
       <c r="Q55">
-        <v>246.0868525317806</v>
+        <v>290.4530677508563</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09590548091285553</v>
+        <v>0.09537270055060963</v>
       </c>
       <c r="T55">
-        <v>1.029686515441155</v>
+        <v>1.019266899491897</v>
       </c>
       <c r="U55">
-        <v>0.1348577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V55">
-        <v>0.1728171701240657</v>
+        <v>0.1901612490495501</v>
       </c>
       <c r="W55">
-        <v>0.1115520106779622</v>
+        <v>0.09925201067796219</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8640858506203285</v>
+        <v>0.9508062452477506</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.105088719132779</v>
+        <v>0.09819631236252338</v>
       </c>
       <c r="C56">
-        <v>246.9541504178669</v>
+        <v>708.1233838260941</v>
       </c>
       <c r="D56">
-        <v>4748.986835319858</v>
+        <v>5210.156068728085</v>
       </c>
       <c r="E56">
         <v>3033.435120268673</v>
@@ -5885,37 +5885,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M56">
-        <v>619.5139142283927</v>
+        <v>563.0097722040981</v>
       </c>
       <c r="N56">
-        <v>-94.11391422839256</v>
+        <v>-37.60977220409802</v>
       </c>
       <c r="O56">
-        <v>-18.82278284567851</v>
+        <v>-7.521954440819605</v>
       </c>
       <c r="P56">
-        <v>-75.29113138271404</v>
+        <v>-30.08781776327842</v>
       </c>
       <c r="Q56">
-        <v>236.9088686172859</v>
+        <v>282.1121822367216</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09699473049791758</v>
+        <v>0.09645036795388376</v>
       </c>
       <c r="T56">
-        <v>1.052071004907267</v>
+        <v>1.041424875567808</v>
       </c>
       <c r="U56">
-        <v>0.1348577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V56">
-        <v>0.1696168521588052</v>
+        <v>0.1866397444375214</v>
       </c>
       <c r="W56">
-        <v>0.1119835983402534</v>
+        <v>0.09968359834025343</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8480842607940261</v>
+        <v>0.933198722187607</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1059792965771958</v>
+        <v>0.09896388980694026</v>
       </c>
       <c r="C57">
-        <v>108.0807990893345</v>
+        <v>567.2022355888876</v>
       </c>
       <c r="D57">
-        <v>4695.18445963766</v>
+        <v>5154.305896137213</v>
       </c>
       <c r="E57">
         <v>3118.506095915007</v>
@@ -5967,37 +5967,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M57">
-        <v>630.9863941215111</v>
+        <v>573.4358790967667</v>
       </c>
       <c r="N57">
-        <v>-105.586394121511</v>
+        <v>-48.03587909676662</v>
       </c>
       <c r="O57">
-        <v>-21.11727882430221</v>
+        <v>-9.607175819353325</v>
       </c>
       <c r="P57">
-        <v>-84.46911529720883</v>
+        <v>-38.4287032774133</v>
       </c>
       <c r="Q57">
-        <v>227.7308847027912</v>
+        <v>273.7712967225867</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.09813239117564909</v>
+        <v>0.09757593168619227</v>
       </c>
       <c r="T57">
-        <v>1.075450360571873</v>
+        <v>1.064567650580426</v>
       </c>
       <c r="U57">
-        <v>0.1348577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V57">
-        <v>0.1665329093922815</v>
+        <v>0.1832462945386574</v>
       </c>
       <c r="W57">
-        <v>0.1123994919057341</v>
+        <v>0.1000994919057341</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8326645469614073</v>
+        <v>0.9162314726932868</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1068698740216127</v>
+        <v>0.09973146725135718</v>
       </c>
       <c r="C58">
-        <v>-29.58712951424422</v>
+        <v>427.4657581004358</v>
       </c>
       <c r="D58">
-        <v>4642.587506680414</v>
+        <v>5099.640394295094</v>
       </c>
       <c r="E58">
         <v>3203.57707156134</v>
@@ -6049,37 +6049,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M58">
-        <v>642.4588740146295</v>
+        <v>583.8619859894352</v>
       </c>
       <c r="N58">
-        <v>-117.0588740146294</v>
+        <v>-58.46198598943511</v>
       </c>
       <c r="O58">
-        <v>-23.41177480292588</v>
+        <v>-11.69239719788702</v>
       </c>
       <c r="P58">
-        <v>-93.64709921170352</v>
+        <v>-46.76958879154809</v>
       </c>
       <c r="Q58">
-        <v>218.5529007882965</v>
+        <v>265.4304112084519</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.09932176370236839</v>
+        <v>0.09875265740633302</v>
       </c>
       <c r="T58">
-        <v>1.099892414221234</v>
+        <v>1.088762369911799</v>
       </c>
       <c r="U58">
-        <v>0.1348577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V58">
-        <v>0.1635591074388479</v>
+        <v>0.1799740392790385</v>
       </c>
       <c r="W58">
-        <v>0.1128005321295904</v>
+        <v>0.1005005321295904</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8177955371942394</v>
+        <v>0.8998701963951924</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1077604514660296</v>
+        <v>0.1004990446957741</v>
       </c>
       <c r="C59">
-        <v>-166.089697196594</v>
+        <v>288.8766538123118</v>
       </c>
       <c r="D59">
-        <v>4591.155914644397</v>
+        <v>5046.122265653303</v>
       </c>
       <c r="E59">
         <v>3288.648047207673</v>
@@ -6131,37 +6131,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M59">
-        <v>653.9313539077478</v>
+        <v>594.2880928821036</v>
       </c>
       <c r="N59">
-        <v>-128.5313539077478</v>
+        <v>-68.88809288210348</v>
       </c>
       <c r="O59">
-        <v>-25.70627078154955</v>
+        <v>-13.7776185764207</v>
       </c>
       <c r="P59">
-        <v>-102.8250831261982</v>
+        <v>-55.11047430568279</v>
       </c>
       <c r="Q59">
-        <v>209.3749168738018</v>
+        <v>257.0895256943172</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1005664558814932</v>
+        <v>0.0999841145553175</v>
       </c>
       <c r="T59">
-        <v>1.125471307575216</v>
+        <v>1.114082425026027</v>
       </c>
       <c r="U59">
-        <v>0.1348577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V59">
-        <v>0.1606896494136049</v>
+        <v>0.1768165999934413</v>
       </c>
       <c r="W59">
-        <v>0.1131875007666448</v>
+        <v>0.1008875007666448</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8034482470680246</v>
+        <v>0.8840829999672066</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1588103659484844</v>
+        <v>0.1012666221401909</v>
       </c>
       <c r="C60">
-        <v>-2034.319053034032</v>
+        <v>151.3991745908615</v>
       </c>
       <c r="D60">
-        <v>2807.997534453292</v>
+        <v>4993.715762078185</v>
       </c>
       <c r="E60">
         <v>3373.719022854006</v>
@@ -6213,45 +6213,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M60">
-        <v>1084.31033207854</v>
+        <v>604.7141997747721</v>
       </c>
       <c r="N60">
-        <v>-558.91033207854</v>
+        <v>-79.31419977477196</v>
       </c>
       <c r="O60">
-        <v>-111.782066415708</v>
+        <v>-15.86283995495439</v>
       </c>
       <c r="P60">
-        <v>-447.128265662832</v>
+        <v>-63.45135981981757</v>
       </c>
       <c r="Q60">
-        <v>-134.928265662832</v>
+        <v>248.7486401801824</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1040545549216189</v>
+        <v>0.1012742125209203</v>
       </c>
       <c r="T60">
-        <v>1.197153057369961</v>
+        <v>1.140608197050456</v>
       </c>
       <c r="U60">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V60">
-        <v>0.09690952570614142</v>
+        <v>0.1737680379245889</v>
       </c>
       <c r="W60">
-        <v>0.1984611256575939</v>
+        <v>0.1012611256575938</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.4845476285307071</v>
+        <v>0.8688401896229445</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1605499433929013</v>
+        <v>0.1020341995846079</v>
       </c>
       <c r="C61">
-        <v>-2156.067827241479</v>
+        <v>14.99904208697353</v>
       </c>
       <c r="D61">
-        <v>2771.319735892178</v>
+        <v>4942.38660522063</v>
       </c>
       <c r="E61">
         <v>3458.789998500339</v>
@@ -6295,45 +6295,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M61">
-        <v>1103.005337804032</v>
+        <v>615.1403066674405</v>
       </c>
       <c r="N61">
-        <v>-577.6053378040319</v>
+        <v>-89.74030666744045</v>
       </c>
       <c r="O61">
-        <v>-115.5210675608064</v>
+        <v>-17.94806133348809</v>
       </c>
       <c r="P61">
-        <v>-462.0842702432255</v>
+        <v>-71.79224533395237</v>
       </c>
       <c r="Q61">
-        <v>-149.8842702432256</v>
+        <v>240.4077546660476</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1054753977245853</v>
+        <v>0.1026272420946013</v>
       </c>
       <c r="T61">
-        <v>1.226351912427765</v>
+        <v>1.168427909173638</v>
       </c>
       <c r="U61">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V61">
-        <v>0.09526699137213904</v>
+        <v>0.1708228169428162</v>
       </c>
       <c r="W61">
-        <v>0.1988220852980023</v>
+        <v>0.1016220852980022</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.4763349568606952</v>
+        <v>0.854114084714081</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1622895208373182</v>
+        <v>0.1028017770290247</v>
       </c>
       <c r="C62">
-        <v>-2276.870791646536</v>
+        <v>-120.3566270331194</v>
       </c>
       <c r="D62">
-        <v>2735.587747133454</v>
+        <v>4892.10191174687</v>
       </c>
       <c r="E62">
         <v>3543.860974146672</v>
@@ -6377,45 +6377,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M62">
-        <v>1121.700343529524</v>
+        <v>625.566413560109</v>
       </c>
       <c r="N62">
-        <v>-596.3003435295241</v>
+        <v>-100.1664135601089</v>
       </c>
       <c r="O62">
-        <v>-119.2600687059048</v>
+        <v>-20.03328271202179</v>
       </c>
       <c r="P62">
-        <v>-477.0402748236193</v>
+        <v>-80.13313084808715</v>
       </c>
       <c r="Q62">
-        <v>-164.8402748236193</v>
+        <v>232.0668691519128</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1069672826676999</v>
+        <v>0.1040479231469663</v>
       </c>
       <c r="T62">
-        <v>1.257010710238459</v>
+        <v>1.197638606902979</v>
       </c>
       <c r="U62">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V62">
-        <v>0.09367920818260339</v>
+        <v>0.1679757699937693</v>
       </c>
       <c r="W62">
-        <v>0.199171012950397</v>
+        <v>0.101971012950397</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.4683960409130169</v>
+        <v>0.8398788499688463</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1640290982817351</v>
+        <v>0.1035693544734416</v>
       </c>
       <c r="C63">
-        <v>-2396.764064926603</v>
+        <v>-254.6993913387496</v>
       </c>
       <c r="D63">
-        <v>2700.76544949972</v>
+        <v>4842.830123087574</v>
       </c>
       <c r="E63">
         <v>3628.931949793006</v>
@@ -6459,45 +6459,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M63">
-        <v>1140.395349255016</v>
+        <v>635.9925204527775</v>
       </c>
       <c r="N63">
-        <v>-614.9953492550162</v>
+        <v>-110.5925204527774</v>
       </c>
       <c r="O63">
-        <v>-122.9990698510032</v>
+        <v>-22.11850409055549</v>
       </c>
       <c r="P63">
-        <v>-491.996279404013</v>
+        <v>-88.47401636222193</v>
       </c>
       <c r="Q63">
-        <v>-179.796279404013</v>
+        <v>223.7259836377781</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1085356745309742</v>
+        <v>0.1055414596379142</v>
       </c>
       <c r="T63">
-        <v>1.289241754090727</v>
+        <v>1.228347289131261</v>
       </c>
       <c r="U63">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V63">
-        <v>0.09214348345829841</v>
+        <v>0.1652220688463304</v>
       </c>
       <c r="W63">
-        <v>0.1995085003518936</v>
+        <v>0.1023085003518936</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.460717417291492</v>
+        <v>0.8261103442316522</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1657686757261519</v>
+        <v>0.1043369319178585</v>
       </c>
       <c r="C64">
-        <v>-2515.781949803583</v>
+        <v>-388.0595506827285</v>
       </c>
       <c r="D64">
-        <v>2666.818540269074</v>
+        <v>4794.540939389928</v>
       </c>
       <c r="E64">
         <v>3714.002925439338</v>
@@ -6541,45 +6541,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M64">
-        <v>1159.090354980508</v>
+        <v>646.418627345446</v>
       </c>
       <c r="N64">
-        <v>-633.6903549805081</v>
+        <v>-121.0186273454459</v>
       </c>
       <c r="O64">
-        <v>-126.7380709961016</v>
+        <v>-24.20372546908918</v>
       </c>
       <c r="P64">
-        <v>-506.9522839844065</v>
+        <v>-96.81490187635673</v>
       </c>
       <c r="Q64">
-        <v>-194.7522839844065</v>
+        <v>215.3850981236433</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1101866133344209</v>
+        <v>0.1071136033125961</v>
       </c>
       <c r="T64">
-        <v>1.323169168672062</v>
+        <v>1.26067221779261</v>
       </c>
       <c r="U64">
-        <v>0.2197577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V64">
-        <v>0.09065729824122909</v>
+        <v>0.1625571967681638</v>
       </c>
       <c r="W64">
-        <v>0.1998351010630194</v>
+        <v>0.1026351010630194</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.4532864912061454</v>
+        <v>0.812785983840819</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1675082531705689</v>
+        <v>0.1233589867728506</v>
       </c>
       <c r="C65">
-        <v>-2633.957045754235</v>
+        <v>-1423.142346598371</v>
       </c>
       <c r="D65">
-        <v>2633.714419964754</v>
+        <v>3844.529119120618</v>
       </c>
       <c r="E65">
         <v>3799.073901085671</v>
@@ -6623,45 +6623,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M65">
-        <v>1177.785360706</v>
+        <v>807.98182957139</v>
       </c>
       <c r="N65">
-        <v>-652.3853607060003</v>
+        <v>-282.5818295713899</v>
       </c>
       <c r="O65">
-        <v>-130.4770721412001</v>
+        <v>-56.51636591427798</v>
       </c>
       <c r="P65">
-        <v>-521.9082885648002</v>
+        <v>-226.0654636571119</v>
       </c>
       <c r="Q65">
-        <v>-209.7082885648002</v>
+        <v>86.13453634288805</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1119267920731891</v>
+        <v>0.1100909369442208</v>
       </c>
       <c r="T65">
-        <v>1.35893049755509</v>
+        <v>1.321889330956757</v>
       </c>
       <c r="U65">
-        <v>0.2197577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V65">
-        <v>0.08921829350724131</v>
+        <v>0.1300524295895884</v>
       </c>
       <c r="W65">
-        <v>0.2001513334976014</v>
+        <v>0.1311513334976014</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.4460914675362065</v>
+        <v>0.650262147947942</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1692478306149858</v>
+        <v>0.1595284372623487</v>
       </c>
       <c r="C66">
-        <v>-2751.320353428783</v>
+        <v>-2560.298534903391</v>
       </c>
       <c r="D66">
-        <v>2601.42208793654</v>
+        <v>2792.443906461932</v>
       </c>
       <c r="E66">
         <v>3884.144876732004</v>
@@ -6705,37 +6705,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M66">
-        <v>1196.480366431492</v>
+        <v>1114.812229811012</v>
       </c>
       <c r="N66">
-        <v>-671.0803664314922</v>
+        <v>-589.4122298110124</v>
       </c>
       <c r="O66">
-        <v>-134.2160732862984</v>
+        <v>-117.8824459622025</v>
       </c>
       <c r="P66">
-        <v>-536.8642931451938</v>
+        <v>-471.5297838488099</v>
       </c>
       <c r="Q66">
-        <v>-224.6642931451938</v>
+        <v>-159.3297838488099</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1137636474085554</v>
+        <v>0.1134319992067859</v>
       </c>
       <c r="T66">
-        <v>1.396678566931621</v>
+        <v>1.390585087604057</v>
       </c>
       <c r="U66">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V66">
-        <v>0.08782425767119068</v>
+        <v>0.09425802587204629</v>
       </c>
       <c r="W66">
-        <v>0.2004576836686028</v>
+        <v>0.1854576836686028</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4391212883559534</v>
+        <v>0.4712901293602314</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1709874080594026</v>
+        <v>0.1611180147067656</v>
       </c>
       <c r="C67">
-        <v>-2867.901371480814</v>
+        <v>-2678.554372670352</v>
       </c>
       <c r="D67">
-        <v>2569.912045530843</v>
+        <v>2759.259044341304</v>
       </c>
       <c r="E67">
         <v>3969.215852378338</v>
@@ -6787,37 +6787,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M67">
-        <v>1215.175372156985</v>
+        <v>1132.23117090181</v>
       </c>
       <c r="N67">
-        <v>-689.7753721569845</v>
+        <v>-606.8311709018096</v>
       </c>
       <c r="O67">
-        <v>-137.9550744313969</v>
+        <v>-121.3662341803619</v>
       </c>
       <c r="P67">
-        <v>-551.8202977255876</v>
+        <v>-485.4649367214477</v>
       </c>
       <c r="Q67">
-        <v>-239.6202977255876</v>
+        <v>-173.2649367214477</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1157054659059427</v>
+        <v>0.1153643420412655</v>
       </c>
       <c r="T67">
-        <v>1.436583668843953</v>
+        <v>1.43031609010703</v>
       </c>
       <c r="U67">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V67">
-        <v>0.08647311524548004</v>
+        <v>0.09280790239709172</v>
       </c>
       <c r="W67">
-        <v>0.2007546076804964</v>
+        <v>0.1857546076804965</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4323655762274001</v>
+        <v>0.4640395119854586</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1727269855038195</v>
+        <v>0.1627075921511825</v>
       </c>
       <c r="C68">
-        <v>-2983.72818644423</v>
+        <v>-2796.030748473865</v>
       </c>
       <c r="D68">
-        <v>2539.15620621376</v>
+        <v>2726.853644184124</v>
       </c>
       <c r="E68">
         <v>4054.286828024671</v>
@@ -6869,37 +6869,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M68">
-        <v>1233.870377882477</v>
+        <v>1149.650111992607</v>
       </c>
       <c r="N68">
-        <v>-708.4703778824764</v>
+        <v>-624.2501119926067</v>
       </c>
       <c r="O68">
-        <v>-141.6940755764953</v>
+        <v>-124.8500223985213</v>
       </c>
       <c r="P68">
-        <v>-566.7763023059812</v>
+        <v>-499.4000895940853</v>
       </c>
       <c r="Q68">
-        <v>-254.5763023059812</v>
+        <v>-187.2000895940853</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1177615090208234</v>
+        <v>0.1174103521013027</v>
       </c>
       <c r="T68">
-        <v>1.478836129692304</v>
+        <v>1.472384210404295</v>
       </c>
       <c r="U68">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V68">
-        <v>0.08516291652963943</v>
+        <v>0.09140172205774184</v>
       </c>
       <c r="W68">
-        <v>0.20104253399506</v>
+        <v>0.18604253399506</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4258145826481972</v>
+        <v>0.4570086102887092</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1744665629482364</v>
+        <v>0.1642971695955994</v>
       </c>
       <c r="C69">
-        <v>-3098.827556232804</v>
+        <v>-2912.754806095718</v>
       </c>
       <c r="D69">
-        <v>2509.127812071518</v>
+        <v>2695.200562208604</v>
       </c>
       <c r="E69">
         <v>4139.357803671004</v>
@@ -6951,37 +6951,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M69">
-        <v>1252.565383607969</v>
+        <v>1167.069053083404</v>
       </c>
       <c r="N69">
-        <v>-727.1653836079686</v>
+        <v>-641.6690530834037</v>
       </c>
       <c r="O69">
-        <v>-145.4330767215937</v>
+        <v>-128.3338106166808</v>
       </c>
       <c r="P69">
-        <v>-581.7323068863749</v>
+        <v>-513.335242466723</v>
       </c>
       <c r="Q69">
-        <v>-269.5323068863749</v>
+        <v>-201.135242466723</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1199421608093332</v>
+        <v>0.1195803627710392</v>
       </c>
       <c r="T69">
-        <v>1.523649345743587</v>
+        <v>1.51700191374988</v>
       </c>
       <c r="U69">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V69">
-        <v>0.08389182822322691</v>
+        <v>0.09003751725090987</v>
       </c>
       <c r="W69">
-        <v>0.2013218654942634</v>
+        <v>0.1863218654942634</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4194591411161345</v>
+        <v>0.4501875862545494</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1762061403926533</v>
+        <v>0.1658867470400163</v>
       </c>
       <c r="C70">
-        <v>-3213.224987784138</v>
+        <v>-3028.752443448919</v>
       </c>
       <c r="D70">
-        <v>2479.801356166518</v>
+        <v>2664.273900501737</v>
       </c>
       <c r="E70">
         <v>4224.428779317338</v>
@@ -7033,37 +7033,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M70">
-        <v>1271.260389333461</v>
+        <v>1184.487994174201</v>
       </c>
       <c r="N70">
-        <v>-745.8603893334607</v>
+        <v>-659.0879941742007</v>
       </c>
       <c r="O70">
-        <v>-149.1720778666921</v>
+        <v>-131.8175988348401</v>
       </c>
       <c r="P70">
-        <v>-596.6883114667686</v>
+        <v>-527.2703953393606</v>
       </c>
       <c r="Q70">
-        <v>-284.4883114667686</v>
+        <v>-215.0703953393606</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1222591033346249</v>
+        <v>0.1218859991076342</v>
       </c>
       <c r="T70">
-        <v>1.571263387798074</v>
+        <v>1.564408223554564</v>
       </c>
       <c r="U70">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V70">
-        <v>0.08265812486700297</v>
+        <v>0.08871343611486709</v>
       </c>
       <c r="W70">
-        <v>0.2015929813611373</v>
+        <v>0.1865929813611373</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4132906243350148</v>
+        <v>0.4435671805743354</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1779457178370702</v>
+        <v>0.1674763244844332</v>
       </c>
       <c r="C71">
-        <v>-3326.944809321537</v>
+        <v>-3144.048383246743</v>
       </c>
       <c r="D71">
-        <v>2451.152510275452</v>
+        <v>2634.048936350246</v>
       </c>
       <c r="E71">
         <v>4309.499754963671</v>
@@ -7115,37 +7115,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M71">
-        <v>1289.955395058953</v>
+        <v>1201.906935264998</v>
       </c>
       <c r="N71">
-        <v>-764.5553950589529</v>
+        <v>-676.5069352649978</v>
       </c>
       <c r="O71">
-        <v>-152.9110790117906</v>
+        <v>-135.3013870529996</v>
       </c>
       <c r="P71">
-        <v>-611.6443160471623</v>
+        <v>-541.2055482119982</v>
       </c>
       <c r="Q71">
-        <v>-299.4443160471623</v>
+        <v>-229.0055482119982</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1247255260228386</v>
+        <v>0.1243403861756224</v>
       </c>
       <c r="T71">
-        <v>1.621949303533496</v>
+        <v>1.61487300495955</v>
       </c>
       <c r="U71">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V71">
-        <v>0.08146018102835076</v>
+        <v>0.08742773414218785</v>
       </c>
       <c r="W71">
-        <v>0.2018562387970874</v>
+        <v>0.1868562387970873</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4073009051417538</v>
+        <v>0.4371386707109393</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1796852952814871</v>
+        <v>0.1690659019288501</v>
       </c>
       <c r="C72">
-        <v>-3440.010237664112</v>
+        <v>-3258.666238915498</v>
       </c>
       <c r="D72">
-        <v>2423.15805757921</v>
+        <v>2604.502056327824</v>
       </c>
       <c r="E72">
         <v>4394.570730610004</v>
@@ -7197,37 +7197,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M72">
-        <v>1308.650400784445</v>
+        <v>1219.325876355795</v>
       </c>
       <c r="N72">
-        <v>-783.2504007844448</v>
+        <v>-693.9258763557948</v>
       </c>
       <c r="O72">
-        <v>-156.650080156889</v>
+        <v>-138.785175271159</v>
       </c>
       <c r="P72">
-        <v>-626.6003206275558</v>
+        <v>-555.1407010846358</v>
       </c>
       <c r="Q72">
-        <v>-314.4003206275558</v>
+        <v>-242.9407010846358</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1273563768902665</v>
+        <v>0.1269583990481431</v>
       </c>
       <c r="T72">
-        <v>1.676014280317945</v>
+        <v>1.668702105124868</v>
       </c>
       <c r="U72">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V72">
-        <v>0.08029646415651719</v>
+        <v>0.08617876651158518</v>
       </c>
       <c r="W72">
-        <v>0.2021119745920102</v>
+        <v>0.1871119745920102</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4014823207825859</v>
+        <v>0.4308938325579259</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.181424872725904</v>
+        <v>0.170655479373267</v>
       </c>
       <c r="C73">
-        <v>-3552.443440976491</v>
+        <v>-3372.628576120307</v>
       </c>
       <c r="D73">
-        <v>2395.795829913164</v>
+        <v>2575.610694769348</v>
       </c>
       <c r="E73">
         <v>4479.641706256337</v>
@@ -7279,37 +7279,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M73">
-        <v>1327.345406509937</v>
+        <v>1236.744817446592</v>
       </c>
       <c r="N73">
-        <v>-801.9454065099369</v>
+        <v>-711.3448174465918</v>
       </c>
       <c r="O73">
-        <v>-160.3890813019874</v>
+        <v>-142.2689634893184</v>
       </c>
       <c r="P73">
-        <v>-641.5563252079495</v>
+        <v>-569.0758539572735</v>
       </c>
       <c r="Q73">
-        <v>-329.3563252079495</v>
+        <v>-256.8758539572735</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1301686657485516</v>
+        <v>0.1297569645325618</v>
       </c>
       <c r="T73">
-        <v>1.733807876190978</v>
+        <v>1.726243557025725</v>
       </c>
       <c r="U73">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V73">
-        <v>0.07916552804163667</v>
+        <v>0.08496498106776003</v>
       </c>
       <c r="W73">
-        <v>0.202360506561724</v>
+        <v>0.187360506561724</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3958276402081833</v>
+        <v>0.4248249053388001</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1831644501703209</v>
+        <v>0.1722450568176839</v>
       </c>
       <c r="C74">
-        <v>-3664.265597314596</v>
+        <v>-3485.956970240858</v>
       </c>
       <c r="D74">
-        <v>2369.044649221392</v>
+        <v>2547.35327629513</v>
       </c>
       <c r="E74">
         <v>4564.71268190267</v>
@@ -7361,37 +7361,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M74">
-        <v>1346.040412235429</v>
+        <v>1254.163758537389</v>
       </c>
       <c r="N74">
-        <v>-820.6404122354288</v>
+        <v>-728.7637585373889</v>
       </c>
       <c r="O74">
-        <v>-164.1280824470858</v>
+        <v>-145.7527517074778</v>
       </c>
       <c r="P74">
-        <v>-656.5123297883431</v>
+        <v>-583.0110068299111</v>
       </c>
       <c r="Q74">
-        <v>-344.3123297883431</v>
+        <v>-270.8110068299112</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1331818323824284</v>
+        <v>0.1327554275515819</v>
       </c>
       <c r="T74">
-        <v>1.795729586054941</v>
+        <v>1.787895112633787</v>
       </c>
       <c r="U74">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V74">
-        <v>0.07806600681883616</v>
+        <v>0.08378491188626337</v>
       </c>
       <c r="W74">
-        <v>0.2026021348656124</v>
+        <v>0.1876021348656124</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3903300340941808</v>
+        <v>0.4189245594313168</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1849040276147378</v>
+        <v>0.1738346342621007</v>
       </c>
       <c r="C75">
-        <v>-3775.496949292437</v>
+        <v>-3598.672060104739</v>
       </c>
       <c r="D75">
-        <v>2342.884272889884</v>
+        <v>2519.709162077582</v>
       </c>
       <c r="E75">
         <v>4649.783657549003</v>
@@ -7443,37 +7443,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M75">
-        <v>1364.735417960921</v>
+        <v>1271.582699628186</v>
       </c>
       <c r="N75">
-        <v>-839.3354179609209</v>
+        <v>-746.1826996281859</v>
       </c>
       <c r="O75">
-        <v>-167.8670835921842</v>
+        <v>-149.2365399256372</v>
       </c>
       <c r="P75">
-        <v>-671.4683343687368</v>
+        <v>-596.9461597025487</v>
       </c>
       <c r="Q75">
-        <v>-359.2683343687368</v>
+        <v>-284.7461597025487</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1364181965447405</v>
+        <v>0.1359759989423812</v>
       </c>
       <c r="T75">
-        <v>1.862238089242161</v>
+        <v>1.854113450138742</v>
       </c>
       <c r="U75">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V75">
-        <v>0.07699660946515346</v>
+        <v>0.08263717336727347</v>
       </c>
       <c r="W75">
-        <v>0.2028371432159696</v>
+        <v>0.1878371432159696</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3849830473257673</v>
+        <v>0.4131858668363673</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1866436050591547</v>
+        <v>0.1754242117065177</v>
       </c>
       <c r="C76">
-        <v>-3886.156855166498</v>
+        <v>-3710.793598259647</v>
       </c>
       <c r="D76">
-        <v>2317.295342662157</v>
+        <v>2492.658599569007</v>
       </c>
       <c r="E76">
         <v>4734.854633195337</v>
@@ -7525,37 +7525,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M76">
-        <v>1383.430423686413</v>
+        <v>1289.001640718983</v>
       </c>
       <c r="N76">
-        <v>-858.0304236864131</v>
+        <v>-763.6016407189832</v>
       </c>
       <c r="O76">
-        <v>-171.6060847372826</v>
+        <v>-152.7203281437966</v>
       </c>
       <c r="P76">
-        <v>-686.4243389491305</v>
+        <v>-610.8813125751865</v>
       </c>
       <c r="Q76">
-        <v>-374.2243389491305</v>
+        <v>-298.6813125751865</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1399035117964613</v>
+        <v>0.1394443065940113</v>
       </c>
       <c r="T76">
-        <v>1.93386263113609</v>
+        <v>1.925425505913309</v>
       </c>
       <c r="U76">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V76">
-        <v>0.07595611474265139</v>
+        <v>0.08152045480825625</v>
       </c>
       <c r="W76">
-        <v>0.2030657999892902</v>
+        <v>0.1880657999892902</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3797805737132569</v>
+        <v>0.4076022740412812</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1883831825035716</v>
+        <v>0.1770137891509345</v>
       </c>
       <c r="C77">
-        <v>-3996.263836608617</v>
+        <v>-3822.340498041749</v>
       </c>
       <c r="D77">
-        <v>2292.259336866371</v>
+        <v>2466.182675433239</v>
       </c>
       <c r="E77">
         <v>4819.92560884167</v>
@@ -7607,37 +7607,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M77">
-        <v>1402.125429411905</v>
+        <v>1306.42058180978</v>
       </c>
       <c r="N77">
-        <v>-876.725429411905</v>
+        <v>-781.0205818097802</v>
       </c>
       <c r="O77">
-        <v>-175.345085882381</v>
+        <v>-156.204116361956</v>
       </c>
       <c r="P77">
-        <v>-701.380343529524</v>
+        <v>-624.8164654478242</v>
       </c>
       <c r="Q77">
-        <v>-389.180343529524</v>
+        <v>-312.6164654478242</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1436676522683198</v>
+        <v>0.1431900788577717</v>
       </c>
       <c r="T77">
-        <v>2.011217136381534</v>
+        <v>2.002442526149841</v>
       </c>
       <c r="U77">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V77">
-        <v>0.07494336654608272</v>
+        <v>0.08043351541081284</v>
       </c>
       <c r="W77">
-        <v>0.2032883592486555</v>
+        <v>0.1882883592486555</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3747168327304136</v>
+        <v>0.4021675770540641</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1901227599479885</v>
+        <v>0.1786033665953514</v>
       </c>
       <c r="C78">
-        <v>-4105.835623415171</v>
+        <v>-3933.330877675962</v>
       </c>
       <c r="D78">
-        <v>2267.758525706151</v>
+        <v>2440.263271445359</v>
       </c>
       <c r="E78">
         <v>4904.996584488003</v>
@@ -7689,37 +7689,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M78">
-        <v>1420.820435137397</v>
+        <v>1323.839522900577</v>
       </c>
       <c r="N78">
-        <v>-895.4204351373971</v>
+        <v>-798.4395229005772</v>
       </c>
       <c r="O78">
-        <v>-179.0840870274794</v>
+        <v>-159.6879045801155</v>
       </c>
       <c r="P78">
-        <v>-716.3363481099177</v>
+        <v>-638.7516183204618</v>
       </c>
       <c r="Q78">
-        <v>-404.1363481099177</v>
+        <v>-326.5516183204618</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1477454711128331</v>
+        <v>0.1472479988101789</v>
       </c>
       <c r="T78">
-        <v>2.095017850397431</v>
+        <v>2.085877631406085</v>
       </c>
       <c r="U78">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V78">
-        <v>0.07395726961784478</v>
+        <v>0.0793751796817232</v>
       </c>
       <c r="W78">
-        <v>0.203505061685406</v>
+        <v>0.1885050616854059</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3697863480892238</v>
+        <v>0.3968758984086159</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1918623373924054</v>
+        <v>0.1801929440397684</v>
       </c>
       <c r="C79">
-        <v>-4214.889195379312</v>
+        <v>-4043.782101624191</v>
       </c>
       <c r="D79">
-        <v>2243.775929388343</v>
+        <v>2414.883023143464</v>
       </c>
       <c r="E79">
         <v>4990.067560134336</v>
@@ -7771,37 +7771,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M79">
-        <v>1439.515440862889</v>
+        <v>1341.258463991375</v>
       </c>
       <c r="N79">
-        <v>-914.1154408628893</v>
+        <v>-815.8584639913745</v>
       </c>
       <c r="O79">
-        <v>-182.8230881725779</v>
+        <v>-163.1716927982749</v>
       </c>
       <c r="P79">
-        <v>-731.2923526903114</v>
+        <v>-652.6867711930996</v>
       </c>
       <c r="Q79">
-        <v>-419.0923526903114</v>
+        <v>-340.4867711930996</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1521778829003476</v>
+        <v>0.1516587813671432</v>
       </c>
       <c r="T79">
-        <v>2.186105583023407</v>
+        <v>2.17656796320635</v>
       </c>
       <c r="U79">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V79">
-        <v>0.0729967855968338</v>
+        <v>0.07834433319235015</v>
       </c>
       <c r="W79">
-        <v>0.2037161354874356</v>
+        <v>0.1887161354874356</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.364983927984169</v>
+        <v>0.3917216659617507</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1936019148368223</v>
+        <v>0.1817825214841852</v>
       </c>
       <c r="C80">
-        <v>-4323.440821534115</v>
+        <v>-4153.710819379851</v>
       </c>
       <c r="D80">
-        <v>2220.295278879873</v>
+        <v>2390.025281034136</v>
       </c>
       <c r="E80">
         <v>5075.138535780669</v>
@@ -7853,37 +7853,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M80">
-        <v>1458.210446588382</v>
+        <v>1358.677405082172</v>
       </c>
       <c r="N80">
-        <v>-932.8104465883814</v>
+        <v>-833.2774050821715</v>
       </c>
       <c r="O80">
-        <v>-186.5620893176763</v>
+        <v>-166.6554810164343</v>
       </c>
       <c r="P80">
-        <v>-746.2483572707051</v>
+        <v>-666.6219240657372</v>
       </c>
       <c r="Q80">
-        <v>-434.0483572707051</v>
+        <v>-354.4219240657372</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1570132412139998</v>
+        <v>0.1564705441565588</v>
       </c>
       <c r="T80">
-        <v>2.28547401861538</v>
+        <v>2.27550287062482</v>
       </c>
       <c r="U80">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V80">
-        <v>0.07206092937123336</v>
+        <v>0.0773399186642431</v>
       </c>
       <c r="W80">
-        <v>0.2039217971406953</v>
+        <v>0.1889217971406953</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3603046468561668</v>
+        <v>0.3866995933212155</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1953414922812392</v>
+        <v>0.1833720989286021</v>
       </c>
       <c r="C81">
-        <v>-4431.50609695721</v>
+        <v>-4263.133001890805</v>
       </c>
       <c r="D81">
-        <v>2197.30097910311</v>
+        <v>2365.674074169516</v>
       </c>
       <c r="E81">
         <v>5160.209511427002</v>
@@ -7935,37 +7935,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M81">
-        <v>1476.905452313873</v>
+        <v>1376.096346172969</v>
       </c>
       <c r="N81">
-        <v>-951.5054523138733</v>
+        <v>-850.6963461729686</v>
       </c>
       <c r="O81">
-        <v>-190.3010904627747</v>
+        <v>-170.1392692345937</v>
       </c>
       <c r="P81">
-        <v>-761.2043618510986</v>
+        <v>-680.5570769383748</v>
       </c>
       <c r="Q81">
-        <v>-449.0043618510986</v>
+        <v>-368.3570769383749</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1623091098432379</v>
+        <v>0.1617405700687759</v>
       </c>
       <c r="T81">
-        <v>2.394306114739922</v>
+        <v>2.383860150178383</v>
       </c>
       <c r="U81">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V81">
-        <v>0.07114876570830636</v>
+        <v>0.0763609323520375</v>
       </c>
       <c r="W81">
-        <v>0.2041222521698218</v>
+        <v>0.1891222521698218</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3557438285415319</v>
+        <v>0.3818046617601875</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1970810697256561</v>
+        <v>0.184961676373019</v>
       </c>
       <c r="C82">
-        <v>-4539.099977311874</v>
+        <v>-4372.063975778137</v>
       </c>
       <c r="D82">
-        <v>2174.778074394781</v>
+        <v>2341.814075928517</v>
       </c>
       <c r="E82">
         <v>5245.280487073336</v>
@@ -8017,37 +8017,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M82">
-        <v>1495.600458039366</v>
+        <v>1393.515287263766</v>
       </c>
       <c r="N82">
-        <v>-970.2004580393657</v>
+        <v>-868.1152872637656</v>
       </c>
       <c r="O82">
-        <v>-194.0400916078731</v>
+        <v>-173.6230574527531</v>
       </c>
       <c r="P82">
-        <v>-776.1603664314925</v>
+        <v>-694.4922298110125</v>
       </c>
       <c r="Q82">
-        <v>-463.9603664314926</v>
+        <v>-382.2922298110125</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1681345653353998</v>
+        <v>0.1675375985722147</v>
       </c>
       <c r="T82">
-        <v>2.514021420476919</v>
+        <v>2.503053157687302</v>
       </c>
       <c r="U82">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V82">
-        <v>0.07025940613695252</v>
+        <v>0.07540642069763703</v>
       </c>
       <c r="W82">
-        <v>0.2043176958232202</v>
+        <v>0.1893176958232201</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3512970306847626</v>
+        <v>0.3770321034881851</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.198820647170073</v>
+        <v>0.1865512538174359</v>
       </c>
       <c r="C83">
-        <v>-4646.236811285335</v>
+        <v>-4480.518455504842</v>
       </c>
       <c r="D83">
-        <v>2152.712216067653</v>
+        <v>2318.430571848145</v>
       </c>
       <c r="E83">
         <v>5330.351462719669</v>
@@ -8099,37 +8099,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M83">
-        <v>1514.295463764858</v>
+        <v>1410.934228354563</v>
       </c>
       <c r="N83">
-        <v>-988.8954637648576</v>
+        <v>-885.5342283545626</v>
       </c>
       <c r="O83">
-        <v>-197.7790927529715</v>
+        <v>-177.1068456709125</v>
       </c>
       <c r="P83">
-        <v>-791.116371011886</v>
+        <v>-708.4273826836501</v>
       </c>
       <c r="Q83">
-        <v>-478.916371011886</v>
+        <v>-396.2273826836501</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1745732266688419</v>
+        <v>0.1739448406023313</v>
       </c>
       <c r="T83">
-        <v>2.646338337344125</v>
+        <v>2.634792797565581</v>
       </c>
       <c r="U83">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V83">
-        <v>0.06939200606118769</v>
+        <v>0.07447547723223411</v>
       </c>
       <c r="W83">
-        <v>0.2045083137073988</v>
+        <v>0.1895083137073987</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3469600303059384</v>
+        <v>0.3723773861611704</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2005602246144899</v>
+        <v>0.1881408312618528</v>
       </c>
       <c r="C84">
-        <v>-4752.930371072167</v>
+        <v>-4588.510573636307</v>
       </c>
       <c r="D84">
-        <v>2131.089631927154</v>
+        <v>2295.509429363014</v>
       </c>
       <c r="E84">
         <v>5415.422438366002</v>
@@ -8181,37 +8181,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M84">
-        <v>1532.99046949035</v>
+        <v>1428.35316944536</v>
       </c>
       <c r="N84">
-        <v>-1007.59046949035</v>
+        <v>-902.9531694453597</v>
       </c>
       <c r="O84">
-        <v>-201.51809389807</v>
+        <v>-180.5906338890719</v>
       </c>
       <c r="P84">
-        <v>-806.0723755922797</v>
+        <v>-722.3625355562878</v>
       </c>
       <c r="Q84">
-        <v>-493.8723755922798</v>
+        <v>-410.1625355562878</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1817272948171109</v>
+        <v>0.1810639984135719</v>
       </c>
       <c r="T84">
-        <v>2.793357133863243</v>
+        <v>2.781170175208114</v>
       </c>
       <c r="U84">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V84">
-        <v>0.06854576208483174</v>
+        <v>0.07356723970501174</v>
       </c>
       <c r="W84">
-        <v>0.2046942823748901</v>
+        <v>0.1896942823748901</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3427288104241587</v>
+        <v>0.3678361985250587</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2022998020589067</v>
+        <v>0.1897304087062697</v>
       </c>
       <c r="C85">
-        <v>-4859.193881038826</v>
+        <v>-4696.053909323334</v>
       </c>
       <c r="D85">
-        <v>2109.897097606828</v>
+        <v>2273.03706932232</v>
       </c>
       <c r="E85">
         <v>5500.493414012336</v>
@@ -8263,37 +8263,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M85">
-        <v>1551.685475215842</v>
+        <v>1445.772110536157</v>
       </c>
       <c r="N85">
-        <v>-1026.285475215842</v>
+        <v>-920.3721105361569</v>
       </c>
       <c r="O85">
-        <v>-205.2570950431684</v>
+        <v>-184.0744221072314</v>
       </c>
       <c r="P85">
-        <v>-821.0283801726735</v>
+        <v>-736.2976884289255</v>
       </c>
       <c r="Q85">
-        <v>-508.8283801726735</v>
+        <v>-424.0976884289256</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1897230180416468</v>
+        <v>0.1890207042026056</v>
       </c>
       <c r="T85">
-        <v>2.95767225938461</v>
+        <v>2.944768420808591</v>
       </c>
       <c r="U85">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V85">
-        <v>0.06771990952959279</v>
+        <v>0.07268088741940917</v>
       </c>
       <c r="W85">
-        <v>0.2048757698696708</v>
+        <v>0.1898757698696708</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.338599547647964</v>
+        <v>0.3634044370970458</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2040393795033237</v>
+        <v>0.1913199861506866</v>
       </c>
       <c r="C86">
-        <v>-4965.040044694705</v>
+        <v>-4803.161515128349</v>
       </c>
       <c r="D86">
-        <v>2089.121909597281</v>
+        <v>2251.000439163637</v>
       </c>
       <c r="E86">
         <v>5585.564389658668</v>
@@ -8345,37 +8345,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M86">
-        <v>1570.380480941334</v>
+        <v>1463.191051626954</v>
       </c>
       <c r="N86">
-        <v>-1044.980480941334</v>
+        <v>-937.7910516269537</v>
       </c>
       <c r="O86">
-        <v>-208.9960961882668</v>
+        <v>-187.5582103253907</v>
       </c>
       <c r="P86">
-        <v>-835.984384753067</v>
+        <v>-750.232841301563</v>
       </c>
       <c r="Q86">
-        <v>-523.7843847530671</v>
+        <v>-438.032841301563</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1987182066692497</v>
+        <v>0.1979719982152683</v>
       </c>
       <c r="T86">
-        <v>3.142526775596147</v>
+        <v>3.128816447109127</v>
       </c>
       <c r="U86">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V86">
-        <v>0.06691372013043098</v>
+        <v>0.07181563875965431</v>
       </c>
       <c r="W86">
-        <v>0.2050529362336234</v>
+        <v>0.1900529362336234</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3345686006521549</v>
+        <v>0.3590781937982715</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2057789569477405</v>
+        <v>0.1929095635951035</v>
       </c>
       <c r="C87">
-        <v>-5070.481070085312</v>
+        <v>-4909.845942306152</v>
       </c>
       <c r="D87">
-        <v>2068.751859853007</v>
+        <v>2229.386987632167</v>
       </c>
       <c r="E87">
         <v>5670.635365305001</v>
@@ -8427,37 +8427,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M87">
-        <v>1589.075486666826</v>
+        <v>1480.609992717751</v>
       </c>
       <c r="N87">
-        <v>-1063.675486666826</v>
+        <v>-955.2099927177508</v>
       </c>
       <c r="O87">
-        <v>-212.7350973333652</v>
+        <v>-191.0419985435502</v>
       </c>
       <c r="P87">
-        <v>-850.9403893334605</v>
+        <v>-764.1679941742007</v>
       </c>
       <c r="Q87">
-        <v>-538.7403893334606</v>
+        <v>-451.9679941742007</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.208912753780533</v>
+        <v>0.2081167980962862</v>
       </c>
       <c r="T87">
-        <v>3.35202856063589</v>
+        <v>3.337404210249735</v>
       </c>
       <c r="U87">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V87">
-        <v>0.06612649989360239</v>
+        <v>0.07097074889189368</v>
       </c>
       <c r="W87">
-        <v>0.2052259339772477</v>
+        <v>0.1902259339772477</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.330632499468012</v>
+        <v>0.3548537444594684</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2075185343921574</v>
+        <v>0.1944991410395204</v>
       </c>
       <c r="C88">
-        <v>-5175.528693714185</v>
+        <v>-5016.119264642068</v>
       </c>
       <c r="D88">
-        <v>2048.775211870468</v>
+        <v>2208.184640942585</v>
       </c>
       <c r="E88">
         <v>5755.706340951335</v>
@@ -8509,37 +8509,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M88">
-        <v>1607.770492392318</v>
+        <v>1498.028933808548</v>
       </c>
       <c r="N88">
-        <v>-1082.370492392318</v>
+        <v>-972.628933808548</v>
       </c>
       <c r="O88">
-        <v>-216.4740984784636</v>
+        <v>-194.5257867617096</v>
       </c>
       <c r="P88">
-        <v>-865.8963939138542</v>
+        <v>-778.1031470468384</v>
       </c>
       <c r="Q88">
-        <v>-553.6963939138543</v>
+        <v>-465.9031470468385</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2205636647648568</v>
+        <v>0.2197108551031638</v>
       </c>
       <c r="T88">
-        <v>3.591459172109882</v>
+        <v>3.575790225267574</v>
       </c>
       <c r="U88">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V88">
-        <v>0.0653575871041419</v>
+        <v>0.07014550762570886</v>
       </c>
       <c r="W88">
-        <v>0.2053949085175319</v>
+        <v>0.1903949085175319</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3267879355207095</v>
+        <v>0.3507275381285443</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2092581118365743</v>
+        <v>0.1960887184839373</v>
       </c>
       <c r="C89">
-        <v>-5280.194203092095</v>
+        <v>-5121.993100942667</v>
       </c>
       <c r="D89">
-        <v>2029.180678138891</v>
+        <v>2187.381780288319</v>
       </c>
       <c r="E89">
         <v>5840.777316597668</v>
@@ -8591,37 +8591,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M89">
-        <v>1626.46549811781</v>
+        <v>1515.447874899345</v>
       </c>
       <c r="N89">
-        <v>-1101.06549811781</v>
+        <v>-990.0478748993451</v>
       </c>
       <c r="O89">
-        <v>-220.213099623562</v>
+        <v>-198.009574979869</v>
       </c>
       <c r="P89">
-        <v>-880.852398494248</v>
+        <v>-792.038299919476</v>
       </c>
       <c r="Q89">
-        <v>-568.652398494248</v>
+        <v>-479.838299919476</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2340070235929227</v>
+        <v>0.2330886131880225</v>
       </c>
       <c r="T89">
-        <v>3.867725262272181</v>
+        <v>3.850851011826617</v>
       </c>
       <c r="U89">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V89">
-        <v>0.06460635047076095</v>
+        <v>0.0693392374231145</v>
       </c>
       <c r="W89">
-        <v>0.2055599985856257</v>
+        <v>0.1905599985856257</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3230317523538048</v>
+        <v>0.3466961871155725</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2109976892809912</v>
+        <v>0.1976782959283542</v>
       </c>
       <c r="C90">
-        <v>-5384.488458004525</v>
+        <v>-5227.478636267069</v>
       </c>
       <c r="D90">
-        <v>2009.957398872793</v>
+        <v>2166.967220610249</v>
       </c>
       <c r="E90">
         <v>5925.848292244001</v>
@@ -8673,37 +8673,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M90">
-        <v>1645.160503843302</v>
+        <v>1532.866815990142</v>
       </c>
       <c r="N90">
-        <v>-1119.760503843302</v>
+        <v>-1007.466815990142</v>
       </c>
       <c r="O90">
-        <v>-223.9521007686604</v>
+        <v>-201.4933631980284</v>
       </c>
       <c r="P90">
-        <v>-895.8084030746415</v>
+        <v>-805.9734527921137</v>
       </c>
       <c r="Q90">
-        <v>-583.6084030746415</v>
+        <v>-493.7734527921137</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2496909422256663</v>
+        <v>0.2486959976203578</v>
       </c>
       <c r="T90">
-        <v>4.190035700794863</v>
+        <v>4.171755262812169</v>
       </c>
       <c r="U90">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V90">
-        <v>0.06387218739722959</v>
+        <v>0.06855129154330639</v>
       </c>
       <c r="W90">
-        <v>0.2057213366067173</v>
+        <v>0.1907213366067173</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3193609369861479</v>
+        <v>0.342756457716532</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2127372667254081</v>
+        <v>0.1992678733727711</v>
       </c>
       <c r="C91">
-        <v>-5488.421910581649</v>
+        <v>-5332.586641980335</v>
       </c>
       <c r="D91">
-        <v>1991.094921942003</v>
+        <v>2146.930190543317</v>
       </c>
       <c r="E91">
         <v>6010.919267890334</v>
@@ -8755,37 +8755,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M91">
-        <v>1663.855509568794</v>
+        <v>1550.285757080939</v>
       </c>
       <c r="N91">
-        <v>-1138.455509568794</v>
+        <v>-1024.885757080939</v>
       </c>
       <c r="O91">
-        <v>-227.6911019137588</v>
+        <v>-204.9771514161878</v>
       </c>
       <c r="P91">
-        <v>-910.7644076550353</v>
+        <v>-819.9086056647513</v>
       </c>
       <c r="Q91">
-        <v>-598.5644076550352</v>
+        <v>-507.7086056647514</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2682264824279996</v>
+        <v>0.2671410883131176</v>
       </c>
       <c r="T91">
-        <v>4.57094803723076</v>
+        <v>4.55100574124964</v>
       </c>
       <c r="U91">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V91">
-        <v>0.06315452237029442</v>
+        <v>0.06778105231248271</v>
       </c>
       <c r="W91">
-        <v>0.2058790490543013</v>
+        <v>0.1908790490543013</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3157726118514721</v>
+        <v>0.3389052615624136</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.214476844169825</v>
+        <v>0.2008574508171879</v>
       </c>
       <c r="C92">
-        <v>-5592.004624248722</v>
+        <v>-5437.327494704502</v>
       </c>
       <c r="D92">
-        <v>1972.583183921264</v>
+        <v>2127.260313465484</v>
       </c>
       <c r="E92">
         <v>6095.990243536668</v>
@@ -8837,37 +8837,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M92">
-        <v>1682.550515294286</v>
+        <v>1567.704698171736</v>
       </c>
       <c r="N92">
-        <v>-1157.150515294286</v>
+        <v>-1042.304698171736</v>
       </c>
       <c r="O92">
-        <v>-231.4301030588572</v>
+        <v>-208.4609396343473</v>
       </c>
       <c r="P92">
-        <v>-925.720412235429</v>
+        <v>-833.8437585373891</v>
       </c>
       <c r="Q92">
-        <v>-613.5204122354289</v>
+        <v>-521.6437585373892</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2904691306707995</v>
+        <v>0.2892751971444294</v>
       </c>
       <c r="T92">
-        <v>5.028042840953836</v>
+        <v>5.006106315374605</v>
       </c>
       <c r="U92">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V92">
-        <v>0.06245280545506892</v>
+        <v>0.06702792950901068</v>
       </c>
       <c r="W92">
-        <v>0.2060332567808278</v>
+        <v>0.1910332567808278</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3122640272753446</v>
+        <v>0.3351396475450534</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2162164216142419</v>
+        <v>0.2024470282616048</v>
       </c>
       <c r="C93">
-        <v>-5695.246291629099</v>
+        <v>-5541.711194237327</v>
       </c>
       <c r="D93">
-        <v>1954.41249218722</v>
+        <v>2107.947589578992</v>
       </c>
       <c r="E93">
         <v>6181.061219183001</v>
@@ -8919,37 +8919,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M93">
-        <v>1701.245521019778</v>
+        <v>1585.123639262534</v>
       </c>
       <c r="N93">
-        <v>-1175.845521019778</v>
+        <v>-1059.723639262533</v>
       </c>
       <c r="O93">
-        <v>-235.1691042039557</v>
+        <v>-211.9447278525067</v>
       </c>
       <c r="P93">
-        <v>-940.6764168158227</v>
+        <v>-847.7789114100267</v>
       </c>
       <c r="Q93">
-        <v>-628.4764168158226</v>
+        <v>-535.5789114100266</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3176545896342218</v>
+        <v>0.3163279968271437</v>
       </c>
       <c r="T93">
-        <v>5.586714267726485</v>
+        <v>5.562340350416227</v>
       </c>
       <c r="U93">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V93">
-        <v>0.0617665108896286</v>
+        <v>0.06629135885506551</v>
       </c>
       <c r="W93">
-        <v>0.2061840753265516</v>
+        <v>0.1911840753265516</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3088325544481429</v>
+        <v>0.3314567942753276</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2179559990586588</v>
+        <v>0.2040366057060218</v>
       </c>
       <c r="C94">
-        <v>-5798.156251466792</v>
+        <v>-5645.747380503724</v>
       </c>
       <c r="D94">
-        <v>1936.57350799586</v>
+        <v>2088.982378958927</v>
       </c>
       <c r="E94">
         <v>6266.132194829333</v>
@@ -9001,37 +9001,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M94">
-        <v>1719.94052674527</v>
+        <v>1602.542580353331</v>
       </c>
       <c r="N94">
-        <v>-1194.54052674527</v>
+        <v>-1077.14258035333</v>
       </c>
       <c r="O94">
-        <v>-238.908105349054</v>
+        <v>-215.4285160706661</v>
       </c>
       <c r="P94">
-        <v>-955.6324213962162</v>
+        <v>-861.7140642826644</v>
       </c>
       <c r="Q94">
-        <v>-643.4324213962161</v>
+        <v>-549.5140642826643</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3516364133384996</v>
+        <v>0.3501439964305369</v>
       </c>
       <c r="T94">
-        <v>6.285053551192298</v>
+        <v>6.257632894218259</v>
       </c>
       <c r="U94">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V94">
-        <v>0.06109513577126308</v>
+        <v>0.06557080060664089</v>
       </c>
       <c r="W94">
-        <v>0.2063316152082379</v>
+        <v>0.1913316152082379</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3054756788563153</v>
+        <v>0.3278540030332044</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2196955765030757</v>
+        <v>0.2056261831504387</v>
       </c>
       <c r="C95">
-        <v>-5900.743504630623</v>
+        <v>-5749.445349600309</v>
       </c>
       <c r="D95">
-        <v>1919.057230478363</v>
+        <v>2070.355385508677</v>
       </c>
       <c r="E95">
         <v>6351.203170475667</v>
@@ -9083,37 +9083,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M95">
-        <v>1738.635532470763</v>
+        <v>1619.961521444128</v>
       </c>
       <c r="N95">
-        <v>-1213.235532470763</v>
+        <v>-1094.561521444127</v>
       </c>
       <c r="O95">
-        <v>-242.6471064941525</v>
+        <v>-218.9123042888255</v>
       </c>
       <c r="P95">
-        <v>-970.5884259766101</v>
+        <v>-875.649217155302</v>
       </c>
       <c r="Q95">
-        <v>-658.3884259766101</v>
+        <v>-563.449217155302</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3953273295297139</v>
+        <v>0.3936217102063279</v>
       </c>
       <c r="T95">
-        <v>7.18291834421977</v>
+        <v>7.151580450535153</v>
       </c>
       <c r="U95">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V95">
-        <v>0.06043819882748605</v>
+        <v>0.06486573823452647</v>
       </c>
       <c r="W95">
-        <v>0.2064759821892427</v>
+        <v>0.1914759821892427</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3021909941374302</v>
+        <v>0.3243286911726323</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2214351539474926</v>
+        <v>0.2072157605948556</v>
       </c>
       <c r="C96">
-        <v>-6003.016729257643</v>
+        <v>-5852.814068989106</v>
       </c>
       <c r="D96">
-        <v>1901.854981497676</v>
+        <v>2052.057641766212</v>
       </c>
       <c r="E96">
         <v>6436.274146122</v>
@@ -9165,37 +9165,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M96">
-        <v>1757.330538196255</v>
+        <v>1637.380462534925</v>
       </c>
       <c r="N96">
-        <v>-1231.930538196254</v>
+        <v>-1111.980462534925</v>
       </c>
       <c r="O96">
-        <v>-246.3861076392509</v>
+        <v>-222.3960925069849</v>
       </c>
       <c r="P96">
-        <v>-985.5444305570036</v>
+        <v>-889.5843700279396</v>
       </c>
       <c r="Q96">
-        <v>-673.3444305570035</v>
+        <v>-577.3843700279397</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4535818844513329</v>
+        <v>0.4515919952407159</v>
       </c>
       <c r="T96">
-        <v>8.380071401589733</v>
+        <v>8.343510525624346</v>
       </c>
       <c r="U96">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V96">
-        <v>0.05979523926549152</v>
+        <v>0.06417567718947832</v>
       </c>
       <c r="W96">
-        <v>0.2066172775323539</v>
+        <v>0.1916172775323538</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2989761963274575</v>
+        <v>0.3208783859473916</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2231747313919095</v>
+        <v>0.2088053380392724</v>
       </c>
       <c r="C97">
-        <v>-6104.984295089309</v>
+        <v>-5955.862191892662</v>
       </c>
       <c r="D97">
-        <v>1884.958391312343</v>
+        <v>2034.08049450899</v>
       </c>
       <c r="E97">
         <v>6521.345121768333</v>
@@ -9247,37 +9247,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M97">
-        <v>1776.025543921747</v>
+        <v>1654.799403625722</v>
       </c>
       <c r="N97">
-        <v>-1250.625543921747</v>
+        <v>-1129.399403625722</v>
       </c>
       <c r="O97">
-        <v>-250.1251087843493</v>
+        <v>-225.8798807251443</v>
       </c>
       <c r="P97">
-        <v>-1000.500435137397</v>
+        <v>-903.5195229005773</v>
       </c>
       <c r="Q97">
-        <v>-688.3004351373972</v>
+        <v>-591.3195229005773</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5351382613415997</v>
+        <v>0.5327503942888593</v>
       </c>
       <c r="T97">
-        <v>10.05608568190769</v>
+        <v>10.01221263074922</v>
       </c>
       <c r="U97">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V97">
-        <v>0.05916581569427581</v>
+        <v>0.06350014374537855</v>
       </c>
       <c r="W97">
-        <v>0.2067555982366626</v>
+        <v>0.1917555982366626</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2958290784713791</v>
+        <v>0.3175007187268928</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2249143088363263</v>
+        <v>0.2103949154836893</v>
       </c>
       <c r="C98">
-        <v>-6206.654277050186</v>
+        <v>-6058.598070939039</v>
       </c>
       <c r="D98">
-        <v>1868.359384997799</v>
+        <v>2016.415591108946</v>
       </c>
       <c r="E98">
         <v>6606.416097414666</v>
@@ -9329,37 +9329,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M98">
-        <v>1794.720549647239</v>
+        <v>1672.218344716519</v>
       </c>
       <c r="N98">
-        <v>-1269.320549647239</v>
+        <v>-1146.818344716519</v>
       </c>
       <c r="O98">
-        <v>-253.8641099294477</v>
+        <v>-229.3636689433037</v>
       </c>
       <c r="P98">
-        <v>-1015.456439717791</v>
+        <v>-917.4546757732148</v>
       </c>
       <c r="Q98">
-        <v>-703.2564397177907</v>
+        <v>-605.2546757732148</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6574728266769981</v>
+        <v>0.6544879928610727</v>
       </c>
       <c r="T98">
-        <v>12.57010710238458</v>
+        <v>12.5152657884365</v>
       </c>
       <c r="U98">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V98">
-        <v>0.05854950511412711</v>
+        <v>0.06283868391469753</v>
       </c>
       <c r="W98">
-        <v>0.2068910372596317</v>
+        <v>0.1918910372596317</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2927475255706355</v>
+        <v>0.3141934195734876</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2266538862807433</v>
+        <v>0.2119844929281062</v>
       </c>
       <c r="C99">
-        <v>-6308.034468115478</v>
+        <v>-6161.029771101965</v>
       </c>
       <c r="D99">
-        <v>1852.05016957884</v>
+        <v>1999.054866592354</v>
       </c>
       <c r="E99">
         <v>6691.487073061</v>
@@ -9411,37 +9411,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M99">
-        <v>1813.415555372731</v>
+        <v>1689.637285807316</v>
       </c>
       <c r="N99">
-        <v>-1288.015555372731</v>
+        <v>-1164.237285807316</v>
       </c>
       <c r="O99">
-        <v>-257.6031110745461</v>
+        <v>-232.8474571614632</v>
       </c>
       <c r="P99">
-        <v>-1030.412444298184</v>
+        <v>-931.3898286458527</v>
       </c>
       <c r="Q99">
-        <v>-718.2124442981844</v>
+        <v>-619.1898286458527</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.8613637689026644</v>
+        <v>0.8573839904814303</v>
       </c>
       <c r="T99">
-        <v>16.76014280317944</v>
+        <v>16.68702105124866</v>
       </c>
       <c r="U99">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V99">
-        <v>0.05794590196862065</v>
+        <v>0.06219086243104084</v>
       </c>
       <c r="W99">
-        <v>0.2070236837254261</v>
+        <v>0.1920236837254261</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2897295098431032</v>
+        <v>0.3109543121552042</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2283934637251602</v>
+        <v>0.2135740703725231</v>
       </c>
       <c r="C100">
-        <v>-6409.132391510455</v>
+        <v>-6263.165081978195</v>
       </c>
       <c r="D100">
-        <v>1836.023221830196</v>
+        <v>1981.990531362456</v>
       </c>
       <c r="E100">
         <v>6776.558048707333</v>
@@ -9493,37 +9493,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M100">
-        <v>1832.110561098223</v>
+        <v>1707.056226898113</v>
       </c>
       <c r="N100">
-        <v>-1306.710561098223</v>
+        <v>-1181.656226898113</v>
       </c>
       <c r="O100">
-        <v>-261.3421122196445</v>
+        <v>-236.3312453796226</v>
       </c>
       <c r="P100">
-        <v>-1045.368448878578</v>
+        <v>-945.3249815184903</v>
       </c>
       <c r="Q100">
-        <v>-733.1684488785781</v>
+        <v>-633.1249815184904</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.269145653353997</v>
+        <v>1.263175985722146</v>
       </c>
       <c r="T100">
-        <v>25.14021420476915</v>
+        <v>25.030531576873</v>
       </c>
       <c r="U100">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V100">
-        <v>0.05735461725465513</v>
+        <v>0.06155626179398941</v>
       </c>
       <c r="W100">
-        <v>0.20715362312049</v>
+        <v>0.19215362312049</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2867730862732756</v>
+        <v>0.307781308969947</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.230133041169577</v>
+        <v>0.21516364781694</v>
       </c>
       <c r="C101">
-        <v>-6509.955312281869</v>
+        <v>-6365.011529441415</v>
       </c>
       <c r="D101">
-        <v>1820.271276705115</v>
+        <v>1965.215059545569</v>
       </c>
       <c r="E101">
         <v>6861.629024353666</v>
@@ -9575,37 +9575,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M101">
-        <v>1850.805566823715</v>
+        <v>1724.47516798891</v>
       </c>
       <c r="N101">
-        <v>-1325.405566823715</v>
+        <v>-1199.07516798891</v>
       </c>
       <c r="O101">
-        <v>-265.081113364743</v>
+        <v>-239.815033597782</v>
       </c>
       <c r="P101">
-        <v>-1060.324453458972</v>
+        <v>-959.260134391128</v>
       </c>
       <c r="Q101">
-        <v>-748.1244534589716</v>
+        <v>-647.060134391128</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.492491306707993</v>
+        <v>2.480551971444291</v>
       </c>
       <c r="T101">
-        <v>50.2804284095383</v>
+        <v>50.06106315374599</v>
       </c>
       <c r="U101">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V101">
-        <v>0.0567752776864263</v>
+        <v>0.0609344813718279</v>
       </c>
       <c r="W101">
-        <v>0.2072809374772698</v>
+        <v>0.1922809374772698</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2838763884321315</v>
+        <v>0.3046724068591394</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/finland/finland_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_telecom_services.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07171057892648268</v>
+        <v>0.07163481972416322</v>
       </c>
       <c r="C2">
-        <v>8413.273980742724</v>
+        <v>8342.441358387407</v>
       </c>
       <c r="D2">
-        <v>8321.473980742725</v>
+        <v>8335.71233403374</v>
       </c>
       <c r="E2">
-        <v>-1560.397564633318</v>
+        <v>-1475.326588986985</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>85.07097564633317</v>
       </c>
       <c r="G2">
         <v>91.8</v>
@@ -1457,28 +1457,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.615759256023928</v>
       </c>
       <c r="N2">
-        <v>525.4000000000001</v>
+        <v>520.7842407439762</v>
       </c>
       <c r="O2">
-        <v>105.08</v>
+        <v>104.1568481487952</v>
       </c>
       <c r="P2">
-        <v>420.3200000000001</v>
+        <v>416.6273925951809</v>
       </c>
       <c r="Q2">
-        <v>732.52</v>
+        <v>728.827392595181</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07171057892648268</v>
+        <v>0.07191995734205021</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5370538146839923</v>
       </c>
       <c r="U2">
         <v>0.0542577444416894</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>113.827427050991</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07163481972416322</v>
+        <v>0.07155906052184377</v>
       </c>
       <c r="C3">
-        <v>8342.441358387407</v>
+        <v>8271.657544255067</v>
       </c>
       <c r="D3">
-        <v>8335.71233403374</v>
+        <v>8349.999495547734</v>
       </c>
       <c r="E3">
-        <v>-1475.326588986985</v>
+        <v>-1390.255613340652</v>
       </c>
       <c r="F3">
-        <v>85.07097564633317</v>
+        <v>170.1419512926663</v>
       </c>
       <c r="G3">
         <v>91.8</v>
@@ -1539,28 +1539,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M3">
-        <v>4.615759256023928</v>
+        <v>9.231518512047856</v>
       </c>
       <c r="N3">
-        <v>520.7842407439762</v>
+        <v>516.1684814879522</v>
       </c>
       <c r="O3">
-        <v>104.1568481487952</v>
+        <v>103.2336962975905</v>
       </c>
       <c r="P3">
-        <v>416.6273925951809</v>
+        <v>412.9347851903618</v>
       </c>
       <c r="Q3">
-        <v>728.827392595181</v>
+        <v>725.1347851903618</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07191995734205021</v>
+        <v>0.07213360878650689</v>
       </c>
       <c r="T3">
-        <v>0.5370538146839923</v>
+        <v>0.5414467132540629</v>
       </c>
       <c r="U3">
         <v>0.0542577444416894</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>113.827427050991</v>
+        <v>56.9137135254955</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07155906052184377</v>
+        <v>0.07148330131952432</v>
       </c>
       <c r="C4">
-        <v>8271.657544255067</v>
+        <v>8200.922789744103</v>
       </c>
       <c r="D4">
-        <v>8349.999495547734</v>
+        <v>8364.335716683103</v>
       </c>
       <c r="E4">
-        <v>-1390.255613340652</v>
+        <v>-1305.184637694319</v>
       </c>
       <c r="F4">
-        <v>170.1419512926663</v>
+        <v>255.2129269389995</v>
       </c>
       <c r="G4">
         <v>91.8</v>
@@ -1621,28 +1621,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M4">
-        <v>9.231518512047856</v>
+        <v>13.84727776807179</v>
       </c>
       <c r="N4">
-        <v>516.1684814879522</v>
+        <v>511.5527222319283</v>
       </c>
       <c r="O4">
-        <v>103.2336962975905</v>
+        <v>102.3105444463857</v>
       </c>
       <c r="P4">
-        <v>412.9347851903618</v>
+        <v>409.2421777855427</v>
       </c>
       <c r="Q4">
-        <v>725.1347851903618</v>
+        <v>721.4421777855426</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07213360878650689</v>
+        <v>0.07235166541538533</v>
       </c>
       <c r="T4">
-        <v>0.5414467132540629</v>
+        <v>0.5459301870523824</v>
       </c>
       <c r="U4">
         <v>0.0542577444416894</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>56.9137135254955</v>
+        <v>37.94247568366366</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07148330131952432</v>
+        <v>0.07140754211720488</v>
       </c>
       <c r="C5">
-        <v>8200.922789744103</v>
+        <v>8130.237347982388</v>
       </c>
       <c r="D5">
-        <v>8364.335716683103</v>
+        <v>8378.721250567722</v>
       </c>
       <c r="E5">
-        <v>-1305.184637694319</v>
+        <v>-1220.113662047986</v>
       </c>
       <c r="F5">
-        <v>255.2129269389995</v>
+        <v>340.2839025853327</v>
       </c>
       <c r="G5">
         <v>91.8</v>
@@ -1703,28 +1703,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M5">
-        <v>13.84727776807179</v>
+        <v>18.46303702409571</v>
       </c>
       <c r="N5">
-        <v>511.5527222319283</v>
+        <v>506.9369629759044</v>
       </c>
       <c r="O5">
-        <v>102.3105444463857</v>
+        <v>101.3873925951809</v>
       </c>
       <c r="P5">
-        <v>409.2421777855427</v>
+        <v>405.5495703807235</v>
       </c>
       <c r="Q5">
-        <v>721.4421777855426</v>
+        <v>717.7495703807235</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07235166541538533</v>
+        <v>0.07257426489069876</v>
       </c>
       <c r="T5">
-        <v>0.5459301870523824</v>
+        <v>0.5505070665548337</v>
       </c>
       <c r="U5">
         <v>0.0542577444416894</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>37.94247568366366</v>
+        <v>28.45685676274775</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07140754211720488</v>
+        <v>0.07133178291488543</v>
       </c>
       <c r="C6">
-        <v>8130.237347982388</v>
+        <v>8059.601473842185</v>
       </c>
       <c r="D6">
-        <v>8378.721250567722</v>
+        <v>8393.156352073851</v>
       </c>
       <c r="E6">
-        <v>-1220.113662047986</v>
+        <v>-1135.042686401652</v>
       </c>
       <c r="F6">
-        <v>340.2839025853327</v>
+        <v>425.3548782316659</v>
       </c>
       <c r="G6">
         <v>91.8</v>
@@ -1785,28 +1785,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M6">
-        <v>18.46303702409571</v>
+        <v>23.07879628011964</v>
       </c>
       <c r="N6">
-        <v>506.9369629759044</v>
+        <v>502.3212037198804</v>
       </c>
       <c r="O6">
-        <v>101.3873925951809</v>
+        <v>100.4642407439761</v>
       </c>
       <c r="P6">
-        <v>405.5495703807235</v>
+        <v>401.8569629759044</v>
       </c>
       <c r="Q6">
-        <v>717.7495703807235</v>
+        <v>714.0569629759043</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07257426489069876</v>
+        <v>0.07280155067075564</v>
       </c>
       <c r="T6">
-        <v>0.5505070665548337</v>
+        <v>0.5551803014152312</v>
       </c>
       <c r="U6">
         <v>0.0542577444416894</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>28.45685676274775</v>
+        <v>22.76548541019819</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07133178291488543</v>
+        <v>0.07125602371256598</v>
       </c>
       <c r="C7">
-        <v>8059.601473842185</v>
+        <v>7989.015423955187</v>
       </c>
       <c r="D7">
-        <v>8393.156352073851</v>
+        <v>8407.641277833187</v>
       </c>
       <c r="E7">
-        <v>-1135.042686401652</v>
+        <v>-1049.971710755319</v>
       </c>
       <c r="F7">
-        <v>425.3548782316659</v>
+        <v>510.4258538779991</v>
       </c>
       <c r="G7">
         <v>91.8</v>
@@ -1867,28 +1867,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M7">
-        <v>23.07879628011964</v>
+        <v>27.69455553614357</v>
       </c>
       <c r="N7">
-        <v>502.3212037198804</v>
+        <v>497.7054444638565</v>
       </c>
       <c r="O7">
-        <v>100.4642407439761</v>
+        <v>99.54108889277131</v>
       </c>
       <c r="P7">
-        <v>401.8569629759044</v>
+        <v>398.1643555710852</v>
       </c>
       <c r="Q7">
-        <v>714.0569629759043</v>
+        <v>710.3643555710852</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07280155067075564</v>
+        <v>0.07303367231847328</v>
       </c>
       <c r="T7">
-        <v>0.5551803014152312</v>
+        <v>0.5599529668045735</v>
       </c>
       <c r="U7">
         <v>0.0542577444416894</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.76548541019819</v>
+        <v>18.97123784183183</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07125602371256598</v>
+        <v>0.07118026451024653</v>
       </c>
       <c r="C8">
-        <v>7989.015423955188</v>
+        <v>7918.479456727739</v>
       </c>
       <c r="D8">
-        <v>8407.641277833187</v>
+        <v>8422.176286252072</v>
       </c>
       <c r="E8">
-        <v>-1049.971710755319</v>
+        <v>-964.9007351089862</v>
       </c>
       <c r="F8">
-        <v>510.425853877999</v>
+        <v>595.4968295243322</v>
       </c>
       <c r="G8">
         <v>91.8</v>
@@ -1949,28 +1949,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M8">
-        <v>27.69455553614357</v>
+        <v>32.3103147921675</v>
       </c>
       <c r="N8">
-        <v>497.7054444638565</v>
+        <v>493.0896852078326</v>
       </c>
       <c r="O8">
-        <v>99.54108889277131</v>
+        <v>98.61793704156652</v>
       </c>
       <c r="P8">
-        <v>398.1643555710852</v>
+        <v>394.4717481662661</v>
       </c>
       <c r="Q8">
-        <v>710.3643555710852</v>
+        <v>706.6717481662661</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07303367231847328</v>
+        <v>0.07327078582958271</v>
       </c>
       <c r="T8">
-        <v>0.5599529668045735</v>
+        <v>0.5648282701592779</v>
       </c>
       <c r="U8">
         <v>0.0542577444416894</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.97123784183183</v>
+        <v>16.26106100728443</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07118026451024652</v>
+        <v>0.07110450530792707</v>
       </c>
       <c r="C9">
-        <v>7918.479456727742</v>
+        <v>7847.993832356191</v>
       </c>
       <c r="D9">
-        <v>8422.176286252075</v>
+        <v>8436.761637526857</v>
       </c>
       <c r="E9">
-        <v>-964.9007351089861</v>
+        <v>-879.829759462653</v>
       </c>
       <c r="F9">
-        <v>595.4968295243323</v>
+        <v>680.5678051706653</v>
       </c>
       <c r="G9">
         <v>91.8</v>
@@ -2031,28 +2031,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M9">
-        <v>32.3103147921675</v>
+        <v>36.92607404819142</v>
       </c>
       <c r="N9">
-        <v>493.0896852078326</v>
+        <v>488.4739259518087</v>
       </c>
       <c r="O9">
-        <v>98.61793704156652</v>
+        <v>97.69478519036174</v>
       </c>
       <c r="P9">
-        <v>394.4717481662661</v>
+        <v>390.7791407614469</v>
       </c>
       <c r="Q9">
-        <v>706.6717481662661</v>
+        <v>702.9791407614468</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07327078582958271</v>
+        <v>0.07351305398223799</v>
       </c>
       <c r="T9">
-        <v>0.5648282701592779</v>
+        <v>0.5698095583695193</v>
       </c>
       <c r="U9">
         <v>0.0542577444416894</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.26106100728443</v>
+        <v>14.22842838137387</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07110450530792707</v>
+        <v>0.07102874610560764</v>
       </c>
       <c r="C10">
-        <v>7847.993832356191</v>
+        <v>7777.55881284243</v>
       </c>
       <c r="D10">
-        <v>8436.761637526857</v>
+        <v>8451.397593659429</v>
       </c>
       <c r="E10">
-        <v>-879.829759462653</v>
+        <v>-794.7587838163198</v>
       </c>
       <c r="F10">
-        <v>680.5678051706653</v>
+        <v>765.6387808169985</v>
       </c>
       <c r="G10">
         <v>91.8</v>
@@ -2113,28 +2113,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M10">
-        <v>36.92607404819142</v>
+        <v>41.54183330421535</v>
       </c>
       <c r="N10">
-        <v>488.4739259518087</v>
+        <v>483.8581666957847</v>
       </c>
       <c r="O10">
-        <v>97.69478519036174</v>
+        <v>96.77163333915695</v>
       </c>
       <c r="P10">
-        <v>390.7791407614469</v>
+        <v>387.0865333566278</v>
       </c>
       <c r="Q10">
-        <v>702.9791407614468</v>
+        <v>699.2865333566278</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07351305398223799</v>
+        <v>0.07376064670967691</v>
       </c>
       <c r="T10">
-        <v>0.5698095583695193</v>
+        <v>0.5749003254415243</v>
       </c>
       <c r="U10">
         <v>0.0542577444416894</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.22842838137387</v>
+        <v>12.64749189455455</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07102874610560764</v>
+        <v>0.07095298690328818</v>
       </c>
       <c r="C11">
-        <v>7777.55881284243</v>
+        <v>7707.174662009576</v>
       </c>
       <c r="D11">
-        <v>8451.397593659429</v>
+        <v>8466.084418472909</v>
       </c>
       <c r="E11">
-        <v>-794.7587838163198</v>
+        <v>-709.6878081699866</v>
       </c>
       <c r="F11">
-        <v>765.6387808169985</v>
+        <v>850.7097564633317</v>
       </c>
       <c r="G11">
         <v>91.8</v>
@@ -2195,28 +2195,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M11">
-        <v>41.54183330421535</v>
+        <v>46.15759256023928</v>
       </c>
       <c r="N11">
-        <v>483.8581666957847</v>
+        <v>479.2424074397608</v>
       </c>
       <c r="O11">
-        <v>96.77163333915695</v>
+        <v>95.84848148795217</v>
       </c>
       <c r="P11">
-        <v>387.0865333566278</v>
+        <v>383.3939259518087</v>
       </c>
       <c r="Q11">
-        <v>699.2865333566278</v>
+        <v>695.5939259518086</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07376064670967691</v>
+        <v>0.07401374149772558</v>
       </c>
       <c r="T11">
-        <v>0.5749003254415243</v>
+        <v>0.5801042206706849</v>
       </c>
       <c r="U11">
         <v>0.0542577444416894</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.64749189455455</v>
+        <v>11.3827427050991</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07095298690328818</v>
+        <v>0.07087722770096873</v>
       </c>
       <c r="C12">
-        <v>7707.174662009576</v>
+        <v>7636.841645517822</v>
       </c>
       <c r="D12">
-        <v>8466.084418472909</v>
+        <v>8480.822377627488</v>
       </c>
       <c r="E12">
-        <v>-709.6878081699865</v>
+        <v>-624.6168325236534</v>
       </c>
       <c r="F12">
-        <v>850.7097564633318</v>
+        <v>935.7807321096649</v>
       </c>
       <c r="G12">
         <v>91.8</v>
@@ -2277,28 +2277,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M12">
-        <v>46.15759256023929</v>
+        <v>50.77335181626321</v>
       </c>
       <c r="N12">
-        <v>479.2424074397608</v>
+        <v>474.6266481837369</v>
       </c>
       <c r="O12">
-        <v>95.84848148795217</v>
+        <v>94.92532963674739</v>
       </c>
       <c r="P12">
-        <v>383.3939259518087</v>
+        <v>379.7013185469895</v>
       </c>
       <c r="Q12">
-        <v>695.5939259518086</v>
+        <v>691.9013185469895</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07401374149772558</v>
+        <v>0.07427252380910118</v>
       </c>
       <c r="T12">
-        <v>0.580104220670685</v>
+        <v>0.5854250573656694</v>
       </c>
       <c r="U12">
         <v>0.0542577444416894</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.3827427050991</v>
+        <v>10.34794791372645</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07087722770096873</v>
+        <v>0.07080146849864928</v>
       </c>
       <c r="C13">
-        <v>7636.841645517822</v>
+        <v>7566.560030880454</v>
       </c>
       <c r="D13">
-        <v>8480.822377627488</v>
+        <v>8495.611738636453</v>
       </c>
       <c r="E13">
-        <v>-624.6168325236534</v>
+        <v>-539.5458568773203</v>
       </c>
       <c r="F13">
-        <v>935.7807321096649</v>
+        <v>1020.851707755998</v>
       </c>
       <c r="G13">
         <v>91.8</v>
@@ -2359,28 +2359,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M13">
-        <v>50.77335181626321</v>
+        <v>55.38911107228714</v>
       </c>
       <c r="N13">
-        <v>474.6266481837369</v>
+        <v>470.0108889277129</v>
       </c>
       <c r="O13">
-        <v>94.92532963674739</v>
+        <v>94.00217778554259</v>
       </c>
       <c r="P13">
-        <v>379.7013185469895</v>
+        <v>376.0087111421703</v>
       </c>
       <c r="Q13">
-        <v>691.9013185469895</v>
+        <v>688.2087111421704</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07427252380910118</v>
+        <v>0.07453718753664443</v>
       </c>
       <c r="T13">
-        <v>0.5854250573656694</v>
+        <v>0.5908668221673582</v>
       </c>
       <c r="U13">
         <v>0.0542577444416894</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.34794791372645</v>
+        <v>9.485618920915915</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07080146849864928</v>
+        <v>0.07072570929632982</v>
       </c>
       <c r="C14">
-        <v>7566.560030880454</v>
+        <v>7496.330087480047</v>
       </c>
       <c r="D14">
-        <v>8495.611738636453</v>
+        <v>8510.452770882379</v>
       </c>
       <c r="E14">
-        <v>-539.5458568773203</v>
+        <v>-454.474881230987</v>
       </c>
       <c r="F14">
-        <v>1020.851707755998</v>
+        <v>1105.922683402331</v>
       </c>
       <c r="G14">
         <v>91.8</v>
@@ -2441,28 +2441,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M14">
-        <v>55.38911107228714</v>
+        <v>60.00487032831107</v>
       </c>
       <c r="N14">
-        <v>470.0108889277129</v>
+        <v>465.395129671689</v>
       </c>
       <c r="O14">
-        <v>94.00217778554259</v>
+        <v>93.07902593433781</v>
       </c>
       <c r="P14">
-        <v>376.0087111421703</v>
+        <v>372.3161037373512</v>
       </c>
       <c r="Q14">
-        <v>688.2087111421704</v>
+        <v>684.5161037373512</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07453718753664443</v>
+        <v>0.07480793548780934</v>
       </c>
       <c r="T14">
-        <v>0.5908668221673582</v>
+        <v>0.596433685010465</v>
       </c>
       <c r="U14">
         <v>0.0542577444416894</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.485618920915915</v>
+        <v>8.755955926999306</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07072570929632982</v>
+        <v>0.07081795009401037</v>
       </c>
       <c r="C15">
-        <v>7496.330087480047</v>
+        <v>7393.196230295174</v>
       </c>
       <c r="D15">
-        <v>8510.452770882379</v>
+        <v>8492.38988934384</v>
       </c>
       <c r="E15">
-        <v>-454.474881230987</v>
+        <v>-369.4039055846538</v>
       </c>
       <c r="F15">
-        <v>1105.922683402331</v>
+        <v>1190.993659048665</v>
       </c>
       <c r="G15">
         <v>91.8</v>
@@ -2523,45 +2523,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M15">
-        <v>60.00487032831107</v>
+        <v>66.407120072908</v>
       </c>
       <c r="N15">
-        <v>465.395129671689</v>
+        <v>458.9928799270921</v>
       </c>
       <c r="O15">
-        <v>93.07902593433781</v>
+        <v>91.79857598541842</v>
       </c>
       <c r="P15">
-        <v>372.3161037373512</v>
+        <v>367.1943039416736</v>
       </c>
       <c r="Q15">
-        <v>684.5161037373512</v>
+        <v>679.3943039416736</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07480793548780934</v>
+        <v>0.07508497990295485</v>
       </c>
       <c r="T15">
-        <v>0.596433685010465</v>
+        <v>0.6021300097801557</v>
       </c>
       <c r="U15">
-        <v>0.0542577444416894</v>
+        <v>0.0557577444416894</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04340619555335153</v>
+        <v>0.04460619555335152</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>8.755955926999306</v>
+        <v>7.911802219749425</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07081795009401037</v>
+        <v>0.07075419089169094</v>
       </c>
       <c r="C16">
-        <v>7393.196230295174</v>
+        <v>7320.602586635501</v>
       </c>
       <c r="D16">
-        <v>8492.38988934384</v>
+        <v>8504.8672213305</v>
       </c>
       <c r="E16">
-        <v>-369.4039055846538</v>
+        <v>-284.3329299383206</v>
       </c>
       <c r="F16">
-        <v>1190.993659048665</v>
+        <v>1276.064634694998</v>
       </c>
       <c r="G16">
         <v>91.8</v>
@@ -2605,28 +2605,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M16">
-        <v>66.407120072908</v>
+        <v>71.15048579240143</v>
       </c>
       <c r="N16">
-        <v>458.9928799270921</v>
+        <v>454.2495142075987</v>
       </c>
       <c r="O16">
-        <v>91.79857598541842</v>
+        <v>90.84990284151974</v>
       </c>
       <c r="P16">
-        <v>367.1943039416736</v>
+        <v>363.3996113660789</v>
       </c>
       <c r="Q16">
-        <v>679.3943039416736</v>
+        <v>675.599611366079</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07508497990295485</v>
+        <v>0.07536854301022142</v>
       </c>
       <c r="T16">
-        <v>0.6021300097801557</v>
+        <v>0.607960365720898</v>
       </c>
       <c r="U16">
         <v>0.0557577444416894</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.911802219749425</v>
+        <v>7.384348738432797</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07075419089169094</v>
+        <v>0.07069043168937147</v>
       </c>
       <c r="C17">
-        <v>7320.602586635501</v>
+        <v>7248.045661235004</v>
       </c>
       <c r="D17">
-        <v>8504.8672213305</v>
+        <v>8517.381271576336</v>
       </c>
       <c r="E17">
-        <v>-284.3329299383208</v>
+        <v>-199.2619542919876</v>
       </c>
       <c r="F17">
-        <v>1276.064634694997</v>
+        <v>1361.135610341331</v>
       </c>
       <c r="G17">
         <v>91.8</v>
@@ -2687,28 +2687,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M17">
-        <v>71.15048579240141</v>
+        <v>75.89385151189484</v>
       </c>
       <c r="N17">
-        <v>454.2495142075987</v>
+        <v>449.5061484881053</v>
       </c>
       <c r="O17">
-        <v>90.84990284151974</v>
+        <v>89.90122969762106</v>
       </c>
       <c r="P17">
-        <v>363.3996113660789</v>
+        <v>359.6049187904842</v>
       </c>
       <c r="Q17">
-        <v>675.599611366079</v>
+        <v>671.8049187904842</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07536854301022142</v>
+        <v>0.07565885762004194</v>
       </c>
       <c r="T17">
-        <v>0.607960365720898</v>
+        <v>0.6139295396602292</v>
       </c>
       <c r="U17">
         <v>0.0557577444416894</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.384348738432798</v>
+        <v>6.922826942280749</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07069043168937147</v>
+        <v>0.07085787248705203</v>
       </c>
       <c r="C18">
-        <v>7248.045661235004</v>
+        <v>7130.189327658223</v>
       </c>
       <c r="D18">
-        <v>8517.381271576336</v>
+        <v>8484.595913645888</v>
       </c>
       <c r="E18">
-        <v>-199.2619542919876</v>
+        <v>-114.1909786456542</v>
       </c>
       <c r="F18">
-        <v>1361.135610341331</v>
+        <v>1446.206585987664</v>
       </c>
       <c r="G18">
         <v>91.8</v>
@@ -2769,45 +2769,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M18">
-        <v>75.89385151189484</v>
+        <v>83.09576842756731</v>
       </c>
       <c r="N18">
-        <v>449.5061484881053</v>
+        <v>442.3042315724328</v>
       </c>
       <c r="O18">
-        <v>89.90122969762106</v>
+        <v>88.46084631448656</v>
       </c>
       <c r="P18">
-        <v>359.6049187904842</v>
+        <v>353.8433852579462</v>
       </c>
       <c r="Q18">
-        <v>671.8049187904842</v>
+        <v>666.0433852579463</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07565885762004194</v>
+        <v>0.07595616776262924</v>
       </c>
       <c r="T18">
-        <v>0.6139295396602292</v>
+        <v>0.6200425491161711</v>
       </c>
       <c r="U18">
-        <v>0.0557577444416894</v>
+        <v>0.0574577444416894</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04460619555335152</v>
+        <v>0.04596619555335152</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.922826942280749</v>
+        <v>6.322824975834712</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07085787248705203</v>
+        <v>0.07080771328473258</v>
       </c>
       <c r="C19">
-        <v>7130.189327658223</v>
+        <v>7054.913148368292</v>
       </c>
       <c r="D19">
-        <v>8484.595913645888</v>
+        <v>8494.39071000229</v>
       </c>
       <c r="E19">
-        <v>-114.1909786456542</v>
+        <v>-29.12000299932106</v>
       </c>
       <c r="F19">
-        <v>1446.206585987664</v>
+        <v>1531.277561633997</v>
       </c>
       <c r="G19">
         <v>91.8</v>
@@ -2851,28 +2851,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M19">
-        <v>83.09576842756731</v>
+        <v>87.9837548056595</v>
       </c>
       <c r="N19">
-        <v>442.3042315724328</v>
+        <v>437.4162451943406</v>
       </c>
       <c r="O19">
-        <v>88.46084631448656</v>
+        <v>87.48324903886812</v>
       </c>
       <c r="P19">
-        <v>353.8433852579462</v>
+        <v>349.9329961554725</v>
       </c>
       <c r="Q19">
-        <v>666.0433852579463</v>
+        <v>662.1329961554725</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07595616776262924</v>
+        <v>0.07626072937210891</v>
       </c>
       <c r="T19">
-        <v>0.6200425491161711</v>
+        <v>0.6263046563637212</v>
       </c>
       <c r="U19">
         <v>0.0574577444416894</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.322824975834712</v>
+        <v>5.971556921621673</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07080771328473258</v>
+        <v>0.07075755408241313</v>
       </c>
       <c r="C20">
-        <v>7054.913148368292</v>
+        <v>6979.659609854078</v>
       </c>
       <c r="D20">
-        <v>8494.39071000229</v>
+        <v>8504.208147134408</v>
       </c>
       <c r="E20">
-        <v>-29.12000299932129</v>
+        <v>55.95097264701189</v>
       </c>
       <c r="F20">
-        <v>1531.277561633997</v>
+        <v>1616.34853728033</v>
       </c>
       <c r="G20">
         <v>91.8</v>
@@ -2933,28 +2933,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M20">
-        <v>87.98375480565949</v>
+        <v>92.87174118375168</v>
       </c>
       <c r="N20">
-        <v>437.4162451943406</v>
+        <v>432.5282588162484</v>
       </c>
       <c r="O20">
-        <v>87.48324903886812</v>
+        <v>86.50565176324969</v>
       </c>
       <c r="P20">
-        <v>349.9329961554725</v>
+        <v>346.0226070529988</v>
       </c>
       <c r="Q20">
-        <v>662.1329961554725</v>
+        <v>658.2226070529987</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0762607293721089</v>
+        <v>0.07657281102132882</v>
       </c>
       <c r="T20">
-        <v>0.6263046563637211</v>
+        <v>0.6327213835433095</v>
       </c>
       <c r="U20">
         <v>0.0574577444416894</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.971556921621674</v>
+        <v>5.657264452062639</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07075755408241313</v>
+        <v>0.07083539488009367</v>
       </c>
       <c r="C21">
-        <v>6979.659609854078</v>
+        <v>6879.362902030521</v>
       </c>
       <c r="D21">
-        <v>8504.208147134408</v>
+        <v>8488.982414957185</v>
       </c>
       <c r="E21">
-        <v>55.95097264701189</v>
+        <v>141.0219482933453</v>
       </c>
       <c r="F21">
-        <v>1616.34853728033</v>
+        <v>1701.419512926664</v>
       </c>
       <c r="G21">
         <v>91.8</v>
@@ -3015,45 +3015,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M21">
-        <v>92.87174118375168</v>
+        <v>99.12086317218522</v>
       </c>
       <c r="N21">
-        <v>432.5282588162484</v>
+        <v>426.2791368278149</v>
       </c>
       <c r="O21">
-        <v>86.50565176324969</v>
+        <v>85.25582736556298</v>
       </c>
       <c r="P21">
-        <v>346.0226070529988</v>
+        <v>341.0233094622519</v>
       </c>
       <c r="Q21">
-        <v>658.2226070529987</v>
+        <v>653.2233094622518</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07657281102132882</v>
+        <v>0.0768926947117792</v>
       </c>
       <c r="T21">
-        <v>0.6327213835433095</v>
+        <v>0.6392985289023875</v>
       </c>
       <c r="U21">
-        <v>0.0574577444416894</v>
+        <v>0.0582577444416894</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04596619555335152</v>
+        <v>0.04660619555335152</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>5.657264452062639</v>
+        <v>5.300599522497248</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07083539488009367</v>
+        <v>0.07079163567777423</v>
       </c>
       <c r="C22">
-        <v>6879.362902030521</v>
+        <v>6802.844550548966</v>
       </c>
       <c r="D22">
-        <v>8488.982414957185</v>
+        <v>8497.535039121964</v>
       </c>
       <c r="E22">
-        <v>141.0219482933453</v>
+        <v>226.0929239396785</v>
       </c>
       <c r="F22">
-        <v>1701.419512926664</v>
+        <v>1786.490488572997</v>
       </c>
       <c r="G22">
         <v>91.8</v>
@@ -3097,28 +3097,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M22">
-        <v>99.12086317218522</v>
+        <v>104.0769063307945</v>
       </c>
       <c r="N22">
-        <v>426.2791368278149</v>
+        <v>421.3230936692056</v>
       </c>
       <c r="O22">
-        <v>85.25582736556298</v>
+        <v>84.26461873384113</v>
       </c>
       <c r="P22">
-        <v>341.0233094622519</v>
+        <v>337.0584749353645</v>
       </c>
       <c r="Q22">
-        <v>653.2233094622518</v>
+        <v>649.2584749353645</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0768926947117792</v>
+        <v>0.07722067672350684</v>
       </c>
       <c r="T22">
-        <v>0.6392985289023875</v>
+        <v>0.6460421842705562</v>
       </c>
       <c r="U22">
         <v>0.0582577444416894</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.300599522497248</v>
+        <v>5.048190021425951</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07079163567777422</v>
+        <v>0.07074787647545477</v>
       </c>
       <c r="C23">
-        <v>6802.844550548968</v>
+        <v>6726.343449933681</v>
       </c>
       <c r="D23">
-        <v>8497.535039121965</v>
+        <v>8506.104914153011</v>
       </c>
       <c r="E23">
-        <v>226.0929239396783</v>
+        <v>311.1638995860114</v>
       </c>
       <c r="F23">
-        <v>1786.490488572997</v>
+        <v>1871.56146421933</v>
       </c>
       <c r="G23">
         <v>91.8</v>
@@ -3179,28 +3179,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M23">
-        <v>104.0769063307945</v>
+        <v>109.0329494894037</v>
       </c>
       <c r="N23">
-        <v>421.3230936692056</v>
+        <v>416.3670505105964</v>
       </c>
       <c r="O23">
-        <v>84.26461873384113</v>
+        <v>83.27341010211927</v>
       </c>
       <c r="P23">
-        <v>337.0584749353645</v>
+        <v>333.0936404084771</v>
       </c>
       <c r="Q23">
-        <v>649.2584749353645</v>
+        <v>645.2936404084771</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07722067672350684</v>
+        <v>0.07755706853040698</v>
       </c>
       <c r="T23">
-        <v>0.6460421842705562</v>
+        <v>0.6529587538789343</v>
       </c>
       <c r="U23">
         <v>0.0582577444416894</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.048190021425952</v>
+        <v>4.818726838633863</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07074787647545477</v>
+        <v>0.07070411727313533</v>
       </c>
       <c r="C24">
-        <v>6726.343449933681</v>
+        <v>6649.859652430523</v>
       </c>
       <c r="D24">
-        <v>8506.104914153011</v>
+        <v>8514.692092296187</v>
       </c>
       <c r="E24">
-        <v>311.1638995860114</v>
+        <v>396.2348752323446</v>
       </c>
       <c r="F24">
-        <v>1871.56146421933</v>
+        <v>1956.632439865663</v>
       </c>
       <c r="G24">
         <v>91.8</v>
@@ -3261,28 +3261,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M24">
-        <v>109.0329494894037</v>
+        <v>113.988992648013</v>
       </c>
       <c r="N24">
-        <v>416.3670505105964</v>
+        <v>411.4110073519871</v>
       </c>
       <c r="O24">
-        <v>83.27341010211927</v>
+        <v>82.28220147039742</v>
       </c>
       <c r="P24">
-        <v>333.0936404084771</v>
+        <v>329.1288058815897</v>
       </c>
       <c r="Q24">
-        <v>645.2936404084771</v>
+        <v>641.3288058815897</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07755706853040698</v>
+        <v>0.07790219778683699</v>
       </c>
       <c r="T24">
-        <v>0.6529587538789343</v>
+        <v>0.6600549746459716</v>
       </c>
       <c r="U24">
         <v>0.0582577444416894</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.818726838633863</v>
+        <v>4.609216976084564</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07070411727313533</v>
+        <v>0.07066035807081589</v>
       </c>
       <c r="C25">
-        <v>6649.859652430523</v>
+        <v>6573.393210496546</v>
       </c>
       <c r="D25">
-        <v>8514.692092296187</v>
+        <v>8523.296626008543</v>
       </c>
       <c r="E25">
-        <v>396.2348752323446</v>
+        <v>481.305850878678</v>
       </c>
       <c r="F25">
-        <v>1956.632439865663</v>
+        <v>2041.703415511996</v>
       </c>
       <c r="G25">
         <v>91.8</v>
@@ -3343,28 +3343,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M25">
-        <v>113.988992648013</v>
+        <v>118.9450358066223</v>
       </c>
       <c r="N25">
-        <v>411.4110073519871</v>
+        <v>406.4549641933778</v>
       </c>
       <c r="O25">
-        <v>82.28220147039742</v>
+        <v>81.29099283867556</v>
       </c>
       <c r="P25">
-        <v>329.1288058815897</v>
+        <v>325.1639713547023</v>
       </c>
       <c r="Q25">
-        <v>641.3288058815897</v>
+        <v>637.3639713547022</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07790219778683699</v>
+        <v>0.07825640939212042</v>
       </c>
       <c r="T25">
-        <v>0.6600549746459716</v>
+        <v>0.667337938064773</v>
       </c>
       <c r="U25">
         <v>0.0582577444416894</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.609216976084564</v>
+        <v>4.417166268747707</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07066035807081587</v>
+        <v>0.07081659886849642</v>
       </c>
       <c r="C26">
-        <v>6573.39321049655</v>
+        <v>6457.679546003166</v>
       </c>
       <c r="D26">
-        <v>8523.296626008547</v>
+        <v>8492.653937161496</v>
       </c>
       <c r="E26">
-        <v>481.3058508786778</v>
+        <v>566.376826525011</v>
       </c>
       <c r="F26">
-        <v>2041.703415511996</v>
+        <v>2126.774391158329</v>
       </c>
       <c r="G26">
         <v>91.8</v>
@@ -3425,45 +3425,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M26">
-        <v>118.9450358066223</v>
+        <v>126.0278533563899</v>
       </c>
       <c r="N26">
-        <v>406.4549641933778</v>
+        <v>399.3721466436102</v>
       </c>
       <c r="O26">
-        <v>81.29099283867556</v>
+        <v>79.87442932872204</v>
       </c>
       <c r="P26">
-        <v>325.1639713547023</v>
+        <v>319.4977173148882</v>
       </c>
       <c r="Q26">
-        <v>637.3639713547022</v>
+        <v>631.6977173148882</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0782564093921204</v>
+        <v>0.07862006664021139</v>
       </c>
       <c r="T26">
-        <v>0.6673379380647729</v>
+        <v>0.674815113841409</v>
       </c>
       <c r="U26">
-        <v>0.0582577444416894</v>
+        <v>0.0592577444416894</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.04660619555335152</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.417166268747707</v>
+        <v>4.168919695190232</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07081659886849642</v>
+        <v>0.07078083966617699</v>
       </c>
       <c r="C27">
-        <v>6457.679546003166</v>
+        <v>6379.602376182995</v>
       </c>
       <c r="D27">
-        <v>8492.653937161496</v>
+        <v>8499.647742987658</v>
       </c>
       <c r="E27">
-        <v>566.376826525011</v>
+        <v>651.4478021713444</v>
       </c>
       <c r="F27">
-        <v>2126.774391158329</v>
+        <v>2211.845366804663</v>
       </c>
       <c r="G27">
         <v>91.8</v>
@@ -3507,28 +3507,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M27">
-        <v>126.0278533563899</v>
+        <v>131.0689674906455</v>
       </c>
       <c r="N27">
-        <v>399.3721466436102</v>
+        <v>394.3310325093546</v>
       </c>
       <c r="O27">
-        <v>79.87442932872204</v>
+        <v>78.86620650187092</v>
       </c>
       <c r="P27">
-        <v>319.4977173148882</v>
+        <v>315.4648260074837</v>
       </c>
       <c r="Q27">
-        <v>631.6977173148882</v>
+        <v>627.6648260074837</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07862006664021139</v>
+        <v>0.07899355246257511</v>
       </c>
       <c r="T27">
-        <v>0.674815113841409</v>
+        <v>0.6824943754498461</v>
       </c>
       <c r="U27">
         <v>0.0592577444416894</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.168919695190232</v>
+        <v>4.008576629990607</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07078083966617699</v>
+        <v>0.07074508046385752</v>
       </c>
       <c r="C28">
-        <v>6379.602376182995</v>
+        <v>6301.536734828303</v>
       </c>
       <c r="D28">
-        <v>8499.647742987658</v>
+        <v>8506.653077279299</v>
       </c>
       <c r="E28">
-        <v>651.4478021713444</v>
+        <v>736.5187778176773</v>
       </c>
       <c r="F28">
-        <v>2211.845366804663</v>
+        <v>2296.916342450996</v>
       </c>
       <c r="G28">
         <v>91.8</v>
@@ -3589,28 +3589,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M28">
-        <v>131.0689674906455</v>
+        <v>136.110081624901</v>
       </c>
       <c r="N28">
-        <v>394.3310325093546</v>
+        <v>389.2899183750991</v>
       </c>
       <c r="O28">
-        <v>78.86620650187092</v>
+        <v>77.85798367501982</v>
       </c>
       <c r="P28">
-        <v>315.4648260074837</v>
+        <v>311.4319347000793</v>
       </c>
       <c r="Q28">
-        <v>627.6648260074837</v>
+        <v>623.6319347000792</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07899355246257511</v>
+        <v>0.07937727077322276</v>
       </c>
       <c r="T28">
-        <v>0.6824943754498461</v>
+        <v>0.6903840277872816</v>
       </c>
       <c r="U28">
         <v>0.0592577444416894</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.008576629990607</v>
+        <v>3.860110828879845</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07074508046385752</v>
+        <v>0.07070932126153807</v>
       </c>
       <c r="C29">
-        <v>6301.536734828303</v>
+        <v>6223.482650467576</v>
       </c>
       <c r="D29">
-        <v>8506.653077279299</v>
+        <v>8513.669968564906</v>
       </c>
       <c r="E29">
-        <v>736.5187778176773</v>
+        <v>821.5897534640108</v>
       </c>
       <c r="F29">
-        <v>2296.916342450996</v>
+        <v>2381.987318097329</v>
       </c>
       <c r="G29">
         <v>91.8</v>
@@ -3671,28 +3671,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M29">
-        <v>136.110081624901</v>
+        <v>141.1511957591566</v>
       </c>
       <c r="N29">
-        <v>389.2899183750991</v>
+        <v>384.2488042408435</v>
       </c>
       <c r="O29">
-        <v>77.85798367501982</v>
+        <v>76.8497608481687</v>
       </c>
       <c r="P29">
-        <v>311.4319347000793</v>
+        <v>307.3990433926748</v>
       </c>
       <c r="Q29">
-        <v>623.6319347000792</v>
+        <v>619.5990433926747</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07937727077322276</v>
+        <v>0.07977164792583284</v>
       </c>
       <c r="T29">
-        <v>0.6903840277872816</v>
+        <v>0.69849283713409</v>
       </c>
       <c r="U29">
         <v>0.0592577444416894</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.860110828879845</v>
+        <v>3.722249727848422</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07070932126153807</v>
+        <v>0.07067356205921863</v>
       </c>
       <c r="C30">
-        <v>6223.482650467576</v>
+        <v>6145.440151723509</v>
       </c>
       <c r="D30">
-        <v>8513.669968564906</v>
+        <v>8520.698445467173</v>
       </c>
       <c r="E30">
-        <v>821.5897534640108</v>
+        <v>906.6607291103442</v>
       </c>
       <c r="F30">
-        <v>2381.987318097329</v>
+        <v>2467.058293743662</v>
       </c>
       <c r="G30">
         <v>91.8</v>
@@ -3753,28 +3753,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M30">
-        <v>141.1511957591566</v>
+        <v>146.1923098934122</v>
       </c>
       <c r="N30">
-        <v>384.2488042408435</v>
+        <v>379.2076901065878</v>
       </c>
       <c r="O30">
-        <v>76.8497608481687</v>
+        <v>75.84153802131758</v>
       </c>
       <c r="P30">
-        <v>307.3990433926748</v>
+        <v>303.3661520852703</v>
       </c>
       <c r="Q30">
-        <v>619.5990433926747</v>
+        <v>615.5661520852702</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07977164792583284</v>
+        <v>0.08017713429400941</v>
       </c>
       <c r="T30">
-        <v>0.69849283713409</v>
+        <v>0.7068300636455975</v>
       </c>
       <c r="U30">
         <v>0.0592577444416894</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.722249727848422</v>
+        <v>3.593896288957096</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07067356205921863</v>
+        <v>0.07063780285689916</v>
       </c>
       <c r="C31">
-        <v>6145.44015172351</v>
+        <v>6067.409267313406</v>
       </c>
       <c r="D31">
-        <v>8520.698445467173</v>
+        <v>8527.738536703402</v>
       </c>
       <c r="E31">
-        <v>906.6607291103437</v>
+        <v>991.7317047566767</v>
       </c>
       <c r="F31">
-        <v>2467.058293743662</v>
+        <v>2552.129269389995</v>
       </c>
       <c r="G31">
         <v>91.8</v>
@@ -3835,28 +3835,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M31">
-        <v>146.1923098934122</v>
+        <v>151.2334240276678</v>
       </c>
       <c r="N31">
-        <v>379.2076901065878</v>
+        <v>374.1665759723323</v>
       </c>
       <c r="O31">
-        <v>75.84153802131758</v>
+        <v>74.83331519446646</v>
       </c>
       <c r="P31">
-        <v>303.3661520852703</v>
+        <v>299.3332607778658</v>
       </c>
       <c r="Q31">
-        <v>615.5661520852702</v>
+        <v>611.5332607778657</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08017713429400941</v>
+        <v>0.08059420598699102</v>
       </c>
       <c r="T31">
-        <v>0.7068300636455975</v>
+        <v>0.7154054966288623</v>
       </c>
       <c r="U31">
         <v>0.0592577444416894</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.593896288957097</v>
+        <v>3.474099745991861</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07063780285689916</v>
+        <v>0.07060204365457973</v>
       </c>
       <c r="C32">
-        <v>6067.409267313406</v>
+        <v>5989.39002604953</v>
       </c>
       <c r="D32">
-        <v>8527.738536703402</v>
+        <v>8534.79027108586</v>
       </c>
       <c r="E32">
-        <v>991.7317047566767</v>
+        <v>1076.80268040301</v>
       </c>
       <c r="F32">
-        <v>2552.129269389995</v>
+        <v>2637.200245036328</v>
       </c>
       <c r="G32">
         <v>91.8</v>
@@ -3917,28 +3917,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M32">
-        <v>151.2334240276678</v>
+        <v>156.2745381619234</v>
       </c>
       <c r="N32">
-        <v>374.1665759723323</v>
+        <v>369.1254618380767</v>
       </c>
       <c r="O32">
-        <v>74.83331519446646</v>
+        <v>73.82509236761534</v>
       </c>
       <c r="P32">
-        <v>299.3332607778658</v>
+        <v>295.3003694704614</v>
       </c>
       <c r="Q32">
-        <v>611.5332607778657</v>
+        <v>607.5003694704614</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08059420598699102</v>
+        <v>0.08102336671455182</v>
       </c>
       <c r="T32">
-        <v>0.7154054966288623</v>
+        <v>0.7242294928870042</v>
       </c>
       <c r="U32">
         <v>0.0592577444416894</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.474099745991861</v>
+        <v>3.362032012250188</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07060204365457973</v>
+        <v>0.07056628445226028</v>
       </c>
       <c r="C33">
-        <v>5989.39002604953</v>
+        <v>5911.382456839558</v>
       </c>
       <c r="D33">
-        <v>8534.79027108586</v>
+        <v>8541.85367752222</v>
       </c>
       <c r="E33">
-        <v>1076.80268040301</v>
+        <v>1161.873656049343</v>
       </c>
       <c r="F33">
-        <v>2637.200245036328</v>
+        <v>2722.271220682661</v>
       </c>
       <c r="G33">
         <v>91.8</v>
@@ -3999,28 +3999,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M33">
-        <v>156.2745381619234</v>
+        <v>161.315652296179</v>
       </c>
       <c r="N33">
-        <v>369.1254618380767</v>
+        <v>364.0843477038211</v>
       </c>
       <c r="O33">
-        <v>73.82509236761534</v>
+        <v>72.81686954076422</v>
       </c>
       <c r="P33">
-        <v>295.3003694704614</v>
+        <v>291.2674781630569</v>
       </c>
       <c r="Q33">
-        <v>607.5003694704614</v>
+        <v>603.4674781630569</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08102336671455182</v>
+        <v>0.08146514981645263</v>
       </c>
       <c r="T33">
-        <v>0.7242294928870042</v>
+        <v>0.7333130184468563</v>
       </c>
       <c r="U33">
         <v>0.0592577444416894</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.362032012250188</v>
+        <v>3.256968511867369</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07056628445226028</v>
+        <v>0.07053052524994083</v>
       </c>
       <c r="C34">
-        <v>5911.382456839558</v>
+        <v>5833.386588686919</v>
       </c>
       <c r="D34">
-        <v>8541.85367752222</v>
+        <v>8548.928785015914</v>
       </c>
       <c r="E34">
-        <v>1161.873656049343</v>
+        <v>1246.944631695676</v>
       </c>
       <c r="F34">
-        <v>2722.271220682661</v>
+        <v>2807.342196328995</v>
       </c>
       <c r="G34">
         <v>91.8</v>
@@ -4081,28 +4081,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M34">
-        <v>161.315652296179</v>
+        <v>166.3567664304346</v>
       </c>
       <c r="N34">
-        <v>364.0843477038211</v>
+        <v>359.0432335695655</v>
       </c>
       <c r="O34">
-        <v>72.81686954076422</v>
+        <v>71.80864671391309</v>
       </c>
       <c r="P34">
-        <v>291.2674781630569</v>
+        <v>287.2345868556524</v>
       </c>
       <c r="Q34">
-        <v>603.4674781630569</v>
+        <v>599.4345868556524</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08146514981645263</v>
+        <v>0.08192012047363406</v>
       </c>
       <c r="T34">
-        <v>0.7333130184468563</v>
+        <v>0.7426676940234204</v>
       </c>
       <c r="U34">
         <v>0.0592577444416894</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.256968511867369</v>
+        <v>3.158272496356236</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07053052524994083</v>
+        <v>0.07049476604762137</v>
       </c>
       <c r="C35">
-        <v>5833.386588686919</v>
+        <v>5755.402450691223</v>
       </c>
       <c r="D35">
-        <v>8548.928785015914</v>
+        <v>8556.015622666551</v>
       </c>
       <c r="E35">
-        <v>1246.944631695676</v>
+        <v>1332.01560734201</v>
       </c>
       <c r="F35">
-        <v>2807.342196328995</v>
+        <v>2892.413171975328</v>
       </c>
       <c r="G35">
         <v>91.8</v>
@@ -4163,28 +4163,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M35">
-        <v>166.3567664304346</v>
+        <v>171.3978805646902</v>
       </c>
       <c r="N35">
-        <v>359.0432335695655</v>
+        <v>354.0021194353099</v>
       </c>
       <c r="O35">
-        <v>71.80864671391309</v>
+        <v>70.80042388706197</v>
       </c>
       <c r="P35">
-        <v>287.2345868556524</v>
+        <v>283.2016955482479</v>
       </c>
       <c r="Q35">
-        <v>599.4345868556524</v>
+        <v>595.4016955482479</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08192012047363406</v>
+        <v>0.08238887812042706</v>
       </c>
       <c r="T35">
-        <v>0.7426676940234204</v>
+        <v>0.7523058446174561</v>
       </c>
       <c r="U35">
         <v>0.0592577444416894</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.158272496356236</v>
+        <v>3.065382128816347</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07049476604762137</v>
+        <v>0.07115900684530192</v>
       </c>
       <c r="C36">
-        <v>5755.402450691223</v>
+        <v>5540.579625101802</v>
       </c>
       <c r="D36">
-        <v>8556.015622666551</v>
+        <v>8426.263772723463</v>
       </c>
       <c r="E36">
-        <v>1332.01560734201</v>
+        <v>1417.086582988343</v>
       </c>
       <c r="F36">
-        <v>2892.413171975328</v>
+        <v>2977.484147621661</v>
       </c>
       <c r="G36">
         <v>91.8</v>
@@ -4245,45 +4245,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M36">
-        <v>171.3978805646902</v>
+        <v>183.8827050679999</v>
       </c>
       <c r="N36">
-        <v>354.0021194353099</v>
+        <v>341.5172949320001</v>
       </c>
       <c r="O36">
-        <v>70.80042388706197</v>
+        <v>68.30345898640003</v>
       </c>
       <c r="P36">
-        <v>283.2016955482479</v>
+        <v>273.2138359456001</v>
       </c>
       <c r="Q36">
-        <v>595.4016955482479</v>
+        <v>585.4138359456001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08238887812042706</v>
+        <v>0.08287205907942907</v>
       </c>
       <c r="T36">
-        <v>0.7523058446174561</v>
+        <v>0.7622405536913083</v>
       </c>
       <c r="U36">
-        <v>0.0592577444416894</v>
+        <v>0.0617577444416894</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.04740619555335152</v>
+        <v>0.04940619555335152</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.065382128816347</v>
+        <v>2.857256204740445</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07115900684530192</v>
+        <v>0.07114324764298247</v>
       </c>
       <c r="C37">
-        <v>5540.579625101802</v>
+        <v>5458.541437139659</v>
       </c>
       <c r="D37">
-        <v>8426.263772723463</v>
+        <v>8429.296560407654</v>
       </c>
       <c r="E37">
-        <v>1417.086582988343</v>
+        <v>1502.157558634676</v>
       </c>
       <c r="F37">
-        <v>2977.484147621661</v>
+        <v>3062.555123267995</v>
       </c>
       <c r="G37">
         <v>91.8</v>
@@ -4327,28 +4327,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M37">
-        <v>183.8827050679999</v>
+        <v>189.1364966413714</v>
       </c>
       <c r="N37">
-        <v>341.5172949320001</v>
+        <v>336.2635033586287</v>
       </c>
       <c r="O37">
-        <v>68.30345898640003</v>
+        <v>67.25270067172575</v>
       </c>
       <c r="P37">
-        <v>273.2138359456001</v>
+        <v>269.010802686903</v>
       </c>
       <c r="Q37">
-        <v>585.4138359456001</v>
+        <v>581.210802686903</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08287205907942907</v>
+        <v>0.08337033944339989</v>
       </c>
       <c r="T37">
-        <v>0.7622405536913083</v>
+        <v>0.7724857224237184</v>
       </c>
       <c r="U37">
         <v>0.0617577444416894</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.857256204740445</v>
+        <v>2.777887976830988</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07114324764298248</v>
+        <v>0.07112748844066302</v>
       </c>
       <c r="C38">
-        <v>5458.541437139658</v>
+        <v>5376.505433090354</v>
       </c>
       <c r="D38">
-        <v>8429.296560407653</v>
+        <v>8432.331532004682</v>
       </c>
       <c r="E38">
-        <v>1502.157558634676</v>
+        <v>1587.228534281009</v>
       </c>
       <c r="F38">
-        <v>3062.555123267994</v>
+        <v>3147.626098914327</v>
       </c>
       <c r="G38">
         <v>91.8</v>
@@ -4409,28 +4409,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M38">
-        <v>189.1364966413713</v>
+        <v>194.3902882147428</v>
       </c>
       <c r="N38">
-        <v>336.2635033586288</v>
+        <v>331.0097117852573</v>
       </c>
       <c r="O38">
-        <v>67.25270067172576</v>
+        <v>66.20194235705146</v>
       </c>
       <c r="P38">
-        <v>269.010802686903</v>
+        <v>264.8077694282059</v>
       </c>
       <c r="Q38">
-        <v>581.210802686903</v>
+        <v>577.0077694282058</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08337033944339989</v>
+        <v>0.08388443823162375</v>
       </c>
       <c r="T38">
-        <v>0.7724857224237183</v>
+        <v>0.783056134607951</v>
       </c>
       <c r="U38">
         <v>0.0617577444416894</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.777887976830989</v>
+        <v>2.702809923403124</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07112748844066302</v>
+        <v>0.07111172923834358</v>
       </c>
       <c r="C39">
-        <v>5376.505433090354</v>
+        <v>5294.47161531369</v>
       </c>
       <c r="D39">
-        <v>8432.331532004682</v>
+        <v>8435.368689874351</v>
       </c>
       <c r="E39">
-        <v>1587.228534281009</v>
+        <v>1672.299509927342</v>
       </c>
       <c r="F39">
-        <v>3147.626098914327</v>
+        <v>3232.69707456066</v>
       </c>
       <c r="G39">
         <v>91.8</v>
@@ -4491,28 +4491,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M39">
-        <v>194.3902882147428</v>
+        <v>199.6440797881142</v>
       </c>
       <c r="N39">
-        <v>331.0097117852573</v>
+        <v>325.7559202118859</v>
       </c>
       <c r="O39">
-        <v>66.20194235705146</v>
+        <v>65.15118404237718</v>
       </c>
       <c r="P39">
-        <v>264.8077694282059</v>
+        <v>260.6047361695087</v>
       </c>
       <c r="Q39">
-        <v>577.0077694282058</v>
+        <v>572.8047361695087</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08388443823162375</v>
+        <v>0.0844151208517258</v>
       </c>
       <c r="T39">
-        <v>0.783056134607951</v>
+        <v>0.7939675278303845</v>
       </c>
       <c r="U39">
         <v>0.0617577444416894</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.702809923403124</v>
+        <v>2.631683346471463</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07111172923834358</v>
+        <v>0.07109597003602412</v>
       </c>
       <c r="C40">
-        <v>5294.47161531369</v>
+        <v>5212.439986172878</v>
       </c>
       <c r="D40">
-        <v>8435.368689874351</v>
+        <v>8438.408036379873</v>
       </c>
       <c r="E40">
-        <v>1672.299509927342</v>
+        <v>1757.370485573676</v>
       </c>
       <c r="F40">
-        <v>3232.69707456066</v>
+        <v>3317.768050206994</v>
       </c>
       <c r="G40">
         <v>91.8</v>
@@ -4573,28 +4573,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M40">
-        <v>199.6440797881142</v>
+        <v>204.8978713614856</v>
       </c>
       <c r="N40">
-        <v>325.7559202118859</v>
+        <v>320.5021286385145</v>
       </c>
       <c r="O40">
-        <v>65.15118404237718</v>
+        <v>64.1004257277029</v>
       </c>
       <c r="P40">
-        <v>260.6047361695087</v>
+        <v>256.4017029108116</v>
       </c>
       <c r="Q40">
-        <v>572.8047361695087</v>
+        <v>568.6017029108116</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.0844151208517258</v>
+        <v>0.08496320290199513</v>
       </c>
       <c r="T40">
-        <v>0.7939675278303845</v>
+        <v>0.805236671650275</v>
       </c>
       <c r="U40">
         <v>0.0617577444416894</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.631683346471463</v>
+        <v>2.564204286305528</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07109597003602412</v>
+        <v>0.07108021083370467</v>
       </c>
       <c r="C41">
-        <v>5212.439986172878</v>
+        <v>5130.410548034528</v>
       </c>
       <c r="D41">
-        <v>8438.408036379873</v>
+        <v>8441.449573887856</v>
       </c>
       <c r="E41">
-        <v>1757.370485573676</v>
+        <v>1842.441461220009</v>
       </c>
       <c r="F41">
-        <v>3317.768050206994</v>
+        <v>3402.839025853327</v>
       </c>
       <c r="G41">
         <v>91.8</v>
@@ -4655,28 +4655,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M41">
-        <v>204.8978713614856</v>
+        <v>210.1516629348571</v>
       </c>
       <c r="N41">
-        <v>320.5021286385145</v>
+        <v>315.248337065143</v>
       </c>
       <c r="O41">
-        <v>64.1004257277029</v>
+        <v>63.0496674130286</v>
       </c>
       <c r="P41">
-        <v>256.4017029108116</v>
+        <v>252.1986696521144</v>
       </c>
       <c r="Q41">
-        <v>568.6017029108116</v>
+        <v>564.3986696521144</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08496320290199513</v>
+        <v>0.08552955435394011</v>
       </c>
       <c r="T41">
-        <v>0.805236671650275</v>
+        <v>0.8168814535974952</v>
       </c>
       <c r="U41">
         <v>0.0617577444416894</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.564204286305528</v>
+        <v>2.500099179147889</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07108021083370467</v>
+        <v>0.07221245163138523</v>
       </c>
       <c r="C42">
-        <v>5130.410548034528</v>
+        <v>4832.255591002307</v>
       </c>
       <c r="D42">
-        <v>8441.449573887856</v>
+        <v>8228.365592501968</v>
       </c>
       <c r="E42">
-        <v>1842.441461220009</v>
+        <v>1927.512436866342</v>
       </c>
       <c r="F42">
-        <v>3402.839025853327</v>
+        <v>3487.91000149966</v>
       </c>
       <c r="G42">
         <v>91.8</v>
@@ -4737,45 +4737,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M42">
-        <v>210.1516629348571</v>
+        <v>227.6131395134773</v>
       </c>
       <c r="N42">
-        <v>315.248337065143</v>
+        <v>297.7868604865228</v>
       </c>
       <c r="O42">
-        <v>63.0496674130286</v>
+        <v>59.55737209730455</v>
       </c>
       <c r="P42">
-        <v>252.1986696521144</v>
+        <v>238.2294883892182</v>
       </c>
       <c r="Q42">
-        <v>564.3986696521144</v>
+        <v>550.4294883892182</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08552955435394011</v>
+        <v>0.0861151041601883</v>
       </c>
       <c r="T42">
-        <v>0.8168814535974952</v>
+        <v>0.8289209739158077</v>
       </c>
       <c r="U42">
-        <v>0.0617577444416894</v>
+        <v>0.0652577444416894</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.04940619555335152</v>
+        <v>0.05220619555335152</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.500099179147889</v>
+        <v>2.308302592385667</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07221245163138523</v>
+        <v>0.07222469242906578</v>
       </c>
       <c r="C43">
-        <v>4832.255591002307</v>
+        <v>4744.939701043004</v>
       </c>
       <c r="D43">
-        <v>8228.365592501968</v>
+        <v>8226.120678188998</v>
       </c>
       <c r="E43">
-        <v>1927.512436866342</v>
+        <v>2012.583412512675</v>
       </c>
       <c r="F43">
-        <v>3487.91000149966</v>
+        <v>3572.980977145994</v>
       </c>
       <c r="G43">
         <v>91.8</v>
@@ -4819,28 +4819,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M43">
-        <v>227.6131395134773</v>
+        <v>233.1646795016109</v>
       </c>
       <c r="N43">
-        <v>297.7868604865228</v>
+        <v>292.2353204983892</v>
       </c>
       <c r="O43">
-        <v>59.55737209730455</v>
+        <v>58.44706409967784</v>
       </c>
       <c r="P43">
-        <v>238.2294883892182</v>
+        <v>233.7882563987113</v>
       </c>
       <c r="Q43">
-        <v>550.4294883892182</v>
+        <v>545.9882563987113</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.0861151041601883</v>
+        <v>0.08672084533906575</v>
       </c>
       <c r="T43">
-        <v>0.8289209739158077</v>
+        <v>0.8413756501071653</v>
       </c>
       <c r="U43">
         <v>0.0652577444416894</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.308302592385667</v>
+        <v>2.253343006852675</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07222469242906576</v>
+        <v>0.07320013322674632</v>
       </c>
       <c r="C44">
-        <v>4744.939701043006</v>
+        <v>4484.830989830723</v>
       </c>
       <c r="D44">
-        <v>8226.120678189</v>
+        <v>8051.08294262305</v>
       </c>
       <c r="E44">
-        <v>2012.583412512675</v>
+        <v>2097.654388159008</v>
       </c>
       <c r="F44">
-        <v>3572.980977145993</v>
+        <v>3658.051952792327</v>
       </c>
       <c r="G44">
         <v>91.8</v>
@@ -4901,45 +4901,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M44">
-        <v>233.1646795016109</v>
+        <v>248.958764957563</v>
       </c>
       <c r="N44">
-        <v>292.2353204983892</v>
+        <v>276.4412350424371</v>
       </c>
       <c r="O44">
-        <v>58.44706409967785</v>
+        <v>55.28824700848742</v>
       </c>
       <c r="P44">
-        <v>233.7882563987114</v>
+        <v>221.1529880339497</v>
       </c>
       <c r="Q44">
-        <v>545.9882563987114</v>
+        <v>533.3529880339497</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08672084533906574</v>
+        <v>0.08734784059439503</v>
       </c>
       <c r="T44">
-        <v>0.8413756501071651</v>
+        <v>0.8542673324806758</v>
       </c>
       <c r="U44">
-        <v>0.0652577444416894</v>
+        <v>0.0680577444416894</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.05220619555335152</v>
+        <v>0.05444619555335152</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.253343006852675</v>
+        <v>2.110389646612999</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07320013322674632</v>
+        <v>0.07323477402442688</v>
       </c>
       <c r="C45">
-        <v>4484.830989830723</v>
+        <v>4393.680766669393</v>
       </c>
       <c r="D45">
-        <v>8051.08294262305</v>
+        <v>8045.003695108052</v>
       </c>
       <c r="E45">
-        <v>2097.654388159008</v>
+        <v>2182.725363805341</v>
       </c>
       <c r="F45">
-        <v>3658.051952792327</v>
+        <v>3743.12292843866</v>
       </c>
       <c r="G45">
         <v>91.8</v>
@@ -4983,28 +4983,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M45">
-        <v>248.958764957563</v>
+        <v>254.7485036775063</v>
       </c>
       <c r="N45">
-        <v>276.4412350424371</v>
+        <v>270.6514963224938</v>
       </c>
       <c r="O45">
-        <v>55.28824700848742</v>
+        <v>54.13029926449877</v>
       </c>
       <c r="P45">
-        <v>221.1529880339497</v>
+        <v>216.521197057995</v>
       </c>
       <c r="Q45">
-        <v>533.3529880339497</v>
+        <v>528.721197057995</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08734784059439503</v>
+        <v>0.08799722853741465</v>
       </c>
       <c r="T45">
-        <v>0.8542673324806758</v>
+        <v>0.8676194320818117</v>
       </c>
       <c r="U45">
         <v>0.0680577444416894</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.110389646612999</v>
+        <v>2.062426245553613</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07323477402442688</v>
+        <v>0.07326941482210743</v>
       </c>
       <c r="C46">
-        <v>4393.680766669393</v>
+        <v>4302.539717271598</v>
       </c>
       <c r="D46">
-        <v>8045.003695108052</v>
+        <v>8038.933621356591</v>
       </c>
       <c r="E46">
-        <v>2182.725363805341</v>
+        <v>2267.796339451675</v>
       </c>
       <c r="F46">
-        <v>3743.12292843866</v>
+        <v>3828.193904084993</v>
       </c>
       <c r="G46">
         <v>91.8</v>
@@ -5065,28 +5065,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M46">
-        <v>254.7485036775063</v>
+        <v>260.5382423974497</v>
       </c>
       <c r="N46">
-        <v>270.6514963224938</v>
+        <v>264.8617576025504</v>
       </c>
       <c r="O46">
-        <v>54.13029926449877</v>
+        <v>52.97235152051009</v>
       </c>
       <c r="P46">
-        <v>216.521197057995</v>
+        <v>211.8894060820404</v>
       </c>
       <c r="Q46">
-        <v>528.721197057995</v>
+        <v>524.0894060820403</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08799722853741465</v>
+        <v>0.08867023058745316</v>
       </c>
       <c r="T46">
-        <v>0.8676194320818117</v>
+        <v>0.8814570625775343</v>
       </c>
       <c r="U46">
         <v>0.0680577444416894</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.062426245553613</v>
+        <v>2.016594551207977</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07326941482210743</v>
+        <v>0.07617445561978797</v>
       </c>
       <c r="C47">
-        <v>4302.539717271598</v>
+        <v>3739.075631231319</v>
       </c>
       <c r="D47">
-        <v>8038.933621356591</v>
+        <v>7560.540510962644</v>
       </c>
       <c r="E47">
-        <v>2267.796339451675</v>
+        <v>2352.867315098008</v>
       </c>
       <c r="F47">
-        <v>3828.193904084993</v>
+        <v>3913.264879731326</v>
       </c>
       <c r="G47">
         <v>91.8</v>
@@ -5147,45 +5147,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M47">
-        <v>260.5382423974497</v>
+        <v>296.8514471792973</v>
       </c>
       <c r="N47">
-        <v>264.8617576025504</v>
+        <v>228.5485528207028</v>
       </c>
       <c r="O47">
-        <v>52.97235152051009</v>
+        <v>45.70971056414055</v>
       </c>
       <c r="P47">
-        <v>211.8894060820404</v>
+        <v>182.8388422565622</v>
       </c>
       <c r="Q47">
-        <v>524.0894060820403</v>
+        <v>495.0388422565622</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08867023058745316</v>
+        <v>0.08936815863934494</v>
       </c>
       <c r="T47">
-        <v>0.8814570625775343</v>
+        <v>0.8958071979064319</v>
       </c>
       <c r="U47">
-        <v>0.0680577444416894</v>
+        <v>0.0758577444416894</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.05444619555335152</v>
+        <v>0.06068619555335152</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.016594551207977</v>
+        <v>1.769908838216511</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07617445561978797</v>
+        <v>0.07773789641746853</v>
       </c>
       <c r="C48">
-        <v>3739.075631231319</v>
+        <v>3419.377928820603</v>
       </c>
       <c r="D48">
-        <v>7560.540510962644</v>
+        <v>7325.913784198262</v>
       </c>
       <c r="E48">
-        <v>2352.867315098008</v>
+        <v>2437.938290744341</v>
       </c>
       <c r="F48">
-        <v>3913.264879731326</v>
+        <v>3998.335855377659</v>
       </c>
       <c r="G48">
         <v>91.8</v>
@@ -5229,45 +5229,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M48">
-        <v>296.8514471792973</v>
+        <v>318.898249345255</v>
       </c>
       <c r="N48">
-        <v>228.5485528207028</v>
+        <v>206.5017506547451</v>
       </c>
       <c r="O48">
-        <v>45.70971056414055</v>
+        <v>41.30035013094903</v>
       </c>
       <c r="P48">
-        <v>182.8388422565622</v>
+        <v>165.2014005237961</v>
       </c>
       <c r="Q48">
-        <v>495.0388422565622</v>
+        <v>477.4014005237961</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08936815863934494</v>
+        <v>0.0900924235988553</v>
       </c>
       <c r="T48">
-        <v>0.8958071979064319</v>
+        <v>0.9106988477760427</v>
       </c>
       <c r="U48">
-        <v>0.0758577444416894</v>
+        <v>0.0797577444416894</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.06068619555335152</v>
+        <v>0.06380619555335153</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.769908838216511</v>
+        <v>1.647547457782298</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07773789641746853</v>
+        <v>0.07786613721514908</v>
       </c>
       <c r="C49">
-        <v>3419.377928820603</v>
+        <v>3315.706345700909</v>
       </c>
       <c r="D49">
-        <v>7325.913784198262</v>
+        <v>7307.313176724901</v>
       </c>
       <c r="E49">
-        <v>2437.938290744341</v>
+        <v>2523.009266390674</v>
       </c>
       <c r="F49">
-        <v>3998.335855377659</v>
+        <v>4083.406831023993</v>
       </c>
       <c r="G49">
         <v>91.8</v>
@@ -5311,28 +5311,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M49">
-        <v>318.898249345255</v>
+        <v>325.6833184802604</v>
       </c>
       <c r="N49">
-        <v>206.5017506547451</v>
+        <v>199.7166815197397</v>
       </c>
       <c r="O49">
-        <v>41.30035013094903</v>
+        <v>39.94333630394794</v>
       </c>
       <c r="P49">
-        <v>165.2014005237961</v>
+        <v>159.7733452157918</v>
       </c>
       <c r="Q49">
-        <v>477.4014005237961</v>
+        <v>471.9733452157918</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.0900924235988553</v>
+        <v>0.0908445449029622</v>
       </c>
       <c r="T49">
-        <v>0.9106988477760427</v>
+        <v>0.9261632534098692</v>
       </c>
       <c r="U49">
         <v>0.0797577444416894</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.647547457782298</v>
+        <v>1.613223552411833</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07786613721514908</v>
+        <v>0.07799437801282963</v>
       </c>
       <c r="C50">
-        <v>3315.706345700909</v>
+        <v>3212.128977822667</v>
       </c>
       <c r="D50">
-        <v>7307.313176724901</v>
+        <v>7288.806784492993</v>
       </c>
       <c r="E50">
-        <v>2523.009266390674</v>
+        <v>2608.080242037007</v>
       </c>
       <c r="F50">
-        <v>4083.406831023992</v>
+        <v>4168.477806670326</v>
       </c>
       <c r="G50">
         <v>91.8</v>
@@ -5393,28 +5393,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M50">
-        <v>325.6833184802604</v>
+        <v>332.4683876152658</v>
       </c>
       <c r="N50">
-        <v>199.7166815197397</v>
+        <v>192.9316123847343</v>
       </c>
       <c r="O50">
-        <v>39.94333630394794</v>
+        <v>38.58632247694686</v>
       </c>
       <c r="P50">
-        <v>159.7733452157918</v>
+        <v>154.3452899077874</v>
       </c>
       <c r="Q50">
-        <v>471.9733452157918</v>
+        <v>466.5452899077874</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.0908445449029622</v>
+        <v>0.09162616116017133</v>
       </c>
       <c r="T50">
-        <v>0.9261632534098692</v>
+        <v>0.9422341063234535</v>
       </c>
       <c r="U50">
         <v>0.0797577444416894</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.613223552411833</v>
+        <v>1.580300622770775</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07799437801282963</v>
+        <v>0.07812261881051016</v>
       </c>
       <c r="C51">
-        <v>3212.128977822667</v>
+        <v>3108.645111169845</v>
       </c>
       <c r="D51">
-        <v>7288.806784492993</v>
+        <v>7270.393893486504</v>
       </c>
       <c r="E51">
-        <v>2608.080242037007</v>
+        <v>2693.15121768334</v>
       </c>
       <c r="F51">
-        <v>4168.477806670326</v>
+        <v>4253.548782316659</v>
       </c>
       <c r="G51">
         <v>91.8</v>
@@ -5475,28 +5475,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M51">
-        <v>332.4683876152658</v>
+        <v>339.2534567502712</v>
       </c>
       <c r="N51">
-        <v>192.9316123847343</v>
+        <v>186.1465432497289</v>
       </c>
       <c r="O51">
-        <v>38.58632247694686</v>
+        <v>37.22930864994578</v>
       </c>
       <c r="P51">
-        <v>154.3452899077874</v>
+        <v>148.9172345997831</v>
       </c>
       <c r="Q51">
-        <v>466.5452899077874</v>
+        <v>461.1172345997831</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09162616116017133</v>
+        <v>0.09243904206766881</v>
       </c>
       <c r="T51">
-        <v>0.9422341063234535</v>
+        <v>0.9589477933535814</v>
       </c>
       <c r="U51">
         <v>0.0797577444416894</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.580300622770775</v>
+        <v>1.54869461031536</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07812261881051016</v>
+        <v>0.07825085960819073</v>
       </c>
       <c r="C52">
-        <v>3108.645111169845</v>
+        <v>3005.254038923174</v>
       </c>
       <c r="D52">
-        <v>7270.393893486504</v>
+        <v>7252.073796886165</v>
       </c>
       <c r="E52">
-        <v>2693.15121768334</v>
+        <v>2778.222193329673</v>
       </c>
       <c r="F52">
-        <v>4253.548782316659</v>
+        <v>4338.619757962992</v>
       </c>
       <c r="G52">
         <v>91.8</v>
@@ -5557,28 +5557,28 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M52">
-        <v>339.2534567502712</v>
+        <v>346.0385258852766</v>
       </c>
       <c r="N52">
-        <v>186.1465432497289</v>
+        <v>179.3614741147235</v>
       </c>
       <c r="O52">
-        <v>37.22930864994578</v>
+        <v>35.8722948229447</v>
       </c>
       <c r="P52">
-        <v>148.9172345997831</v>
+        <v>143.4891792917788</v>
       </c>
       <c r="Q52">
-        <v>461.1172345997831</v>
+        <v>455.6891792917788</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09243904206766881</v>
+        <v>0.09328510178771723</v>
       </c>
       <c r="T52">
-        <v>0.9589477933535814</v>
+        <v>0.9763436716910614</v>
       </c>
       <c r="U52">
         <v>0.0797577444416894</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.54869461031536</v>
+        <v>1.518328049328785</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07825085960819073</v>
+        <v>0.08428630040587128</v>
       </c>
       <c r="C53">
-        <v>3005.254038923174</v>
+        <v>2151.329902743016</v>
       </c>
       <c r="D53">
-        <v>7252.073796886165</v>
+        <v>6483.220636352341</v>
       </c>
       <c r="E53">
-        <v>2778.222193329673</v>
+        <v>2863.293168976007</v>
       </c>
       <c r="F53">
-        <v>4338.619757962992</v>
+        <v>4423.690733609325</v>
       </c>
       <c r="G53">
         <v>91.8</v>
@@ -5639,45 +5639,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M53">
-        <v>346.0385258852766</v>
+        <v>415.6400034375345</v>
       </c>
       <c r="N53">
-        <v>179.3614741147235</v>
+        <v>109.7599965624656</v>
       </c>
       <c r="O53">
-        <v>35.8722948229447</v>
+        <v>21.95199931249311</v>
       </c>
       <c r="P53">
-        <v>143.4891792917788</v>
+        <v>87.80799724997246</v>
       </c>
       <c r="Q53">
-        <v>455.6891792917788</v>
+        <v>400.0079972499724</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09328510178771723</v>
+        <v>0.094166413996101</v>
       </c>
       <c r="T53">
-        <v>0.9763436716910614</v>
+        <v>0.9944643782926028</v>
       </c>
       <c r="U53">
-        <v>0.0797577444416894</v>
+        <v>0.0939577444416894</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.06380619555335153</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.518328049328785</v>
+        <v>1.264074669557068</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08428630040587128</v>
+        <v>0.0974287349181065</v>
       </c>
       <c r="C54">
-        <v>2151.329902743016</v>
+        <v>850.268134639281</v>
       </c>
       <c r="D54">
-        <v>6483.220636352341</v>
+        <v>5267.229843894939</v>
       </c>
       <c r="E54">
-        <v>2863.293168976007</v>
+        <v>2948.36414462234</v>
       </c>
       <c r="F54">
-        <v>4423.690733609325</v>
+        <v>4508.761709255658</v>
       </c>
       <c r="G54">
         <v>91.8</v>
@@ -5721,45 +5721,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M54">
-        <v>415.6400034375345</v>
+        <v>552.5836653114296</v>
       </c>
       <c r="N54">
-        <v>109.7599965624656</v>
+        <v>-27.18366531142954</v>
       </c>
       <c r="O54">
-        <v>21.95199931249311</v>
+        <v>-5.436733062285907</v>
       </c>
       <c r="P54">
-        <v>87.80799724997246</v>
+        <v>-21.74693224914363</v>
       </c>
       <c r="Q54">
-        <v>400.0079972499724</v>
+        <v>290.4530677508563</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.094166413996101</v>
+        <v>0.09537270055060963</v>
       </c>
       <c r="T54">
-        <v>0.9944643782926028</v>
+        <v>1.019266899491897</v>
       </c>
       <c r="U54">
-        <v>0.0939577444416894</v>
+        <v>0.1225577444416894</v>
       </c>
       <c r="V54">
-        <v>0.2</v>
+        <v>0.1901612490495501</v>
       </c>
       <c r="W54">
-        <v>0.07516619555335152</v>
+        <v>0.09925201067796219</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.264074669557068</v>
+        <v>0.9508062452477506</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0974287349181065</v>
+        <v>0.09819631236252338</v>
       </c>
       <c r="C55">
-        <v>850.268134639281</v>
+        <v>708.1233838260941</v>
       </c>
       <c r="D55">
-        <v>5267.229843894939</v>
+        <v>5210.156068728085</v>
       </c>
       <c r="E55">
-        <v>2948.36414462234</v>
+        <v>3033.435120268673</v>
       </c>
       <c r="F55">
-        <v>4508.761709255658</v>
+        <v>4593.832684901991</v>
       </c>
       <c r="G55">
         <v>91.8</v>
@@ -5803,37 +5803,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M55">
-        <v>552.5836653114296</v>
+        <v>563.0097722040981</v>
       </c>
       <c r="N55">
-        <v>-27.18366531142954</v>
+        <v>-37.60977220409802</v>
       </c>
       <c r="O55">
-        <v>-5.436733062285907</v>
+        <v>-7.521954440819605</v>
       </c>
       <c r="P55">
-        <v>-21.74693224914363</v>
+        <v>-30.08781776327842</v>
       </c>
       <c r="Q55">
-        <v>290.4530677508563</v>
+        <v>282.1121822367216</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09537270055060963</v>
+        <v>0.09645036795388376</v>
       </c>
       <c r="T55">
-        <v>1.019266899491897</v>
+        <v>1.041424875567808</v>
       </c>
       <c r="U55">
         <v>0.1225577444416894</v>
       </c>
       <c r="V55">
-        <v>0.1901612490495501</v>
+        <v>0.1866397444375214</v>
       </c>
       <c r="W55">
-        <v>0.09925201067796219</v>
+        <v>0.09968359834025343</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.9508062452477506</v>
+        <v>0.933198722187607</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09819631236252338</v>
+        <v>0.09896388980694026</v>
       </c>
       <c r="C56">
-        <v>708.1233838260941</v>
+        <v>567.2022355888876</v>
       </c>
       <c r="D56">
-        <v>5210.156068728085</v>
+        <v>5154.305896137213</v>
       </c>
       <c r="E56">
-        <v>3033.435120268673</v>
+        <v>3118.506095915007</v>
       </c>
       <c r="F56">
-        <v>4593.832684901991</v>
+        <v>4678.903660548325</v>
       </c>
       <c r="G56">
         <v>91.8</v>
@@ -5885,37 +5885,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M56">
-        <v>563.0097722040981</v>
+        <v>573.4358790967667</v>
       </c>
       <c r="N56">
-        <v>-37.60977220409802</v>
+        <v>-48.03587909676662</v>
       </c>
       <c r="O56">
-        <v>-7.521954440819605</v>
+        <v>-9.607175819353325</v>
       </c>
       <c r="P56">
-        <v>-30.08781776327842</v>
+        <v>-38.4287032774133</v>
       </c>
       <c r="Q56">
-        <v>282.1121822367216</v>
+        <v>273.7712967225867</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09645036795388376</v>
+        <v>0.09757593168619227</v>
       </c>
       <c r="T56">
-        <v>1.041424875567808</v>
+        <v>1.064567650580426</v>
       </c>
       <c r="U56">
         <v>0.1225577444416894</v>
       </c>
       <c r="V56">
-        <v>0.1866397444375214</v>
+        <v>0.1832462945386574</v>
       </c>
       <c r="W56">
-        <v>0.09968359834025343</v>
+        <v>0.1000994919057341</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.933198722187607</v>
+        <v>0.9162314726932868</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09896388980694026</v>
+        <v>0.09973146725135718</v>
       </c>
       <c r="C57">
-        <v>567.2022355888876</v>
+        <v>427.4657581004358</v>
       </c>
       <c r="D57">
-        <v>5154.305896137213</v>
+        <v>5099.640394295094</v>
       </c>
       <c r="E57">
-        <v>3118.506095915007</v>
+        <v>3203.57707156134</v>
       </c>
       <c r="F57">
-        <v>4678.903660548325</v>
+        <v>4763.974636194658</v>
       </c>
       <c r="G57">
         <v>91.8</v>
@@ -5967,37 +5967,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M57">
-        <v>573.4358790967667</v>
+        <v>583.8619859894352</v>
       </c>
       <c r="N57">
-        <v>-48.03587909676662</v>
+        <v>-58.46198598943511</v>
       </c>
       <c r="O57">
-        <v>-9.607175819353325</v>
+        <v>-11.69239719788702</v>
       </c>
       <c r="P57">
-        <v>-38.4287032774133</v>
+        <v>-46.76958879154809</v>
       </c>
       <c r="Q57">
-        <v>273.7712967225867</v>
+        <v>265.4304112084519</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09757593168619227</v>
+        <v>0.09875265740633302</v>
       </c>
       <c r="T57">
-        <v>1.064567650580426</v>
+        <v>1.088762369911799</v>
       </c>
       <c r="U57">
         <v>0.1225577444416894</v>
       </c>
       <c r="V57">
-        <v>0.1832462945386574</v>
+        <v>0.1799740392790385</v>
       </c>
       <c r="W57">
-        <v>0.1000994919057341</v>
+        <v>0.1005005321295904</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9162314726932868</v>
+        <v>0.8998701963951924</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09973146725135718</v>
+        <v>0.1004990446957741</v>
       </c>
       <c r="C58">
-        <v>427.4657581004358</v>
+        <v>288.8766538123118</v>
       </c>
       <c r="D58">
-        <v>5099.640394295094</v>
+        <v>5046.122265653303</v>
       </c>
       <c r="E58">
-        <v>3203.57707156134</v>
+        <v>3288.648047207673</v>
       </c>
       <c r="F58">
-        <v>4763.974636194658</v>
+        <v>4849.045611840991</v>
       </c>
       <c r="G58">
         <v>91.8</v>
@@ -6049,37 +6049,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M58">
-        <v>583.8619859894352</v>
+        <v>594.2880928821036</v>
       </c>
       <c r="N58">
-        <v>-58.46198598943511</v>
+        <v>-68.88809288210348</v>
       </c>
       <c r="O58">
-        <v>-11.69239719788702</v>
+        <v>-13.7776185764207</v>
       </c>
       <c r="P58">
-        <v>-46.76958879154809</v>
+        <v>-55.11047430568279</v>
       </c>
       <c r="Q58">
-        <v>265.4304112084519</v>
+        <v>257.0895256943172</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09875265740633302</v>
+        <v>0.0999841145553175</v>
       </c>
       <c r="T58">
-        <v>1.088762369911799</v>
+        <v>1.114082425026027</v>
       </c>
       <c r="U58">
         <v>0.1225577444416894</v>
       </c>
       <c r="V58">
-        <v>0.1799740392790385</v>
+        <v>0.1768165999934413</v>
       </c>
       <c r="W58">
-        <v>0.1005005321295904</v>
+        <v>0.1008875007666448</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8998701963951924</v>
+        <v>0.8840829999672066</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1004990446957741</v>
+        <v>0.101266622140191</v>
       </c>
       <c r="C59">
-        <v>288.8766538123118</v>
+        <v>151.3991745908588</v>
       </c>
       <c r="D59">
-        <v>5046.122265653303</v>
+        <v>4993.715762078184</v>
       </c>
       <c r="E59">
-        <v>3288.648047207673</v>
+        <v>3373.719022854007</v>
       </c>
       <c r="F59">
-        <v>4849.045611840991</v>
+        <v>4934.116587487325</v>
       </c>
       <c r="G59">
         <v>91.8</v>
@@ -6131,37 +6131,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M59">
-        <v>594.2880928821036</v>
+        <v>604.7141997747722</v>
       </c>
       <c r="N59">
-        <v>-68.88809288210348</v>
+        <v>-79.31419977477208</v>
       </c>
       <c r="O59">
-        <v>-13.7776185764207</v>
+        <v>-15.86283995495442</v>
       </c>
       <c r="P59">
-        <v>-55.11047430568279</v>
+        <v>-63.45135981981766</v>
       </c>
       <c r="Q59">
-        <v>257.0895256943172</v>
+        <v>248.7486401801823</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.0999841145553175</v>
+        <v>0.1012742125209203</v>
       </c>
       <c r="T59">
-        <v>1.114082425026027</v>
+        <v>1.140608197050457</v>
       </c>
       <c r="U59">
         <v>0.1225577444416894</v>
       </c>
       <c r="V59">
-        <v>0.1768165999934413</v>
+        <v>0.1737680379245889</v>
       </c>
       <c r="W59">
-        <v>0.1008875007666448</v>
+        <v>0.1012611256575938</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8840829999672066</v>
+        <v>0.8688401896229443</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1012666221401909</v>
+        <v>0.1020341995846079</v>
       </c>
       <c r="C60">
-        <v>151.3991745908615</v>
+        <v>14.99904208697353</v>
       </c>
       <c r="D60">
-        <v>4993.715762078185</v>
+        <v>4942.38660522063</v>
       </c>
       <c r="E60">
-        <v>3373.719022854006</v>
+        <v>3458.789998500339</v>
       </c>
       <c r="F60">
-        <v>4934.116587487324</v>
+        <v>5019.187563133657</v>
       </c>
       <c r="G60">
         <v>91.8</v>
@@ -6213,37 +6213,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M60">
-        <v>604.7141997747721</v>
+        <v>615.1403066674405</v>
       </c>
       <c r="N60">
-        <v>-79.31419977477196</v>
+        <v>-89.74030666744045</v>
       </c>
       <c r="O60">
-        <v>-15.86283995495439</v>
+        <v>-17.94806133348809</v>
       </c>
       <c r="P60">
-        <v>-63.45135981981757</v>
+        <v>-71.79224533395237</v>
       </c>
       <c r="Q60">
-        <v>248.7486401801824</v>
+        <v>240.4077546660476</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1012742125209203</v>
+        <v>0.1026272420946013</v>
       </c>
       <c r="T60">
-        <v>1.140608197050456</v>
+        <v>1.168427909173638</v>
       </c>
       <c r="U60">
         <v>0.1225577444416894</v>
       </c>
       <c r="V60">
-        <v>0.1737680379245889</v>
+        <v>0.1708228169428162</v>
       </c>
       <c r="W60">
-        <v>0.1012611256575938</v>
+        <v>0.1016220852980022</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8688401896229445</v>
+        <v>0.854114084714081</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1020341995846079</v>
+        <v>0.1028017770290247</v>
       </c>
       <c r="C61">
-        <v>14.99904208697353</v>
+        <v>-120.3566270331194</v>
       </c>
       <c r="D61">
-        <v>4942.38660522063</v>
+        <v>4892.10191174687</v>
       </c>
       <c r="E61">
-        <v>3458.789998500339</v>
+        <v>3543.860974146672</v>
       </c>
       <c r="F61">
-        <v>5019.187563133657</v>
+        <v>5104.25853877999</v>
       </c>
       <c r="G61">
         <v>91.8</v>
@@ -6295,37 +6295,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M61">
-        <v>615.1403066674405</v>
+        <v>625.566413560109</v>
       </c>
       <c r="N61">
-        <v>-89.74030666744045</v>
+        <v>-100.1664135601089</v>
       </c>
       <c r="O61">
-        <v>-17.94806133348809</v>
+        <v>-20.03328271202179</v>
       </c>
       <c r="P61">
-        <v>-71.79224533395237</v>
+        <v>-80.13313084808715</v>
       </c>
       <c r="Q61">
-        <v>240.4077546660476</v>
+        <v>232.0668691519128</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1026272420946013</v>
+        <v>0.1040479231469663</v>
       </c>
       <c r="T61">
-        <v>1.168427909173638</v>
+        <v>1.197638606902979</v>
       </c>
       <c r="U61">
         <v>0.1225577444416894</v>
       </c>
       <c r="V61">
-        <v>0.1708228169428162</v>
+        <v>0.1679757699937693</v>
       </c>
       <c r="W61">
-        <v>0.1016220852980022</v>
+        <v>0.101971012950397</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.854114084714081</v>
+        <v>0.8398788499688463</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1028017770290247</v>
+        <v>0.1035693544734416</v>
       </c>
       <c r="C62">
-        <v>-120.3566270331194</v>
+        <v>-254.6993913387496</v>
       </c>
       <c r="D62">
-        <v>4892.10191174687</v>
+        <v>4842.830123087574</v>
       </c>
       <c r="E62">
-        <v>3543.860974146672</v>
+        <v>3628.931949793006</v>
       </c>
       <c r="F62">
-        <v>5104.25853877999</v>
+        <v>5189.329514426324</v>
       </c>
       <c r="G62">
         <v>91.8</v>
@@ -6377,37 +6377,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M62">
-        <v>625.566413560109</v>
+        <v>635.9925204527775</v>
       </c>
       <c r="N62">
-        <v>-100.1664135601089</v>
+        <v>-110.5925204527774</v>
       </c>
       <c r="O62">
-        <v>-20.03328271202179</v>
+        <v>-22.11850409055549</v>
       </c>
       <c r="P62">
-        <v>-80.13313084808715</v>
+        <v>-88.47401636222193</v>
       </c>
       <c r="Q62">
-        <v>232.0668691519128</v>
+        <v>223.7259836377781</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1040479231469663</v>
+        <v>0.1055414596379142</v>
       </c>
       <c r="T62">
-        <v>1.197638606902979</v>
+        <v>1.228347289131261</v>
       </c>
       <c r="U62">
         <v>0.1225577444416894</v>
       </c>
       <c r="V62">
-        <v>0.1679757699937693</v>
+        <v>0.1652220688463304</v>
       </c>
       <c r="W62">
-        <v>0.101971012950397</v>
+        <v>0.1023085003518936</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8398788499688463</v>
+        <v>0.8261103442316522</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1035693544734416</v>
+        <v>0.1043369319178585</v>
       </c>
       <c r="C63">
-        <v>-254.6993913387496</v>
+        <v>-388.0595506827285</v>
       </c>
       <c r="D63">
-        <v>4842.830123087574</v>
+        <v>4794.540939389928</v>
       </c>
       <c r="E63">
-        <v>3628.931949793006</v>
+        <v>3714.002925439338</v>
       </c>
       <c r="F63">
-        <v>5189.329514426324</v>
+        <v>5274.400490072657</v>
       </c>
       <c r="G63">
         <v>91.8</v>
@@ -6459,37 +6459,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M63">
-        <v>635.9925204527775</v>
+        <v>646.418627345446</v>
       </c>
       <c r="N63">
-        <v>-110.5925204527774</v>
+        <v>-121.0186273454459</v>
       </c>
       <c r="O63">
-        <v>-22.11850409055549</v>
+        <v>-24.20372546908918</v>
       </c>
       <c r="P63">
-        <v>-88.47401636222193</v>
+        <v>-96.81490187635673</v>
       </c>
       <c r="Q63">
-        <v>223.7259836377781</v>
+        <v>215.3850981236433</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1055414596379142</v>
+        <v>0.1071136033125961</v>
       </c>
       <c r="T63">
-        <v>1.228347289131261</v>
+        <v>1.26067221779261</v>
       </c>
       <c r="U63">
         <v>0.1225577444416894</v>
       </c>
       <c r="V63">
-        <v>0.1652220688463304</v>
+        <v>0.1625571967681638</v>
       </c>
       <c r="W63">
-        <v>0.1023085003518936</v>
+        <v>0.1026351010630194</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8261103442316522</v>
+        <v>0.812785983840819</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1043369319178585</v>
+        <v>0.1233589867728506</v>
       </c>
       <c r="C64">
-        <v>-388.0595506827285</v>
+        <v>-1423.142346598371</v>
       </c>
       <c r="D64">
-        <v>4794.540939389928</v>
+        <v>3844.529119120618</v>
       </c>
       <c r="E64">
-        <v>3714.002925439338</v>
+        <v>3799.073901085671</v>
       </c>
       <c r="F64">
-        <v>5274.400490072657</v>
+        <v>5359.47146571899</v>
       </c>
       <c r="G64">
         <v>91.8</v>
@@ -6541,45 +6541,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M64">
-        <v>646.418627345446</v>
+        <v>807.98182957139</v>
       </c>
       <c r="N64">
-        <v>-121.0186273454459</v>
+        <v>-282.5818295713899</v>
       </c>
       <c r="O64">
-        <v>-24.20372546908918</v>
+        <v>-56.51636591427798</v>
       </c>
       <c r="P64">
-        <v>-96.81490187635673</v>
+        <v>-226.0654636571119</v>
       </c>
       <c r="Q64">
-        <v>215.3850981236433</v>
+        <v>86.13453634288805</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1071136033125961</v>
+        <v>0.1100909369442208</v>
       </c>
       <c r="T64">
-        <v>1.26067221779261</v>
+        <v>1.321889330956757</v>
       </c>
       <c r="U64">
-        <v>0.1225577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V64">
-        <v>0.1625571967681638</v>
+        <v>0.1300524295895884</v>
       </c>
       <c r="W64">
-        <v>0.1026351010630194</v>
+        <v>0.1311513334976014</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.812785983840819</v>
+        <v>0.650262147947942</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1233589867728506</v>
+        <v>0.1595284372623487</v>
       </c>
       <c r="C65">
-        <v>-1423.142346598371</v>
+        <v>-2560.298534903391</v>
       </c>
       <c r="D65">
-        <v>3844.529119120618</v>
+        <v>2792.443906461932</v>
       </c>
       <c r="E65">
-        <v>3799.073901085671</v>
+        <v>3884.144876732004</v>
       </c>
       <c r="F65">
-        <v>5359.47146571899</v>
+        <v>5444.542441365323</v>
       </c>
       <c r="G65">
         <v>91.8</v>
@@ -6623,45 +6623,45 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M65">
-        <v>807.98182957139</v>
+        <v>1114.812229811012</v>
       </c>
       <c r="N65">
-        <v>-282.5818295713899</v>
+        <v>-589.4122298110124</v>
       </c>
       <c r="O65">
-        <v>-56.51636591427798</v>
+        <v>-117.8824459622025</v>
       </c>
       <c r="P65">
-        <v>-226.0654636571119</v>
+        <v>-471.5297838488099</v>
       </c>
       <c r="Q65">
-        <v>86.13453634288805</v>
+        <v>-159.3297838488099</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1100909369442208</v>
+        <v>0.1134319992067859</v>
       </c>
       <c r="T65">
-        <v>1.321889330956757</v>
+        <v>1.390585087604057</v>
       </c>
       <c r="U65">
-        <v>0.1507577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V65">
-        <v>0.1300524295895884</v>
+        <v>0.09425802587204629</v>
       </c>
       <c r="W65">
-        <v>0.1311513334976014</v>
+        <v>0.1854576836686028</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.650262147947942</v>
+        <v>0.4712901293602314</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1595284372623487</v>
+        <v>0.1611180147067656</v>
       </c>
       <c r="C66">
-        <v>-2560.298534903391</v>
+        <v>-2678.554372670352</v>
       </c>
       <c r="D66">
-        <v>2792.443906461932</v>
+        <v>2759.259044341304</v>
       </c>
       <c r="E66">
-        <v>3884.144876732004</v>
+        <v>3969.215852378338</v>
       </c>
       <c r="F66">
-        <v>5444.542441365323</v>
+        <v>5529.613417011657</v>
       </c>
       <c r="G66">
         <v>91.8</v>
@@ -6705,37 +6705,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M66">
-        <v>1114.812229811012</v>
+        <v>1132.23117090181</v>
       </c>
       <c r="N66">
-        <v>-589.4122298110124</v>
+        <v>-606.8311709018096</v>
       </c>
       <c r="O66">
-        <v>-117.8824459622025</v>
+        <v>-121.3662341803619</v>
       </c>
       <c r="P66">
-        <v>-471.5297838488099</v>
+        <v>-485.4649367214477</v>
       </c>
       <c r="Q66">
-        <v>-159.3297838488099</v>
+        <v>-173.2649367214477</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1134319992067859</v>
+        <v>0.1153643420412655</v>
       </c>
       <c r="T66">
-        <v>1.390585087604057</v>
+        <v>1.43031609010703</v>
       </c>
       <c r="U66">
         <v>0.2047577444416894</v>
       </c>
       <c r="V66">
-        <v>0.09425802587204629</v>
+        <v>0.09280790239709172</v>
       </c>
       <c r="W66">
-        <v>0.1854576836686028</v>
+        <v>0.1857546076804965</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4712901293602314</v>
+        <v>0.4640395119854586</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1611180147067656</v>
+        <v>0.1627075921511825</v>
       </c>
       <c r="C67">
-        <v>-2678.554372670352</v>
+        <v>-2796.030748473865</v>
       </c>
       <c r="D67">
-        <v>2759.259044341304</v>
+        <v>2726.853644184124</v>
       </c>
       <c r="E67">
-        <v>3969.215852378338</v>
+        <v>4054.286828024671</v>
       </c>
       <c r="F67">
-        <v>5529.613417011657</v>
+        <v>5614.68439265799</v>
       </c>
       <c r="G67">
         <v>91.8</v>
@@ -6787,37 +6787,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M67">
-        <v>1132.23117090181</v>
+        <v>1149.650111992607</v>
       </c>
       <c r="N67">
-        <v>-606.8311709018096</v>
+        <v>-624.2501119926067</v>
       </c>
       <c r="O67">
-        <v>-121.3662341803619</v>
+        <v>-124.8500223985213</v>
       </c>
       <c r="P67">
-        <v>-485.4649367214477</v>
+        <v>-499.4000895940853</v>
       </c>
       <c r="Q67">
-        <v>-173.2649367214477</v>
+        <v>-187.2000895940853</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1153643420412655</v>
+        <v>0.1174103521013027</v>
       </c>
       <c r="T67">
-        <v>1.43031609010703</v>
+        <v>1.472384210404295</v>
       </c>
       <c r="U67">
         <v>0.2047577444416894</v>
       </c>
       <c r="V67">
-        <v>0.09280790239709172</v>
+        <v>0.09140172205774184</v>
       </c>
       <c r="W67">
-        <v>0.1857546076804965</v>
+        <v>0.18604253399506</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4640395119854586</v>
+        <v>0.4570086102887092</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1627075921511825</v>
+        <v>0.1642971695955994</v>
       </c>
       <c r="C68">
-        <v>-2796.030748473865</v>
+        <v>-2912.754806095718</v>
       </c>
       <c r="D68">
-        <v>2726.853644184124</v>
+        <v>2695.200562208604</v>
       </c>
       <c r="E68">
-        <v>4054.286828024671</v>
+        <v>4139.357803671004</v>
       </c>
       <c r="F68">
-        <v>5614.68439265799</v>
+        <v>5699.755368304322</v>
       </c>
       <c r="G68">
         <v>91.8</v>
@@ -6869,37 +6869,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M68">
-        <v>1149.650111992607</v>
+        <v>1167.069053083404</v>
       </c>
       <c r="N68">
-        <v>-624.2501119926067</v>
+        <v>-641.6690530834037</v>
       </c>
       <c r="O68">
-        <v>-124.8500223985213</v>
+        <v>-128.3338106166808</v>
       </c>
       <c r="P68">
-        <v>-499.4000895940853</v>
+        <v>-513.335242466723</v>
       </c>
       <c r="Q68">
-        <v>-187.2000895940853</v>
+        <v>-201.135242466723</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1174103521013027</v>
+        <v>0.1195803627710392</v>
       </c>
       <c r="T68">
-        <v>1.472384210404295</v>
+        <v>1.51700191374988</v>
       </c>
       <c r="U68">
         <v>0.2047577444416894</v>
       </c>
       <c r="V68">
-        <v>0.09140172205774184</v>
+        <v>0.09003751725090987</v>
       </c>
       <c r="W68">
-        <v>0.18604253399506</v>
+        <v>0.1863218654942634</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4570086102887092</v>
+        <v>0.4501875862545494</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1642971695955994</v>
+        <v>0.1658867470400163</v>
       </c>
       <c r="C69">
-        <v>-2912.754806095718</v>
+        <v>-3028.752443448919</v>
       </c>
       <c r="D69">
-        <v>2695.200562208604</v>
+        <v>2664.273900501737</v>
       </c>
       <c r="E69">
-        <v>4139.357803671004</v>
+        <v>4224.428779317338</v>
       </c>
       <c r="F69">
-        <v>5699.755368304322</v>
+        <v>5784.826343950656</v>
       </c>
       <c r="G69">
         <v>91.8</v>
@@ -6951,37 +6951,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M69">
-        <v>1167.069053083404</v>
+        <v>1184.487994174201</v>
       </c>
       <c r="N69">
-        <v>-641.6690530834037</v>
+        <v>-659.0879941742007</v>
       </c>
       <c r="O69">
-        <v>-128.3338106166808</v>
+        <v>-131.8175988348401</v>
       </c>
       <c r="P69">
-        <v>-513.335242466723</v>
+        <v>-527.2703953393606</v>
       </c>
       <c r="Q69">
-        <v>-201.135242466723</v>
+        <v>-215.0703953393606</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1195803627710392</v>
+        <v>0.1218859991076342</v>
       </c>
       <c r="T69">
-        <v>1.51700191374988</v>
+        <v>1.564408223554564</v>
       </c>
       <c r="U69">
         <v>0.2047577444416894</v>
       </c>
       <c r="V69">
-        <v>0.09003751725090987</v>
+        <v>0.08871343611486709</v>
       </c>
       <c r="W69">
-        <v>0.1863218654942634</v>
+        <v>0.1865929813611373</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4501875862545494</v>
+        <v>0.4435671805743354</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1658867470400163</v>
+        <v>0.1674763244844332</v>
       </c>
       <c r="C70">
-        <v>-3028.752443448919</v>
+        <v>-3144.048383246743</v>
       </c>
       <c r="D70">
-        <v>2664.273900501737</v>
+        <v>2634.048936350246</v>
       </c>
       <c r="E70">
-        <v>4224.428779317338</v>
+        <v>4309.499754963671</v>
       </c>
       <c r="F70">
-        <v>5784.826343950656</v>
+        <v>5869.897319596989</v>
       </c>
       <c r="G70">
         <v>91.8</v>
@@ -7033,37 +7033,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M70">
-        <v>1184.487994174201</v>
+        <v>1201.906935264998</v>
       </c>
       <c r="N70">
-        <v>-659.0879941742007</v>
+        <v>-676.5069352649978</v>
       </c>
       <c r="O70">
-        <v>-131.8175988348401</v>
+        <v>-135.3013870529996</v>
       </c>
       <c r="P70">
-        <v>-527.2703953393606</v>
+        <v>-541.2055482119982</v>
       </c>
       <c r="Q70">
-        <v>-215.0703953393606</v>
+        <v>-229.0055482119982</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1218859991076342</v>
+        <v>0.1243403861756224</v>
       </c>
       <c r="T70">
-        <v>1.564408223554564</v>
+        <v>1.61487300495955</v>
       </c>
       <c r="U70">
         <v>0.2047577444416894</v>
       </c>
       <c r="V70">
-        <v>0.08871343611486709</v>
+        <v>0.08742773414218785</v>
       </c>
       <c r="W70">
-        <v>0.1865929813611373</v>
+        <v>0.1868562387970873</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4435671805743354</v>
+        <v>0.4371386707109393</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1674763244844332</v>
+        <v>0.1690659019288501</v>
       </c>
       <c r="C71">
-        <v>-3144.048383246743</v>
+        <v>-3258.666238915498</v>
       </c>
       <c r="D71">
-        <v>2634.048936350246</v>
+        <v>2604.502056327824</v>
       </c>
       <c r="E71">
-        <v>4309.499754963671</v>
+        <v>4394.570730610004</v>
       </c>
       <c r="F71">
-        <v>5869.897319596989</v>
+        <v>5954.968295243322</v>
       </c>
       <c r="G71">
         <v>91.8</v>
@@ -7115,37 +7115,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M71">
-        <v>1201.906935264998</v>
+        <v>1219.325876355795</v>
       </c>
       <c r="N71">
-        <v>-676.5069352649978</v>
+        <v>-693.9258763557948</v>
       </c>
       <c r="O71">
-        <v>-135.3013870529996</v>
+        <v>-138.785175271159</v>
       </c>
       <c r="P71">
-        <v>-541.2055482119982</v>
+        <v>-555.1407010846358</v>
       </c>
       <c r="Q71">
-        <v>-229.0055482119982</v>
+        <v>-242.9407010846358</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1243403861756224</v>
+        <v>0.1269583990481431</v>
       </c>
       <c r="T71">
-        <v>1.61487300495955</v>
+        <v>1.668702105124868</v>
       </c>
       <c r="U71">
         <v>0.2047577444416894</v>
       </c>
       <c r="V71">
-        <v>0.08742773414218785</v>
+        <v>0.08617876651158518</v>
       </c>
       <c r="W71">
-        <v>0.1868562387970873</v>
+        <v>0.1871119745920102</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4371386707109393</v>
+        <v>0.4308938325579259</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1690659019288501</v>
+        <v>0.170655479373267</v>
       </c>
       <c r="C72">
-        <v>-3258.666238915498</v>
+        <v>-3372.628576120309</v>
       </c>
       <c r="D72">
-        <v>2604.502056327824</v>
+        <v>2575.610694769347</v>
       </c>
       <c r="E72">
-        <v>4394.570730610004</v>
+        <v>4479.641706256338</v>
       </c>
       <c r="F72">
-        <v>5954.968295243322</v>
+        <v>6040.039270889656</v>
       </c>
       <c r="G72">
         <v>91.8</v>
@@ -7197,37 +7197,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M72">
-        <v>1219.325876355795</v>
+        <v>1236.744817446592</v>
       </c>
       <c r="N72">
-        <v>-693.9258763557948</v>
+        <v>-711.3448174465921</v>
       </c>
       <c r="O72">
-        <v>-138.785175271159</v>
+        <v>-142.2689634893184</v>
       </c>
       <c r="P72">
-        <v>-555.1407010846358</v>
+        <v>-569.0758539572737</v>
       </c>
       <c r="Q72">
-        <v>-242.9407010846358</v>
+        <v>-256.8758539572737</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1269583990481431</v>
+        <v>0.1297569645325619</v>
       </c>
       <c r="T72">
-        <v>1.668702105124868</v>
+        <v>1.726243557025726</v>
       </c>
       <c r="U72">
         <v>0.2047577444416894</v>
       </c>
       <c r="V72">
-        <v>0.08617876651158518</v>
+        <v>0.08496498106776001</v>
       </c>
       <c r="W72">
-        <v>0.1871119745920102</v>
+        <v>0.187360506561724</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4308938325579259</v>
+        <v>0.4248249053388001</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.170655479373267</v>
+        <v>0.1722450568176839</v>
       </c>
       <c r="C73">
-        <v>-3372.628576120307</v>
+        <v>-3485.956970240858</v>
       </c>
       <c r="D73">
-        <v>2575.610694769348</v>
+        <v>2547.35327629513</v>
       </c>
       <c r="E73">
-        <v>4479.641706256337</v>
+        <v>4564.71268190267</v>
       </c>
       <c r="F73">
-        <v>6040.039270889655</v>
+        <v>6125.110246535988</v>
       </c>
       <c r="G73">
         <v>91.8</v>
@@ -7279,37 +7279,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M73">
-        <v>1236.744817446592</v>
+        <v>1254.163758537389</v>
       </c>
       <c r="N73">
-        <v>-711.3448174465918</v>
+        <v>-728.7637585373889</v>
       </c>
       <c r="O73">
-        <v>-142.2689634893184</v>
+        <v>-145.7527517074778</v>
       </c>
       <c r="P73">
-        <v>-569.0758539572735</v>
+        <v>-583.0110068299111</v>
       </c>
       <c r="Q73">
-        <v>-256.8758539572735</v>
+        <v>-270.8110068299112</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1297569645325618</v>
+        <v>0.1327554275515819</v>
       </c>
       <c r="T73">
-        <v>1.726243557025725</v>
+        <v>1.787895112633787</v>
       </c>
       <c r="U73">
         <v>0.2047577444416894</v>
       </c>
       <c r="V73">
-        <v>0.08496498106776003</v>
+        <v>0.08378491188626337</v>
       </c>
       <c r="W73">
-        <v>0.187360506561724</v>
+        <v>0.1876021348656124</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4248249053388001</v>
+        <v>0.4189245594313168</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1722450568176839</v>
+        <v>0.1738346342621007</v>
       </c>
       <c r="C74">
-        <v>-3485.956970240858</v>
+        <v>-3598.672060104739</v>
       </c>
       <c r="D74">
-        <v>2547.35327629513</v>
+        <v>2519.709162077582</v>
       </c>
       <c r="E74">
-        <v>4564.71268190267</v>
+        <v>4649.783657549003</v>
       </c>
       <c r="F74">
-        <v>6125.110246535988</v>
+        <v>6210.181222182321</v>
       </c>
       <c r="G74">
         <v>91.8</v>
@@ -7361,37 +7361,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M74">
-        <v>1254.163758537389</v>
+        <v>1271.582699628186</v>
       </c>
       <c r="N74">
-        <v>-728.7637585373889</v>
+        <v>-746.1826996281859</v>
       </c>
       <c r="O74">
-        <v>-145.7527517074778</v>
+        <v>-149.2365399256372</v>
       </c>
       <c r="P74">
-        <v>-583.0110068299111</v>
+        <v>-596.9461597025487</v>
       </c>
       <c r="Q74">
-        <v>-270.8110068299112</v>
+        <v>-284.7461597025487</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1327554275515819</v>
+        <v>0.1359759989423812</v>
       </c>
       <c r="T74">
-        <v>1.787895112633787</v>
+        <v>1.854113450138742</v>
       </c>
       <c r="U74">
         <v>0.2047577444416894</v>
       </c>
       <c r="V74">
-        <v>0.08378491188626337</v>
+        <v>0.08263717336727347</v>
       </c>
       <c r="W74">
-        <v>0.1876021348656124</v>
+        <v>0.1878371432159696</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4189245594313168</v>
+        <v>0.4131858668363673</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1738346342621007</v>
+        <v>0.1754242117065177</v>
       </c>
       <c r="C75">
-        <v>-3598.672060104739</v>
+        <v>-3710.793598259647</v>
       </c>
       <c r="D75">
-        <v>2519.709162077582</v>
+        <v>2492.658599569007</v>
       </c>
       <c r="E75">
-        <v>4649.783657549003</v>
+        <v>4734.854633195337</v>
       </c>
       <c r="F75">
-        <v>6210.181222182321</v>
+        <v>6295.252197828655</v>
       </c>
       <c r="G75">
         <v>91.8</v>
@@ -7443,37 +7443,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M75">
-        <v>1271.582699628186</v>
+        <v>1289.001640718983</v>
       </c>
       <c r="N75">
-        <v>-746.1826996281859</v>
+        <v>-763.6016407189832</v>
       </c>
       <c r="O75">
-        <v>-149.2365399256372</v>
+        <v>-152.7203281437966</v>
       </c>
       <c r="P75">
-        <v>-596.9461597025487</v>
+        <v>-610.8813125751865</v>
       </c>
       <c r="Q75">
-        <v>-284.7461597025487</v>
+        <v>-298.6813125751865</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1359759989423812</v>
+        <v>0.1394443065940113</v>
       </c>
       <c r="T75">
-        <v>1.854113450138742</v>
+        <v>1.925425505913309</v>
       </c>
       <c r="U75">
         <v>0.2047577444416894</v>
       </c>
       <c r="V75">
-        <v>0.08263717336727347</v>
+        <v>0.08152045480825625</v>
       </c>
       <c r="W75">
-        <v>0.1878371432159696</v>
+        <v>0.1880657999892902</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4131858668363673</v>
+        <v>0.4076022740412812</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1754242117065177</v>
+        <v>0.1770137891509345</v>
       </c>
       <c r="C76">
-        <v>-3710.793598259647</v>
+        <v>-3822.340498041749</v>
       </c>
       <c r="D76">
-        <v>2492.658599569007</v>
+        <v>2466.182675433239</v>
       </c>
       <c r="E76">
-        <v>4734.854633195337</v>
+        <v>4819.92560884167</v>
       </c>
       <c r="F76">
-        <v>6295.252197828655</v>
+        <v>6380.323173474988</v>
       </c>
       <c r="G76">
         <v>91.8</v>
@@ -7525,37 +7525,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M76">
-        <v>1289.001640718983</v>
+        <v>1306.42058180978</v>
       </c>
       <c r="N76">
-        <v>-763.6016407189832</v>
+        <v>-781.0205818097802</v>
       </c>
       <c r="O76">
-        <v>-152.7203281437966</v>
+        <v>-156.204116361956</v>
       </c>
       <c r="P76">
-        <v>-610.8813125751865</v>
+        <v>-624.8164654478242</v>
       </c>
       <c r="Q76">
-        <v>-298.6813125751865</v>
+        <v>-312.6164654478242</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1394443065940113</v>
+        <v>0.1431900788577717</v>
       </c>
       <c r="T76">
-        <v>1.925425505913309</v>
+        <v>2.002442526149841</v>
       </c>
       <c r="U76">
         <v>0.2047577444416894</v>
       </c>
       <c r="V76">
-        <v>0.08152045480825625</v>
+        <v>0.08043351541081284</v>
       </c>
       <c r="W76">
-        <v>0.1880657999892902</v>
+        <v>0.1882883592486555</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4076022740412812</v>
+        <v>0.4021675770540641</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1770137891509345</v>
+        <v>0.1786033665953514</v>
       </c>
       <c r="C77">
-        <v>-3822.340498041749</v>
+        <v>-3933.330877675962</v>
       </c>
       <c r="D77">
-        <v>2466.182675433239</v>
+        <v>2440.263271445359</v>
       </c>
       <c r="E77">
-        <v>4819.92560884167</v>
+        <v>4904.996584488003</v>
       </c>
       <c r="F77">
-        <v>6380.323173474988</v>
+        <v>6465.394149121321</v>
       </c>
       <c r="G77">
         <v>91.8</v>
@@ -7607,37 +7607,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M77">
-        <v>1306.42058180978</v>
+        <v>1323.839522900577</v>
       </c>
       <c r="N77">
-        <v>-781.0205818097802</v>
+        <v>-798.4395229005772</v>
       </c>
       <c r="O77">
-        <v>-156.204116361956</v>
+        <v>-159.6879045801155</v>
       </c>
       <c r="P77">
-        <v>-624.8164654478242</v>
+        <v>-638.7516183204618</v>
       </c>
       <c r="Q77">
-        <v>-312.6164654478242</v>
+        <v>-326.5516183204618</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1431900788577717</v>
+        <v>0.1472479988101789</v>
       </c>
       <c r="T77">
-        <v>2.002442526149841</v>
+        <v>2.085877631406085</v>
       </c>
       <c r="U77">
         <v>0.2047577444416894</v>
       </c>
       <c r="V77">
-        <v>0.08043351541081284</v>
+        <v>0.0793751796817232</v>
       </c>
       <c r="W77">
-        <v>0.1882883592486555</v>
+        <v>0.1885050616854059</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4021675770540641</v>
+        <v>0.3968758984086159</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1786033665953514</v>
+        <v>0.1801929440397684</v>
       </c>
       <c r="C78">
-        <v>-3933.330877675962</v>
+        <v>-4043.782101624191</v>
       </c>
       <c r="D78">
-        <v>2440.263271445359</v>
+        <v>2414.883023143464</v>
       </c>
       <c r="E78">
-        <v>4904.996584488003</v>
+        <v>4990.067560134336</v>
       </c>
       <c r="F78">
-        <v>6465.394149121321</v>
+        <v>6550.465124767655</v>
       </c>
       <c r="G78">
         <v>91.8</v>
@@ -7689,37 +7689,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M78">
-        <v>1323.839522900577</v>
+        <v>1341.258463991375</v>
       </c>
       <c r="N78">
-        <v>-798.4395229005772</v>
+        <v>-815.8584639913745</v>
       </c>
       <c r="O78">
-        <v>-159.6879045801155</v>
+        <v>-163.1716927982749</v>
       </c>
       <c r="P78">
-        <v>-638.7516183204618</v>
+        <v>-652.6867711930996</v>
       </c>
       <c r="Q78">
-        <v>-326.5516183204618</v>
+        <v>-340.4867711930996</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1472479988101789</v>
+        <v>0.1516587813671432</v>
       </c>
       <c r="T78">
-        <v>2.085877631406085</v>
+        <v>2.17656796320635</v>
       </c>
       <c r="U78">
         <v>0.2047577444416894</v>
       </c>
       <c r="V78">
-        <v>0.0793751796817232</v>
+        <v>0.07834433319235015</v>
       </c>
       <c r="W78">
-        <v>0.1885050616854059</v>
+        <v>0.1887161354874356</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3968758984086159</v>
+        <v>0.3917216659617507</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1801929440397684</v>
+        <v>0.1817825214841852</v>
       </c>
       <c r="C79">
-        <v>-4043.782101624191</v>
+        <v>-4153.710819379851</v>
       </c>
       <c r="D79">
-        <v>2414.883023143464</v>
+        <v>2390.025281034136</v>
       </c>
       <c r="E79">
-        <v>4990.067560134336</v>
+        <v>5075.138535780669</v>
       </c>
       <c r="F79">
-        <v>6550.465124767655</v>
+        <v>6635.536100413988</v>
       </c>
       <c r="G79">
         <v>91.8</v>
@@ -7771,37 +7771,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M79">
-        <v>1341.258463991375</v>
+        <v>1358.677405082172</v>
       </c>
       <c r="N79">
-        <v>-815.8584639913745</v>
+        <v>-833.2774050821715</v>
       </c>
       <c r="O79">
-        <v>-163.1716927982749</v>
+        <v>-166.6554810164343</v>
       </c>
       <c r="P79">
-        <v>-652.6867711930996</v>
+        <v>-666.6219240657372</v>
       </c>
       <c r="Q79">
-        <v>-340.4867711930996</v>
+        <v>-354.4219240657372</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1516587813671432</v>
+        <v>0.1564705441565588</v>
       </c>
       <c r="T79">
-        <v>2.17656796320635</v>
+        <v>2.27550287062482</v>
       </c>
       <c r="U79">
         <v>0.2047577444416894</v>
       </c>
       <c r="V79">
-        <v>0.07834433319235015</v>
+        <v>0.0773399186642431</v>
       </c>
       <c r="W79">
-        <v>0.1887161354874356</v>
+        <v>0.1889217971406953</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3917216659617507</v>
+        <v>0.3866995933212155</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1817825214841852</v>
+        <v>0.1833720989286021</v>
       </c>
       <c r="C80">
-        <v>-4153.710819379851</v>
+        <v>-4263.133001890805</v>
       </c>
       <c r="D80">
-        <v>2390.025281034136</v>
+        <v>2365.674074169516</v>
       </c>
       <c r="E80">
-        <v>5075.138535780669</v>
+        <v>5160.209511427002</v>
       </c>
       <c r="F80">
-        <v>6635.536100413988</v>
+        <v>6720.607076060321</v>
       </c>
       <c r="G80">
         <v>91.8</v>
@@ -7853,37 +7853,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M80">
-        <v>1358.677405082172</v>
+        <v>1376.096346172969</v>
       </c>
       <c r="N80">
-        <v>-833.2774050821715</v>
+        <v>-850.6963461729686</v>
       </c>
       <c r="O80">
-        <v>-166.6554810164343</v>
+        <v>-170.1392692345937</v>
       </c>
       <c r="P80">
-        <v>-666.6219240657372</v>
+        <v>-680.5570769383748</v>
       </c>
       <c r="Q80">
-        <v>-354.4219240657372</v>
+        <v>-368.3570769383749</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1564705441565588</v>
+        <v>0.1617405700687759</v>
       </c>
       <c r="T80">
-        <v>2.27550287062482</v>
+        <v>2.383860150178383</v>
       </c>
       <c r="U80">
         <v>0.2047577444416894</v>
       </c>
       <c r="V80">
-        <v>0.0773399186642431</v>
+        <v>0.0763609323520375</v>
       </c>
       <c r="W80">
-        <v>0.1889217971406953</v>
+        <v>0.1891222521698218</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3866995933212155</v>
+        <v>0.3818046617601875</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1833720989286021</v>
+        <v>0.184961676373019</v>
       </c>
       <c r="C81">
-        <v>-4263.133001890805</v>
+        <v>-4372.063975778137</v>
       </c>
       <c r="D81">
-        <v>2365.674074169516</v>
+        <v>2341.814075928517</v>
       </c>
       <c r="E81">
-        <v>5160.209511427002</v>
+        <v>5245.280487073336</v>
       </c>
       <c r="F81">
-        <v>6720.607076060321</v>
+        <v>6805.678051706655</v>
       </c>
       <c r="G81">
         <v>91.8</v>
@@ -7935,37 +7935,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M81">
-        <v>1376.096346172969</v>
+        <v>1393.515287263766</v>
       </c>
       <c r="N81">
-        <v>-850.6963461729686</v>
+        <v>-868.1152872637656</v>
       </c>
       <c r="O81">
-        <v>-170.1392692345937</v>
+        <v>-173.6230574527531</v>
       </c>
       <c r="P81">
-        <v>-680.5570769383748</v>
+        <v>-694.4922298110125</v>
       </c>
       <c r="Q81">
-        <v>-368.3570769383749</v>
+        <v>-382.2922298110125</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1617405700687759</v>
+        <v>0.1675375985722147</v>
       </c>
       <c r="T81">
-        <v>2.383860150178383</v>
+        <v>2.503053157687302</v>
       </c>
       <c r="U81">
         <v>0.2047577444416894</v>
       </c>
       <c r="V81">
-        <v>0.0763609323520375</v>
+        <v>0.07540642069763703</v>
       </c>
       <c r="W81">
-        <v>0.1891222521698218</v>
+        <v>0.1893176958232201</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3818046617601875</v>
+        <v>0.3770321034881851</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.184961676373019</v>
+        <v>0.1865512538174359</v>
       </c>
       <c r="C82">
-        <v>-4372.063975778137</v>
+        <v>-4480.518455504842</v>
       </c>
       <c r="D82">
-        <v>2341.814075928517</v>
+        <v>2318.430571848145</v>
       </c>
       <c r="E82">
-        <v>5245.280487073336</v>
+        <v>5330.351462719669</v>
       </c>
       <c r="F82">
-        <v>6805.678051706655</v>
+        <v>6890.749027352987</v>
       </c>
       <c r="G82">
         <v>91.8</v>
@@ -8017,37 +8017,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M82">
-        <v>1393.515287263766</v>
+        <v>1410.934228354563</v>
       </c>
       <c r="N82">
-        <v>-868.1152872637656</v>
+        <v>-885.5342283545626</v>
       </c>
       <c r="O82">
-        <v>-173.6230574527531</v>
+        <v>-177.1068456709125</v>
       </c>
       <c r="P82">
-        <v>-694.4922298110125</v>
+        <v>-708.4273826836501</v>
       </c>
       <c r="Q82">
-        <v>-382.2922298110125</v>
+        <v>-396.2273826836501</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1675375985722147</v>
+        <v>0.1739448406023313</v>
       </c>
       <c r="T82">
-        <v>2.503053157687302</v>
+        <v>2.634792797565581</v>
       </c>
       <c r="U82">
         <v>0.2047577444416894</v>
       </c>
       <c r="V82">
-        <v>0.07540642069763703</v>
+        <v>0.07447547723223411</v>
       </c>
       <c r="W82">
-        <v>0.1893176958232201</v>
+        <v>0.1895083137073987</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3770321034881851</v>
+        <v>0.3723773861611704</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1865512538174359</v>
+        <v>0.1881408312618528</v>
       </c>
       <c r="C83">
-        <v>-4480.518455504842</v>
+        <v>-4588.510573636307</v>
       </c>
       <c r="D83">
-        <v>2318.430571848145</v>
+        <v>2295.509429363014</v>
       </c>
       <c r="E83">
-        <v>5330.351462719669</v>
+        <v>5415.422438366002</v>
       </c>
       <c r="F83">
-        <v>6890.749027352987</v>
+        <v>6975.82000299932</v>
       </c>
       <c r="G83">
         <v>91.8</v>
@@ -8099,37 +8099,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M83">
-        <v>1410.934228354563</v>
+        <v>1428.35316944536</v>
       </c>
       <c r="N83">
-        <v>-885.5342283545626</v>
+        <v>-902.9531694453597</v>
       </c>
       <c r="O83">
-        <v>-177.1068456709125</v>
+        <v>-180.5906338890719</v>
       </c>
       <c r="P83">
-        <v>-708.4273826836501</v>
+        <v>-722.3625355562878</v>
       </c>
       <c r="Q83">
-        <v>-396.2273826836501</v>
+        <v>-410.1625355562878</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1739448406023313</v>
+        <v>0.1810639984135719</v>
       </c>
       <c r="T83">
-        <v>2.634792797565581</v>
+        <v>2.781170175208114</v>
       </c>
       <c r="U83">
         <v>0.2047577444416894</v>
       </c>
       <c r="V83">
-        <v>0.07447547723223411</v>
+        <v>0.07356723970501174</v>
       </c>
       <c r="W83">
-        <v>0.1895083137073987</v>
+        <v>0.1896942823748901</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3723773861611704</v>
+        <v>0.3678361985250587</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1881408312618528</v>
+        <v>0.1897304087062697</v>
       </c>
       <c r="C84">
-        <v>-4588.510573636307</v>
+        <v>-4696.053909323334</v>
       </c>
       <c r="D84">
-        <v>2295.509429363014</v>
+        <v>2273.03706932232</v>
       </c>
       <c r="E84">
-        <v>5415.422438366002</v>
+        <v>5500.493414012336</v>
       </c>
       <c r="F84">
-        <v>6975.82000299932</v>
+        <v>7060.890978645654</v>
       </c>
       <c r="G84">
         <v>91.8</v>
@@ -8181,37 +8181,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M84">
-        <v>1428.35316944536</v>
+        <v>1445.772110536157</v>
       </c>
       <c r="N84">
-        <v>-902.9531694453597</v>
+        <v>-920.3721105361569</v>
       </c>
       <c r="O84">
-        <v>-180.5906338890719</v>
+        <v>-184.0744221072314</v>
       </c>
       <c r="P84">
-        <v>-722.3625355562878</v>
+        <v>-736.2976884289255</v>
       </c>
       <c r="Q84">
-        <v>-410.1625355562878</v>
+        <v>-424.0976884289256</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1810639984135719</v>
+        <v>0.1890207042026056</v>
       </c>
       <c r="T84">
-        <v>2.781170175208114</v>
+        <v>2.944768420808591</v>
       </c>
       <c r="U84">
         <v>0.2047577444416894</v>
       </c>
       <c r="V84">
-        <v>0.07356723970501174</v>
+        <v>0.07268088741940917</v>
       </c>
       <c r="W84">
-        <v>0.1896942823748901</v>
+        <v>0.1898757698696708</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3678361985250587</v>
+        <v>0.3634044370970458</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1897304087062697</v>
+        <v>0.1913199861506866</v>
       </c>
       <c r="C85">
-        <v>-4696.053909323334</v>
+        <v>-4803.16151512835</v>
       </c>
       <c r="D85">
-        <v>2273.03706932232</v>
+        <v>2251.000439163637</v>
       </c>
       <c r="E85">
-        <v>5500.493414012336</v>
+        <v>5585.564389658669</v>
       </c>
       <c r="F85">
-        <v>7060.890978645654</v>
+        <v>7145.961954291987</v>
       </c>
       <c r="G85">
         <v>91.8</v>
@@ -8263,37 +8263,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M85">
-        <v>1445.772110536157</v>
+        <v>1463.191051626954</v>
       </c>
       <c r="N85">
-        <v>-920.3721105361569</v>
+        <v>-937.791051626954</v>
       </c>
       <c r="O85">
-        <v>-184.0744221072314</v>
+        <v>-187.5582103253908</v>
       </c>
       <c r="P85">
-        <v>-736.2976884289255</v>
+        <v>-750.2328413015632</v>
       </c>
       <c r="Q85">
-        <v>-424.0976884289256</v>
+        <v>-438.0328413015632</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1890207042026056</v>
+        <v>0.1979719982152685</v>
       </c>
       <c r="T85">
-        <v>2.944768420808591</v>
+        <v>3.128816447109129</v>
       </c>
       <c r="U85">
         <v>0.2047577444416894</v>
       </c>
       <c r="V85">
-        <v>0.07268088741940917</v>
+        <v>0.0718156387596543</v>
       </c>
       <c r="W85">
-        <v>0.1898757698696708</v>
+        <v>0.1900529362336234</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3634044370970458</v>
+        <v>0.3590781937982715</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1913199861506866</v>
+        <v>0.1929095635951035</v>
       </c>
       <c r="C86">
-        <v>-4803.161515128349</v>
+        <v>-4909.845942306152</v>
       </c>
       <c r="D86">
-        <v>2251.000439163637</v>
+        <v>2229.386987632167</v>
       </c>
       <c r="E86">
-        <v>5585.564389658668</v>
+        <v>5670.635365305001</v>
       </c>
       <c r="F86">
-        <v>7145.961954291986</v>
+        <v>7231.032929938319</v>
       </c>
       <c r="G86">
         <v>91.8</v>
@@ -8345,37 +8345,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M86">
-        <v>1463.191051626954</v>
+        <v>1480.609992717751</v>
       </c>
       <c r="N86">
-        <v>-937.7910516269537</v>
+        <v>-955.2099927177508</v>
       </c>
       <c r="O86">
-        <v>-187.5582103253907</v>
+        <v>-191.0419985435502</v>
       </c>
       <c r="P86">
-        <v>-750.232841301563</v>
+        <v>-764.1679941742007</v>
       </c>
       <c r="Q86">
-        <v>-438.032841301563</v>
+        <v>-451.9679941742007</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1979719982152683</v>
+        <v>0.2081167980962862</v>
       </c>
       <c r="T86">
-        <v>3.128816447109127</v>
+        <v>3.337404210249735</v>
       </c>
       <c r="U86">
         <v>0.2047577444416894</v>
       </c>
       <c r="V86">
-        <v>0.07181563875965431</v>
+        <v>0.07097074889189368</v>
       </c>
       <c r="W86">
-        <v>0.1900529362336234</v>
+        <v>0.1902259339772477</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3590781937982715</v>
+        <v>0.3548537444594684</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1929095635951035</v>
+        <v>0.1944991410395204</v>
       </c>
       <c r="C87">
-        <v>-4909.845942306152</v>
+        <v>-5016.119264642068</v>
       </c>
       <c r="D87">
-        <v>2229.386987632167</v>
+        <v>2208.184640942585</v>
       </c>
       <c r="E87">
-        <v>5670.635365305001</v>
+        <v>5755.706340951335</v>
       </c>
       <c r="F87">
-        <v>7231.032929938319</v>
+        <v>7316.103905584653</v>
       </c>
       <c r="G87">
         <v>91.8</v>
@@ -8427,37 +8427,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M87">
-        <v>1480.609992717751</v>
+        <v>1498.028933808548</v>
       </c>
       <c r="N87">
-        <v>-955.2099927177508</v>
+        <v>-972.628933808548</v>
       </c>
       <c r="O87">
-        <v>-191.0419985435502</v>
+        <v>-194.5257867617096</v>
       </c>
       <c r="P87">
-        <v>-764.1679941742007</v>
+        <v>-778.1031470468384</v>
       </c>
       <c r="Q87">
-        <v>-451.9679941742007</v>
+        <v>-465.9031470468385</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2081167980962862</v>
+        <v>0.2197108551031638</v>
       </c>
       <c r="T87">
-        <v>3.337404210249735</v>
+        <v>3.575790225267574</v>
       </c>
       <c r="U87">
         <v>0.2047577444416894</v>
       </c>
       <c r="V87">
-        <v>0.07097074889189368</v>
+        <v>0.07014550762570886</v>
       </c>
       <c r="W87">
-        <v>0.1902259339772477</v>
+        <v>0.1903949085175319</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3548537444594684</v>
+        <v>0.3507275381285443</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1944991410395204</v>
+        <v>0.1960887184839373</v>
       </c>
       <c r="C88">
-        <v>-5016.119264642068</v>
+        <v>-5121.993100942667</v>
       </c>
       <c r="D88">
-        <v>2208.184640942585</v>
+        <v>2187.381780288319</v>
       </c>
       <c r="E88">
-        <v>5755.706340951335</v>
+        <v>5840.777316597668</v>
       </c>
       <c r="F88">
-        <v>7316.103905584653</v>
+        <v>7401.174881230986</v>
       </c>
       <c r="G88">
         <v>91.8</v>
@@ -8509,37 +8509,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M88">
-        <v>1498.028933808548</v>
+        <v>1515.447874899345</v>
       </c>
       <c r="N88">
-        <v>-972.628933808548</v>
+        <v>-990.0478748993451</v>
       </c>
       <c r="O88">
-        <v>-194.5257867617096</v>
+        <v>-198.009574979869</v>
       </c>
       <c r="P88">
-        <v>-778.1031470468384</v>
+        <v>-792.038299919476</v>
       </c>
       <c r="Q88">
-        <v>-465.9031470468385</v>
+        <v>-479.838299919476</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2197108551031638</v>
+        <v>0.2330886131880225</v>
       </c>
       <c r="T88">
-        <v>3.575790225267574</v>
+        <v>3.850851011826617</v>
       </c>
       <c r="U88">
         <v>0.2047577444416894</v>
       </c>
       <c r="V88">
-        <v>0.07014550762570886</v>
+        <v>0.0693392374231145</v>
       </c>
       <c r="W88">
-        <v>0.1903949085175319</v>
+        <v>0.1905599985856257</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3507275381285443</v>
+        <v>0.3466961871155725</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1960887184839373</v>
+        <v>0.1976782959283542</v>
       </c>
       <c r="C89">
-        <v>-5121.993100942667</v>
+        <v>-5227.478636267069</v>
       </c>
       <c r="D89">
-        <v>2187.381780288319</v>
+        <v>2166.967220610249</v>
       </c>
       <c r="E89">
-        <v>5840.777316597668</v>
+        <v>5925.848292244001</v>
       </c>
       <c r="F89">
-        <v>7401.174881230986</v>
+        <v>7486.245856877319</v>
       </c>
       <c r="G89">
         <v>91.8</v>
@@ -8591,37 +8591,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M89">
-        <v>1515.447874899345</v>
+        <v>1532.866815990142</v>
       </c>
       <c r="N89">
-        <v>-990.0478748993451</v>
+        <v>-1007.466815990142</v>
       </c>
       <c r="O89">
-        <v>-198.009574979869</v>
+        <v>-201.4933631980284</v>
       </c>
       <c r="P89">
-        <v>-792.038299919476</v>
+        <v>-805.9734527921137</v>
       </c>
       <c r="Q89">
-        <v>-479.838299919476</v>
+        <v>-493.7734527921137</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2330886131880225</v>
+        <v>0.2486959976203578</v>
       </c>
       <c r="T89">
-        <v>3.850851011826617</v>
+        <v>4.171755262812169</v>
       </c>
       <c r="U89">
         <v>0.2047577444416894</v>
       </c>
       <c r="V89">
-        <v>0.0693392374231145</v>
+        <v>0.06855129154330639</v>
       </c>
       <c r="W89">
-        <v>0.1905599985856257</v>
+        <v>0.1907213366067173</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3466961871155725</v>
+        <v>0.342756457716532</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1976782959283542</v>
+        <v>0.1992678733727711</v>
       </c>
       <c r="C90">
-        <v>-5227.478636267069</v>
+        <v>-5332.586641980335</v>
       </c>
       <c r="D90">
-        <v>2166.967220610249</v>
+        <v>2146.930190543317</v>
       </c>
       <c r="E90">
-        <v>5925.848292244001</v>
+        <v>6010.919267890334</v>
       </c>
       <c r="F90">
-        <v>7486.245856877319</v>
+        <v>7571.316832523652</v>
       </c>
       <c r="G90">
         <v>91.8</v>
@@ -8673,37 +8673,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M90">
-        <v>1532.866815990142</v>
+        <v>1550.285757080939</v>
       </c>
       <c r="N90">
-        <v>-1007.466815990142</v>
+        <v>-1024.885757080939</v>
       </c>
       <c r="O90">
-        <v>-201.4933631980284</v>
+        <v>-204.9771514161878</v>
       </c>
       <c r="P90">
-        <v>-805.9734527921137</v>
+        <v>-819.9086056647513</v>
       </c>
       <c r="Q90">
-        <v>-493.7734527921137</v>
+        <v>-507.7086056647514</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2486959976203578</v>
+        <v>0.2671410883131176</v>
       </c>
       <c r="T90">
-        <v>4.171755262812169</v>
+        <v>4.55100574124964</v>
       </c>
       <c r="U90">
         <v>0.2047577444416894</v>
       </c>
       <c r="V90">
-        <v>0.06855129154330639</v>
+        <v>0.06778105231248271</v>
       </c>
       <c r="W90">
-        <v>0.1907213366067173</v>
+        <v>0.1908790490543013</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.342756457716532</v>
+        <v>0.3389052615624136</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1992678733727711</v>
+        <v>0.2008574508171879</v>
       </c>
       <c r="C91">
-        <v>-5332.586641980335</v>
+        <v>-5437.327494704502</v>
       </c>
       <c r="D91">
-        <v>2146.930190543317</v>
+        <v>2127.260313465484</v>
       </c>
       <c r="E91">
-        <v>6010.919267890334</v>
+        <v>6095.990243536668</v>
       </c>
       <c r="F91">
-        <v>7571.316832523652</v>
+        <v>7656.387808169986</v>
       </c>
       <c r="G91">
         <v>91.8</v>
@@ -8755,37 +8755,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M91">
-        <v>1550.285757080939</v>
+        <v>1567.704698171736</v>
       </c>
       <c r="N91">
-        <v>-1024.885757080939</v>
+        <v>-1042.304698171736</v>
       </c>
       <c r="O91">
-        <v>-204.9771514161878</v>
+        <v>-208.4609396343473</v>
       </c>
       <c r="P91">
-        <v>-819.9086056647513</v>
+        <v>-833.8437585373891</v>
       </c>
       <c r="Q91">
-        <v>-507.7086056647514</v>
+        <v>-521.6437585373892</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2671410883131176</v>
+        <v>0.2892751971444294</v>
       </c>
       <c r="T91">
-        <v>4.55100574124964</v>
+        <v>5.006106315374605</v>
       </c>
       <c r="U91">
         <v>0.2047577444416894</v>
       </c>
       <c r="V91">
-        <v>0.06778105231248271</v>
+        <v>0.06702792950901068</v>
       </c>
       <c r="W91">
-        <v>0.1908790490543013</v>
+        <v>0.1910332567808278</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3389052615624136</v>
+        <v>0.3351396475450534</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2008574508171879</v>
+        <v>0.2024470282616048</v>
       </c>
       <c r="C92">
-        <v>-5437.327494704502</v>
+        <v>-5541.711194237327</v>
       </c>
       <c r="D92">
-        <v>2127.260313465484</v>
+        <v>2107.947589578992</v>
       </c>
       <c r="E92">
-        <v>6095.990243536668</v>
+        <v>6181.061219183001</v>
       </c>
       <c r="F92">
-        <v>7656.387808169986</v>
+        <v>7741.458783816319</v>
       </c>
       <c r="G92">
         <v>91.8</v>
@@ -8837,37 +8837,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M92">
-        <v>1567.704698171736</v>
+        <v>1585.123639262534</v>
       </c>
       <c r="N92">
-        <v>-1042.304698171736</v>
+        <v>-1059.723639262533</v>
       </c>
       <c r="O92">
-        <v>-208.4609396343473</v>
+        <v>-211.9447278525067</v>
       </c>
       <c r="P92">
-        <v>-833.8437585373891</v>
+        <v>-847.7789114100267</v>
       </c>
       <c r="Q92">
-        <v>-521.6437585373892</v>
+        <v>-535.5789114100266</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2892751971444294</v>
+        <v>0.3163279968271437</v>
       </c>
       <c r="T92">
-        <v>5.006106315374605</v>
+        <v>5.562340350416227</v>
       </c>
       <c r="U92">
         <v>0.2047577444416894</v>
       </c>
       <c r="V92">
-        <v>0.06702792950901068</v>
+        <v>0.06629135885506551</v>
       </c>
       <c r="W92">
-        <v>0.1910332567808278</v>
+        <v>0.1911840753265516</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3351396475450534</v>
+        <v>0.3314567942753276</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2024470282616048</v>
+        <v>0.2040366057060218</v>
       </c>
       <c r="C93">
-        <v>-5541.711194237327</v>
+        <v>-5645.747380503724</v>
       </c>
       <c r="D93">
-        <v>2107.947589578992</v>
+        <v>2088.982378958927</v>
       </c>
       <c r="E93">
-        <v>6181.061219183001</v>
+        <v>6266.132194829333</v>
       </c>
       <c r="F93">
-        <v>7741.458783816319</v>
+        <v>7826.529759462652</v>
       </c>
       <c r="G93">
         <v>91.8</v>
@@ -8919,37 +8919,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M93">
-        <v>1585.123639262534</v>
+        <v>1602.542580353331</v>
       </c>
       <c r="N93">
-        <v>-1059.723639262533</v>
+        <v>-1077.14258035333</v>
       </c>
       <c r="O93">
-        <v>-211.9447278525067</v>
+        <v>-215.4285160706661</v>
       </c>
       <c r="P93">
-        <v>-847.7789114100267</v>
+        <v>-861.7140642826644</v>
       </c>
       <c r="Q93">
-        <v>-535.5789114100266</v>
+        <v>-549.5140642826643</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3163279968271437</v>
+        <v>0.3501439964305369</v>
       </c>
       <c r="T93">
-        <v>5.562340350416227</v>
+        <v>6.257632894218259</v>
       </c>
       <c r="U93">
         <v>0.2047577444416894</v>
       </c>
       <c r="V93">
-        <v>0.06629135885506551</v>
+        <v>0.06557080060664089</v>
       </c>
       <c r="W93">
-        <v>0.1911840753265516</v>
+        <v>0.1913316152082379</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3314567942753276</v>
+        <v>0.3278540030332044</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2040366057060218</v>
+        <v>0.2056261831504387</v>
       </c>
       <c r="C94">
-        <v>-5645.747380503724</v>
+        <v>-5749.445349600309</v>
       </c>
       <c r="D94">
-        <v>2088.982378958927</v>
+        <v>2070.355385508677</v>
       </c>
       <c r="E94">
-        <v>6266.132194829333</v>
+        <v>6351.203170475667</v>
       </c>
       <c r="F94">
-        <v>7826.529759462652</v>
+        <v>7911.600735108986</v>
       </c>
       <c r="G94">
         <v>91.8</v>
@@ -9001,37 +9001,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M94">
-        <v>1602.542580353331</v>
+        <v>1619.961521444128</v>
       </c>
       <c r="N94">
-        <v>-1077.14258035333</v>
+        <v>-1094.561521444127</v>
       </c>
       <c r="O94">
-        <v>-215.4285160706661</v>
+        <v>-218.9123042888255</v>
       </c>
       <c r="P94">
-        <v>-861.7140642826644</v>
+        <v>-875.649217155302</v>
       </c>
       <c r="Q94">
-        <v>-549.5140642826643</v>
+        <v>-563.449217155302</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3501439964305369</v>
+        <v>0.3936217102063279</v>
       </c>
       <c r="T94">
-        <v>6.257632894218259</v>
+        <v>7.151580450535153</v>
       </c>
       <c r="U94">
         <v>0.2047577444416894</v>
       </c>
       <c r="V94">
-        <v>0.06557080060664089</v>
+        <v>0.06486573823452647</v>
       </c>
       <c r="W94">
-        <v>0.1913316152082379</v>
+        <v>0.1914759821892427</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3278540030332044</v>
+        <v>0.3243286911726323</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2056261831504387</v>
+        <v>0.2072157605948556</v>
       </c>
       <c r="C95">
-        <v>-5749.445349600309</v>
+        <v>-5852.814068989106</v>
       </c>
       <c r="D95">
-        <v>2070.355385508677</v>
+        <v>2052.057641766212</v>
       </c>
       <c r="E95">
-        <v>6351.203170475667</v>
+        <v>6436.274146122</v>
       </c>
       <c r="F95">
-        <v>7911.600735108986</v>
+        <v>7996.671710755319</v>
       </c>
       <c r="G95">
         <v>91.8</v>
@@ -9083,37 +9083,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M95">
-        <v>1619.961521444128</v>
+        <v>1637.380462534925</v>
       </c>
       <c r="N95">
-        <v>-1094.561521444127</v>
+        <v>-1111.980462534925</v>
       </c>
       <c r="O95">
-        <v>-218.9123042888255</v>
+        <v>-222.3960925069849</v>
       </c>
       <c r="P95">
-        <v>-875.649217155302</v>
+        <v>-889.5843700279396</v>
       </c>
       <c r="Q95">
-        <v>-563.449217155302</v>
+        <v>-577.3843700279397</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3936217102063279</v>
+        <v>0.4515919952407159</v>
       </c>
       <c r="T95">
-        <v>7.151580450535153</v>
+        <v>8.343510525624346</v>
       </c>
       <c r="U95">
         <v>0.2047577444416894</v>
       </c>
       <c r="V95">
-        <v>0.06486573823452647</v>
+        <v>0.06417567718947832</v>
       </c>
       <c r="W95">
-        <v>0.1914759821892427</v>
+        <v>0.1916172775323538</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3243286911726323</v>
+        <v>0.3208783859473916</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2072157605948556</v>
+        <v>0.2088053380392724</v>
       </c>
       <c r="C96">
-        <v>-5852.814068989106</v>
+        <v>-5955.862191892662</v>
       </c>
       <c r="D96">
-        <v>2052.057641766212</v>
+        <v>2034.08049450899</v>
       </c>
       <c r="E96">
-        <v>6436.274146122</v>
+        <v>6521.345121768333</v>
       </c>
       <c r="F96">
-        <v>7996.671710755319</v>
+        <v>8081.742686401652</v>
       </c>
       <c r="G96">
         <v>91.8</v>
@@ -9165,37 +9165,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M96">
-        <v>1637.380462534925</v>
+        <v>1654.799403625722</v>
       </c>
       <c r="N96">
-        <v>-1111.980462534925</v>
+        <v>-1129.399403625722</v>
       </c>
       <c r="O96">
-        <v>-222.3960925069849</v>
+        <v>-225.8798807251443</v>
       </c>
       <c r="P96">
-        <v>-889.5843700279396</v>
+        <v>-903.5195229005773</v>
       </c>
       <c r="Q96">
-        <v>-577.3843700279397</v>
+        <v>-591.3195229005773</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4515919952407159</v>
+        <v>0.5327503942888593</v>
       </c>
       <c r="T96">
-        <v>8.343510525624346</v>
+        <v>10.01221263074922</v>
       </c>
       <c r="U96">
         <v>0.2047577444416894</v>
       </c>
       <c r="V96">
-        <v>0.06417567718947832</v>
+        <v>0.06350014374537855</v>
       </c>
       <c r="W96">
-        <v>0.1916172775323538</v>
+        <v>0.1917555982366626</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3208783859473916</v>
+        <v>0.3175007187268928</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2088053380392724</v>
+        <v>0.2103949154836894</v>
       </c>
       <c r="C97">
-        <v>-5955.862191892662</v>
+        <v>-6058.59807093904</v>
       </c>
       <c r="D97">
-        <v>2034.08049450899</v>
+        <v>2016.415591108946</v>
       </c>
       <c r="E97">
-        <v>6521.345121768333</v>
+        <v>6606.416097414667</v>
       </c>
       <c r="F97">
-        <v>8081.742686401652</v>
+        <v>8166.813662047985</v>
       </c>
       <c r="G97">
         <v>91.8</v>
@@ -9247,37 +9247,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M97">
-        <v>1654.799403625722</v>
+        <v>1672.218344716519</v>
       </c>
       <c r="N97">
-        <v>-1129.399403625722</v>
+        <v>-1146.818344716519</v>
       </c>
       <c r="O97">
-        <v>-225.8798807251443</v>
+        <v>-229.3636689433038</v>
       </c>
       <c r="P97">
-        <v>-903.5195229005773</v>
+        <v>-917.4546757732151</v>
       </c>
       <c r="Q97">
-        <v>-591.3195229005773</v>
+        <v>-605.254675773215</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5327503942888593</v>
+        <v>0.6544879928610744</v>
       </c>
       <c r="T97">
-        <v>10.01221263074922</v>
+        <v>12.51526578843653</v>
       </c>
       <c r="U97">
         <v>0.2047577444416894</v>
       </c>
       <c r="V97">
-        <v>0.06350014374537855</v>
+        <v>0.06283868391469752</v>
       </c>
       <c r="W97">
-        <v>0.1917555982366626</v>
+        <v>0.1918910372596317</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3175007187268928</v>
+        <v>0.3141934195734876</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2103949154836893</v>
+        <v>0.2119844929281062</v>
       </c>
       <c r="C98">
-        <v>-6058.598070939039</v>
+        <v>-6161.029771101965</v>
       </c>
       <c r="D98">
-        <v>2016.415591108946</v>
+        <v>1999.054866592354</v>
       </c>
       <c r="E98">
-        <v>6606.416097414666</v>
+        <v>6691.487073061</v>
       </c>
       <c r="F98">
-        <v>8166.813662047985</v>
+        <v>8251.884637694318</v>
       </c>
       <c r="G98">
         <v>91.8</v>
@@ -9329,37 +9329,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M98">
-        <v>1672.218344716519</v>
+        <v>1689.637285807316</v>
       </c>
       <c r="N98">
-        <v>-1146.818344716519</v>
+        <v>-1164.237285807316</v>
       </c>
       <c r="O98">
-        <v>-229.3636689433037</v>
+        <v>-232.8474571614632</v>
       </c>
       <c r="P98">
-        <v>-917.4546757732148</v>
+        <v>-931.3898286458527</v>
       </c>
       <c r="Q98">
-        <v>-605.2546757732148</v>
+        <v>-619.1898286458527</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6544879928610727</v>
+        <v>0.8573839904814303</v>
       </c>
       <c r="T98">
-        <v>12.5152657884365</v>
+        <v>16.68702105124866</v>
       </c>
       <c r="U98">
         <v>0.2047577444416894</v>
       </c>
       <c r="V98">
-        <v>0.06283868391469753</v>
+        <v>0.06219086243104084</v>
       </c>
       <c r="W98">
-        <v>0.1918910372596317</v>
+        <v>0.1920236837254261</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3141934195734876</v>
+        <v>0.3109543121552042</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2119844929281062</v>
+        <v>0.2135740703725231</v>
       </c>
       <c r="C99">
-        <v>-6161.029771101965</v>
+        <v>-6263.165081978195</v>
       </c>
       <c r="D99">
-        <v>1999.054866592354</v>
+        <v>1981.990531362456</v>
       </c>
       <c r="E99">
-        <v>6691.487073061</v>
+        <v>6776.558048707333</v>
       </c>
       <c r="F99">
-        <v>8251.884637694318</v>
+        <v>8336.955613340651</v>
       </c>
       <c r="G99">
         <v>91.8</v>
@@ -9411,37 +9411,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M99">
-        <v>1689.637285807316</v>
+        <v>1707.056226898113</v>
       </c>
       <c r="N99">
-        <v>-1164.237285807316</v>
+        <v>-1181.656226898113</v>
       </c>
       <c r="O99">
-        <v>-232.8474571614632</v>
+        <v>-236.3312453796226</v>
       </c>
       <c r="P99">
-        <v>-931.3898286458527</v>
+        <v>-945.3249815184903</v>
       </c>
       <c r="Q99">
-        <v>-619.1898286458527</v>
+        <v>-633.1249815184904</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8573839904814303</v>
+        <v>1.263175985722146</v>
       </c>
       <c r="T99">
-        <v>16.68702105124866</v>
+        <v>25.030531576873</v>
       </c>
       <c r="U99">
         <v>0.2047577444416894</v>
       </c>
       <c r="V99">
-        <v>0.06219086243104084</v>
+        <v>0.06155626179398941</v>
       </c>
       <c r="W99">
-        <v>0.1920236837254261</v>
+        <v>0.19215362312049</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3109543121552042</v>
+        <v>0.307781308969947</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2135740703725231</v>
+        <v>0.21516364781694</v>
       </c>
       <c r="C100">
-        <v>-6263.165081978195</v>
+        <v>-6365.011529441415</v>
       </c>
       <c r="D100">
-        <v>1981.990531362456</v>
+        <v>1965.215059545569</v>
       </c>
       <c r="E100">
-        <v>6776.558048707333</v>
+        <v>6861.629024353666</v>
       </c>
       <c r="F100">
-        <v>8336.955613340651</v>
+        <v>8422.026588986984</v>
       </c>
       <c r="G100">
         <v>91.8</v>
@@ -9493,37 +9493,37 @@
         <v>525.4000000000001</v>
       </c>
       <c r="M100">
-        <v>1707.056226898113</v>
+        <v>1724.47516798891</v>
       </c>
       <c r="N100">
-        <v>-1181.656226898113</v>
+        <v>-1199.07516798891</v>
       </c>
       <c r="O100">
-        <v>-236.3312453796226</v>
+        <v>-239.815033597782</v>
       </c>
       <c r="P100">
-        <v>-945.3249815184903</v>
+        <v>-959.260134391128</v>
       </c>
       <c r="Q100">
-        <v>-633.1249815184904</v>
+        <v>-647.060134391128</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.263175985722146</v>
+        <v>2.480551971444291</v>
       </c>
       <c r="T100">
-        <v>25.030531576873</v>
+        <v>50.06106315374599</v>
       </c>
       <c r="U100">
         <v>0.2047577444416894</v>
       </c>
       <c r="V100">
-        <v>0.06155626179398941</v>
+        <v>0.0609344813718279</v>
       </c>
       <c r="W100">
-        <v>0.19215362312049</v>
+        <v>0.1922809374772698</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.307781308969947</v>
+        <v>0.3046724068591394</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.21516364781694</v>
-      </c>
-      <c r="C101">
-        <v>-6365.011529441415</v>
-      </c>
-      <c r="D101">
-        <v>1965.215059545569</v>
-      </c>
-      <c r="E101">
-        <v>6861.629024353666</v>
-      </c>
-      <c r="F101">
-        <v>8422.026588986984</v>
-      </c>
-      <c r="G101">
-        <v>91.8</v>
-      </c>
-      <c r="H101">
-        <v>6946.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>837.6</v>
-      </c>
-      <c r="K101">
-        <v>312.2</v>
-      </c>
-      <c r="L101">
-        <v>525.4000000000001</v>
-      </c>
-      <c r="M101">
-        <v>1724.47516798891</v>
-      </c>
-      <c r="N101">
-        <v>-1199.07516798891</v>
-      </c>
-      <c r="O101">
-        <v>-239.815033597782</v>
-      </c>
-      <c r="P101">
-        <v>-959.260134391128</v>
-      </c>
-      <c r="Q101">
-        <v>-647.060134391128</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.480551971444291</v>
-      </c>
-      <c r="T101">
-        <v>50.06106315374599</v>
-      </c>
-      <c r="U101">
-        <v>0.2047577444416894</v>
-      </c>
-      <c r="V101">
-        <v>0.0609344813718279</v>
-      </c>
-      <c r="W101">
-        <v>0.1922809374772698</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3046724068591394</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
